--- a/docs/working_documents/regression_building.xlsx
+++ b/docs/working_documents/regression_building.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/janlinzner/Projects/Master-Thesis-Spatial-Proximity-Venture-Capital/docs/working_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F42217-30A7-1240-97F6-4F90648F5207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0317EAC9-CB19-D44B-9607-843D0163967D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{181369B0-5107-194E-B3EC-08338497CAFD}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="2" xr2:uid="{181369B0-5107-194E-B3EC-08338497CAFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Network-Approach" sheetId="1" r:id="rId1"/>
+    <sheet name="Follow-On-Approach" sheetId="3" r:id="rId2"/>
+    <sheet name="Follow-On-Approach(2)" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="85">
   <si>
     <t>Model No.</t>
   </si>
@@ -137,6 +139,33 @@
     <t>seed_investor_same_city</t>
   </si>
   <si>
+    <t>homecountry_investor_in_seed_binary</t>
+  </si>
+  <si>
+    <t>number_of_founders</t>
+  </si>
+  <si>
+    <t>energy</t>
+  </si>
+  <si>
+    <t>materials</t>
+  </si>
+  <si>
+    <t>industrials</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>headquarters_country</t>
+  </si>
+  <si>
+    <t>hub_binary</t>
+  </si>
+  <si>
+    <t>b2b_binary</t>
+  </si>
+  <si>
     <t>Control 11</t>
   </si>
   <si>
@@ -161,6 +190,33 @@
     <t>Control 18</t>
   </si>
   <si>
+    <t>consumer_discretionary</t>
+  </si>
+  <si>
+    <t>consumer_staples</t>
+  </si>
+  <si>
+    <t>health_care</t>
+  </si>
+  <si>
+    <t>financials</t>
+  </si>
+  <si>
+    <t>information_technology</t>
+  </si>
+  <si>
+    <t>communication_services</t>
+  </si>
+  <si>
+    <t>utilities</t>
+  </si>
+  <si>
+    <t>real_estate</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
     <t>years_to_exit</t>
   </si>
   <si>
@@ -198,6 +254,45 @@
   </si>
   <si>
     <t>Linear Regression (Med -&gt; IV)</t>
+  </si>
+  <si>
+    <t>minimum_seed_vc_distance</t>
+  </si>
+  <si>
+    <t>follow_on_after_1_year</t>
+  </si>
+  <si>
+    <t>follow_on_after_2_year</t>
+  </si>
+  <si>
+    <t>follow_on_after_3_year</t>
+  </si>
+  <si>
+    <t>follow_on_after_4_year</t>
+  </si>
+  <si>
+    <t>follow_on_after_5_year</t>
+  </si>
+  <si>
+    <t>Logistic Regression (IV -&gt; MED)</t>
+  </si>
+  <si>
+    <t>Control 20</t>
+  </si>
+  <si>
+    <t>Control 21</t>
+  </si>
+  <si>
+    <t>number_seed_rounds</t>
+  </si>
+  <si>
+    <t>number_seed_investors</t>
+  </si>
+  <si>
+    <t>Logistic Regression (MED -&gt; DV)</t>
+  </si>
+  <si>
+    <t>all_dach_investor</t>
   </si>
 </sst>
 </file>
@@ -207,7 +302,7 @@
   <numFmts count="1">
     <numFmt numFmtId="170" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -219,6 +314,13 @@
       <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -352,15 +454,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -369,13 +474,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -384,10 +489,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -399,19 +504,40 @@
     <xf numFmtId="170" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="170" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -424,6 +550,27 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="170" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="170" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -785,24 +932,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" style="8" customWidth="1"/>
     <col min="3" max="3" width="38.5" style="1" customWidth="1"/>
     <col min="4" max="5" width="8.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="9"/>
-    <col min="7" max="7" width="32.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.1640625" style="10" customWidth="1"/>
-    <col min="9" max="9" width="19.6640625" style="9" customWidth="1"/>
-    <col min="10" max="10" width="30.83203125" style="13" customWidth="1"/>
-    <col min="11" max="11" width="30.83203125" style="7" customWidth="1"/>
-    <col min="12" max="12" width="22" style="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="28.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="30.83203125" style="7" customWidth="1"/>
-    <col min="17" max="17" width="25.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="27.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" style="10"/>
+    <col min="7" max="7" width="32.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.1640625" style="11" customWidth="1"/>
+    <col min="9" max="9" width="19.6640625" style="10" customWidth="1"/>
+    <col min="10" max="10" width="30.83203125" style="14" customWidth="1"/>
+    <col min="11" max="11" width="30.83203125" style="8" customWidth="1"/>
+    <col min="12" max="12" width="22" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="30.83203125" style="8" customWidth="1"/>
+    <col min="17" max="17" width="25.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.6640625" style="10" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="40.5" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="8.5" style="1" bestFit="1" customWidth="1"/>
@@ -820,191 +967,191 @@
     <col min="36" max="36" width="21.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="9.5" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="9.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="9.5" style="10" bestFit="1" customWidth="1"/>
     <col min="40" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:39" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="2:39" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="D1" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="Q1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="R1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="T1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="11" t="s">
+      <c r="U1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="V1" s="11" t="s">
+      <c r="V1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="W1" s="11" t="s">
+      <c r="W1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="X1" s="11" t="s">
+      <c r="X1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" s="11" t="s">
+      <c r="Y1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" s="11" t="s">
+      <c r="Z1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="AA1" s="11" t="s">
+      <c r="AA1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="AB1" s="11" t="s">
+      <c r="AB1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="AC1" s="11" t="s">
+      <c r="AC1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="11" t="s">
+      <c r="AD1" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="AE1" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF1" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG1" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="AH1" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI1" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AJ1" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK1" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="AL1" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="AM1" s="11" t="s">
+      <c r="AE1" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF1" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH1" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI1" s="12" t="s">
         <v>46</v>
       </c>
+      <c r="AJ1" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK1" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL1" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM1" s="12" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="2" spans="2:39" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
-      <c r="AF2" s="4"/>
-      <c r="AG2" s="4"/>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
-      <c r="AJ2" s="4"/>
-      <c r="AK2" s="4"/>
-      <c r="AL2" s="4"/>
-      <c r="AM2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="5"/>
+      <c r="AJ2" s="5"/>
+      <c r="AK2" s="5"/>
+      <c r="AL2" s="5"/>
+      <c r="AM2" s="6"/>
     </row>
     <row r="3" spans="2:39" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="25">
         <v>4254</v>
       </c>
       <c r="E3" s="1">
         <v>500</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="19">
         <v>9.3200000000000005E-2</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="20">
+      <c r="H3" s="27">
         <v>0.16</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="26">
         <v>5.5E-2</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="14" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1012,25 +1159,25 @@
       <c r="C4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="25">
         <v>4254</v>
       </c>
       <c r="E4" s="1">
         <v>500</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="10">
         <v>0.16200000000000001</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="29">
         <v>-7.0000000000000001E-3</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="30">
         <v>6.8000000000000005E-2</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="14" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1038,77 +1185,77 @@
       <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="25">
         <v>4254</v>
       </c>
       <c r="E5" s="1">
         <v>500</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="10">
         <v>5.1799999999999999E-2</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="15">
         <v>0.113</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="16">
         <v>0.26200000000000001</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="6" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="18">
+        <v>65</v>
+      </c>
+      <c r="D6" s="25">
         <v>587</v>
       </c>
       <c r="E6" s="1">
         <v>500</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="19">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="20">
         <v>-0.318</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="19">
         <v>0.217</v>
       </c>
-      <c r="J6" s="13" t="s">
-        <v>41</v>
+      <c r="J6" s="14" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="25">
         <v>4254</v>
       </c>
       <c r="E7" s="1">
         <v>500</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="19">
         <v>9.1999999999999998E-2</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="17">
+      <c r="G7" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" s="20">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="19">
         <v>0.40100000000000002</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="14" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1116,25 +1263,25 @@
       <c r="C8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="25">
         <v>4254</v>
       </c>
       <c r="E8" s="1">
         <v>500</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="19">
         <v>0.16200000000000001</v>
       </c>
-      <c r="G8" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" s="17">
+      <c r="G8" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="20">
         <v>0.23100000000000001</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="19">
         <v>3.9E-2</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="14" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1142,77 +1289,77 @@
       <c r="C9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="25">
         <v>4254</v>
       </c>
       <c r="E9" s="1">
         <v>500</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="19">
         <v>5.16E-2</v>
       </c>
-      <c r="G9" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="17">
+      <c r="G9" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="20">
         <v>-9.2999999999999999E-2</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="19">
         <v>0.373</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="10" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="18">
+        <v>65</v>
+      </c>
+      <c r="D10" s="25">
         <v>587</v>
       </c>
       <c r="E10" s="1">
         <v>500</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="19">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="G10" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" s="17">
+      <c r="G10" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="27">
         <v>0.97899999999999998</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="26">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="J10" s="13" t="s">
-        <v>41</v>
+      <c r="J10" s="14" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="25">
         <v>4254</v>
       </c>
       <c r="E11" s="1">
         <v>500</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="19">
         <v>9.1999999999999998E-2</v>
       </c>
-      <c r="G11" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11" s="17">
+      <c r="G11" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="20">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="19">
         <v>0.39600000000000002</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="14" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1220,25 +1367,25 @@
       <c r="C12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="25">
         <v>4254</v>
       </c>
       <c r="E12" s="1">
         <v>500</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="19">
         <v>0.16200000000000001</v>
       </c>
-      <c r="G12" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H12" s="17">
+      <c r="G12" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="20">
         <v>0.13100000000000001</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="19">
         <v>0.20799999999999999</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J12" s="14" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1246,77 +1393,77 @@
       <c r="C13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="25">
         <v>4254</v>
       </c>
       <c r="E13" s="1">
         <v>500</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="19">
         <v>5.1499999999999997E-2</v>
       </c>
-      <c r="G13" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H13" s="17">
+      <c r="G13" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="20">
         <v>-6.6000000000000003E-2</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="20">
         <v>0.53100000000000003</v>
       </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="18">
+        <v>65</v>
+      </c>
+      <c r="D14" s="25">
         <v>587</v>
       </c>
       <c r="E14" s="1">
         <v>500</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="19">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="G14" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H14" s="17">
+      <c r="G14" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" s="20">
         <v>0.35099999999999998</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="19">
         <v>0.17899999999999999</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>41</v>
+      <c r="J14" s="14" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="25">
         <v>4254</v>
       </c>
       <c r="E15" s="1">
         <v>500</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="19">
         <v>9.2100000000000001E-2</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="20">
         <v>-3.0000000000000001E-3</v>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="19">
         <v>0.25800000000000001</v>
       </c>
-      <c r="J15" s="13" t="s">
+      <c r="J15" s="14" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1324,25 +1471,25 @@
       <c r="C16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="25">
         <v>4254</v>
       </c>
       <c r="E16" s="1">
         <v>500</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="19">
         <v>0.16200000000000001</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="27">
         <v>-7.0000000000000001E-3</v>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="26">
         <v>6.8000000000000005E-2</v>
       </c>
-      <c r="J16" s="13" t="s">
+      <c r="J16" s="14" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1350,1015 +1497,3768 @@
       <c r="C17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="25">
         <v>4254</v>
       </c>
       <c r="E17" s="1">
         <v>500</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="19">
         <v>5.1400000000000001E-2</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="20">
         <v>1E-3</v>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="19">
         <v>0.75800000000000001</v>
       </c>
-      <c r="J17" s="13" t="s">
+      <c r="J17" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="18">
+        <v>65</v>
+      </c>
+      <c r="D18" s="25">
         <v>587</v>
       </c>
       <c r="E18" s="1">
         <v>500</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="19">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="20">
+      <c r="H18" s="27">
         <v>-2.4E-2</v>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="26">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="J18" s="13" t="s">
-        <v>41</v>
+      <c r="J18" s="14" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="2:39" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="4"/>
-      <c r="Z19" s="4"/>
-      <c r="AA19" s="4"/>
-      <c r="AB19" s="4"/>
-      <c r="AC19" s="4"/>
-      <c r="AD19" s="4"/>
-      <c r="AE19" s="4"/>
-      <c r="AF19" s="4"/>
-      <c r="AG19" s="4"/>
-      <c r="AH19" s="4"/>
-      <c r="AI19" s="4"/>
-      <c r="AJ19" s="4"/>
-      <c r="AK19" s="4"/>
-      <c r="AL19" s="4"/>
-      <c r="AM19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="5"/>
+      <c r="Y19" s="5"/>
+      <c r="Z19" s="5"/>
+      <c r="AA19" s="5"/>
+      <c r="AB19" s="5"/>
+      <c r="AC19" s="5"/>
+      <c r="AD19" s="5"/>
+      <c r="AE19" s="5"/>
+      <c r="AF19" s="5"/>
+      <c r="AG19" s="5"/>
+      <c r="AH19" s="5"/>
+      <c r="AI19" s="5"/>
+      <c r="AJ19" s="5"/>
+      <c r="AK19" s="5"/>
+      <c r="AL19" s="5"/>
+      <c r="AM19" s="6"/>
     </row>
     <row r="20" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="18">
+        <v>67</v>
+      </c>
+      <c r="D20" s="25">
         <v>4254</v>
       </c>
       <c r="E20" s="1">
         <v>500</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="10">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="15">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="16">
         <v>0</v>
       </c>
-      <c r="J20" s="13" t="s">
-        <v>42</v>
+      <c r="J20" s="14" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="18">
+        <v>67</v>
+      </c>
+      <c r="D21" s="25">
         <v>4254</v>
       </c>
       <c r="E21" s="1">
         <v>500</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="10">
         <v>0.14099999999999999</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="G21" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="15">
         <v>0.05</v>
       </c>
-      <c r="I21" s="15">
+      <c r="I21" s="16">
         <v>0</v>
       </c>
-      <c r="J21" s="13" t="s">
-        <v>43</v>
+      <c r="J21" s="14" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D22" s="18">
+        <v>67</v>
+      </c>
+      <c r="D22" s="25">
         <v>4254</v>
       </c>
       <c r="E22" s="1">
         <v>500</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="10">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G22" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="21">
+      <c r="H22" s="29">
         <v>0.313</v>
       </c>
-      <c r="I22" s="22">
+      <c r="I22" s="30">
         <v>0</v>
       </c>
-      <c r="J22" s="13" t="s">
-        <v>44</v>
+      <c r="J22" s="14" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="18">
+        <v>67</v>
+      </c>
+      <c r="D23" s="25">
         <v>4254</v>
       </c>
       <c r="E23" s="1">
         <v>500</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="10">
         <v>0.20100000000000001</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="G23" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="21">
+      <c r="H23" s="29">
         <v>0.61499999999999999</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23" s="30">
         <v>0</v>
       </c>
-      <c r="J23" s="13" t="s">
-        <v>45</v>
+      <c r="J23" s="14" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="18">
+        <v>67</v>
+      </c>
+      <c r="D24" s="25">
         <v>4254</v>
       </c>
       <c r="E24" s="1">
         <v>500</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="10">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="H24" s="14">
+      <c r="G24" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H24" s="15">
         <v>-1.2E-2</v>
       </c>
-      <c r="I24" s="15">
+      <c r="I24" s="16">
         <v>0</v>
       </c>
-      <c r="J24" s="13" t="s">
-        <v>42</v>
+      <c r="J24" s="14" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D25" s="18">
+        <v>67</v>
+      </c>
+      <c r="D25" s="25">
         <v>4254</v>
       </c>
       <c r="E25" s="1">
         <v>500</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="10">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="G25" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="H25" s="14">
+      <c r="G25" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H25" s="15">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I25" s="15">
+      <c r="I25" s="16">
         <v>0.30599999999999999</v>
       </c>
-      <c r="J25" s="13" t="s">
-        <v>43</v>
+      <c r="J25" s="14" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" s="18">
+        <v>67</v>
+      </c>
+      <c r="D26" s="25">
         <v>4254</v>
       </c>
       <c r="E26" s="1">
         <v>500</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="10">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="G26" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="H26" s="14">
+      <c r="G26" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H26" s="15">
         <v>-0.58899999999999997</v>
       </c>
-      <c r="I26" s="15">
+      <c r="I26" s="16">
         <v>0</v>
       </c>
-      <c r="J26" s="13" t="s">
-        <v>44</v>
+      <c r="J26" s="14" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D27" s="18">
+        <v>67</v>
+      </c>
+      <c r="D27" s="25">
         <v>4254</v>
       </c>
       <c r="E27" s="1">
         <v>500</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="10">
         <v>0.17299999999999999</v>
       </c>
-      <c r="G27" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="H27" s="14">
+      <c r="G27" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H27" s="15">
         <v>-0.19700000000000001</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="16">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="J27" s="13" t="s">
-        <v>45</v>
+      <c r="J27" s="14" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="18">
+        <v>67</v>
+      </c>
+      <c r="D28" s="25">
         <v>4254</v>
       </c>
       <c r="E28" s="1">
         <v>500</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="10">
         <v>0.159</v>
       </c>
-      <c r="G28" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H28" s="14">
+      <c r="G28" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H28" s="15">
         <v>-3.9E-2</v>
       </c>
-      <c r="I28" s="15">
+      <c r="I28" s="16">
         <v>0</v>
       </c>
-      <c r="J28" s="13" t="s">
-        <v>42</v>
+      <c r="J28" s="14" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D29" s="18">
+        <v>67</v>
+      </c>
+      <c r="D29" s="25">
         <v>4254</v>
       </c>
       <c r="E29" s="1">
         <v>500</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="10">
         <v>0.107</v>
       </c>
-      <c r="G29" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H29" s="14">
+      <c r="G29" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H29" s="15">
         <v>-3.4000000000000002E-2</v>
       </c>
-      <c r="I29" s="15">
+      <c r="I29" s="16">
         <v>0</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>43</v>
+      <c r="J29" s="14" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" s="18">
+        <v>67</v>
+      </c>
+      <c r="D30" s="25">
         <v>4254</v>
       </c>
       <c r="E30" s="1">
         <v>500</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="10">
         <v>0.20699999999999999</v>
       </c>
-      <c r="G30" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H30" s="14">
+      <c r="G30" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H30" s="15">
         <v>-1.3819999999999999</v>
       </c>
-      <c r="I30" s="15">
+      <c r="I30" s="16">
         <v>0</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>44</v>
+      <c r="J30" s="14" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D31" s="18">
+        <v>67</v>
+      </c>
+      <c r="D31" s="25">
         <v>4254</v>
       </c>
       <c r="E31" s="1">
         <v>500</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="10">
         <v>0.185</v>
       </c>
-      <c r="G31" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H31" s="14">
+      <c r="G31" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H31" s="15">
         <v>-0.46600000000000003</v>
       </c>
-      <c r="I31" s="15">
+      <c r="I31" s="16">
         <v>0</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>45</v>
+      <c r="J31" s="14" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D32" s="18">
+        <v>67</v>
+      </c>
+      <c r="D32" s="25">
         <v>4254</v>
       </c>
       <c r="E32" s="1">
         <v>500</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F32" s="10">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="G32" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H32" s="14">
+      <c r="H32" s="15">
         <v>1E-3</v>
       </c>
-      <c r="I32" s="15">
+      <c r="I32" s="16">
         <v>0</v>
       </c>
-      <c r="J32" s="13" t="s">
-        <v>42</v>
+      <c r="J32" s="14" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D33" s="18">
+        <v>67</v>
+      </c>
+      <c r="D33" s="25">
         <v>4254</v>
       </c>
       <c r="E33" s="1">
         <v>500</v>
       </c>
-      <c r="F33" s="9">
+      <c r="F33" s="10">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="G33" s="10" t="s">
+      <c r="G33" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H33" s="14">
+      <c r="H33" s="15">
         <v>-4.0000000000000002E-4</v>
       </c>
-      <c r="I33" s="15">
+      <c r="I33" s="16">
         <v>2E-3</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>43</v>
+      <c r="J33" s="14" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D34" s="18">
+        <v>67</v>
+      </c>
+      <c r="D34" s="25">
         <v>4254</v>
       </c>
       <c r="E34" s="1">
         <v>500</v>
       </c>
-      <c r="F34" s="9">
+      <c r="F34" s="10">
         <v>0.14499999999999999</v>
       </c>
-      <c r="G34" s="10" t="s">
+      <c r="G34" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H34" s="14">
+      <c r="H34" s="15">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="I34" s="15">
+      <c r="I34" s="16">
         <v>0</v>
       </c>
-      <c r="J34" s="13" t="s">
-        <v>44</v>
+      <c r="J34" s="14" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D35" s="18">
+        <v>67</v>
+      </c>
+      <c r="D35" s="25">
         <v>4254</v>
       </c>
       <c r="E35" s="1">
         <v>500</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F35" s="10">
         <v>0.17</v>
       </c>
-      <c r="G35" s="10" t="s">
+      <c r="G35" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H35" s="14">
+      <c r="H35" s="15">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I35" s="15">
+      <c r="I35" s="16">
         <v>0.13100000000000001</v>
       </c>
-      <c r="J35" s="13" t="s">
-        <v>45</v>
+      <c r="J35" s="14" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="36" spans="2:39" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
-      <c r="V36" s="4"/>
-      <c r="W36" s="4"/>
-      <c r="X36" s="4"/>
-      <c r="Y36" s="4"/>
-      <c r="Z36" s="4"/>
-      <c r="AA36" s="4"/>
-      <c r="AB36" s="4"/>
-      <c r="AC36" s="4"/>
-      <c r="AD36" s="4"/>
-      <c r="AE36" s="4"/>
-      <c r="AF36" s="4"/>
-      <c r="AG36" s="4"/>
-      <c r="AH36" s="4"/>
-      <c r="AI36" s="4"/>
-      <c r="AJ36" s="4"/>
-      <c r="AK36" s="4"/>
-      <c r="AL36" s="4"/>
-      <c r="AM36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+      <c r="U36" s="5"/>
+      <c r="V36" s="5"/>
+      <c r="W36" s="5"/>
+      <c r="X36" s="5"/>
+      <c r="Y36" s="5"/>
+      <c r="Z36" s="5"/>
+      <c r="AA36" s="5"/>
+      <c r="AB36" s="5"/>
+      <c r="AC36" s="5"/>
+      <c r="AD36" s="5"/>
+      <c r="AE36" s="5"/>
+      <c r="AF36" s="5"/>
+      <c r="AG36" s="5"/>
+      <c r="AH36" s="5"/>
+      <c r="AI36" s="5"/>
+      <c r="AJ36" s="5"/>
+      <c r="AK36" s="5"/>
+      <c r="AL36" s="5"/>
+      <c r="AM36" s="6"/>
     </row>
     <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C37" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D37" s="18">
+        <v>71</v>
+      </c>
+      <c r="D37" s="25">
         <v>4254</v>
       </c>
       <c r="E37" s="1">
         <v>500</v>
       </c>
-      <c r="F37" s="9">
+      <c r="F37" s="10">
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H37" s="23">
+        <v>60</v>
+      </c>
+      <c r="H37" s="31">
         <v>0.39400000000000002</v>
       </c>
-      <c r="I37" s="23">
+      <c r="I37" s="31">
         <v>2E-3</v>
       </c>
-      <c r="J37" s="13" t="s">
+      <c r="J37" s="14" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D38" s="18">
+        <v>71</v>
+      </c>
+      <c r="D38" s="25">
         <v>4254</v>
       </c>
       <c r="E38" s="1">
         <v>500</v>
       </c>
-      <c r="F38" s="9">
+      <c r="F38" s="10">
         <v>0.11700000000000001</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H38" s="24">
+        <v>60</v>
+      </c>
+      <c r="H38" s="32">
         <v>0.21199999999999999</v>
       </c>
-      <c r="I38" s="24">
+      <c r="I38" s="32">
         <v>2.4E-2</v>
       </c>
-      <c r="J38" s="13" t="s">
+      <c r="J38" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D39" s="18">
+        <v>71</v>
+      </c>
+      <c r="D39" s="25">
         <v>4254</v>
       </c>
       <c r="E39" s="1">
         <v>500</v>
       </c>
-      <c r="F39" s="9">
+      <c r="F39" s="10">
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H39" s="23">
+        <v>60</v>
+      </c>
+      <c r="H39" s="31">
         <v>0.214</v>
       </c>
-      <c r="I39" s="23">
+      <c r="I39" s="31">
         <v>0.03</v>
       </c>
-      <c r="J39" s="13" t="s">
+      <c r="J39" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D40" s="18">
+        <v>71</v>
+      </c>
+      <c r="D40" s="25">
         <v>4254</v>
       </c>
       <c r="E40" s="1">
         <v>500</v>
       </c>
-      <c r="F40" s="9">
+      <c r="F40" s="10">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H40" s="24">
+        <v>60</v>
+      </c>
+      <c r="H40" s="32">
         <v>-0.16200000000000001</v>
       </c>
-      <c r="I40" s="24">
+      <c r="I40" s="32">
         <v>0.94499999999999995</v>
       </c>
-      <c r="J40" s="13" t="s">
-        <v>41</v>
+      <c r="J40" s="14" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D41" s="18">
+        <v>71</v>
+      </c>
+      <c r="D41" s="25">
         <v>4254</v>
       </c>
       <c r="E41" s="1">
         <v>500</v>
       </c>
-      <c r="F41" s="9">
+      <c r="F41" s="10">
         <v>9.0999999999999998E-2</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H41" s="23">
+        <v>61</v>
+      </c>
+      <c r="H41" s="31">
         <v>0.122</v>
       </c>
-      <c r="I41" s="23">
+      <c r="I41" s="31">
         <v>0.08</v>
       </c>
-      <c r="J41" s="13" t="s">
+      <c r="J41" s="14" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D42" s="18">
+        <v>71</v>
+      </c>
+      <c r="D42" s="25">
         <v>4254</v>
       </c>
       <c r="E42" s="1">
         <v>500</v>
       </c>
-      <c r="F42" s="9">
+      <c r="F42" s="10">
         <v>0.11600000000000001</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H42" s="24">
+        <v>61</v>
+      </c>
+      <c r="H42" s="32">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="I42" s="24">
+      <c r="I42" s="32">
         <v>0.495</v>
       </c>
-      <c r="J42" s="13" t="s">
+      <c r="J42" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D43" s="18">
+        <v>71</v>
+      </c>
+      <c r="D43" s="25">
         <v>4254</v>
       </c>
       <c r="E43" s="1">
         <v>500</v>
       </c>
-      <c r="F43" s="9">
+      <c r="F43" s="10">
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H43" s="24">
+        <v>61</v>
+      </c>
+      <c r="H43" s="32">
         <v>6.3E-2</v>
       </c>
-      <c r="I43" s="24">
+      <c r="I43" s="32">
         <v>0.106</v>
       </c>
-      <c r="J43" s="13" t="s">
+      <c r="J43" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D44" s="18">
+        <v>71</v>
+      </c>
+      <c r="D44" s="25">
         <v>4254</v>
       </c>
       <c r="E44" s="1">
         <v>500</v>
       </c>
-      <c r="F44" s="9">
+      <c r="F44" s="10">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H44" s="24">
+        <v>61</v>
+      </c>
+      <c r="H44" s="32">
         <v>0.71499999999999997</v>
       </c>
-      <c r="I44" s="24">
+      <c r="I44" s="32">
         <v>-0.47699999999999998</v>
       </c>
-      <c r="J44" s="13" t="s">
-        <v>41</v>
+      <c r="J44" s="14" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D45" s="18">
+        <v>71</v>
+      </c>
+      <c r="D45" s="25">
         <v>4254</v>
       </c>
       <c r="E45" s="1">
         <v>500</v>
       </c>
-      <c r="F45" s="9">
+      <c r="F45" s="10">
         <v>9.0999999999999998E-2</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H45" s="23">
+        <v>62</v>
+      </c>
+      <c r="H45" s="31">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="I45" s="23">
+      <c r="I45" s="31">
         <v>6.8000000000000005E-2</v>
       </c>
-      <c r="J45" s="13" t="s">
+      <c r="J45" s="14" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D46" s="18">
+        <v>71</v>
+      </c>
+      <c r="D46" s="25">
         <v>4254</v>
       </c>
       <c r="E46" s="1">
         <v>500</v>
       </c>
-      <c r="F46" s="9">
+      <c r="F46" s="10">
         <v>0.11600000000000001</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H46" s="24">
+        <v>62</v>
+      </c>
+      <c r="H46" s="32">
         <v>1E-3</v>
       </c>
-      <c r="I46" s="24">
+      <c r="I46" s="32">
         <v>0.84199999999999997</v>
       </c>
-      <c r="J46" s="13" t="s">
+      <c r="J46" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D47" s="18">
+        <v>71</v>
+      </c>
+      <c r="D47" s="25">
         <v>4254</v>
       </c>
       <c r="E47" s="1">
         <v>500</v>
       </c>
-      <c r="F47" s="9">
+      <c r="F47" s="10">
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H47" s="23">
+        <v>62</v>
+      </c>
+      <c r="H47" s="31">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="I47" s="23">
+      <c r="I47" s="31">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J47" s="13" t="s">
+      <c r="J47" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D48" s="18">
+        <v>71</v>
+      </c>
+      <c r="D48" s="25">
         <v>4254</v>
       </c>
       <c r="E48" s="1">
         <v>500</v>
       </c>
-      <c r="F48" s="9">
+      <c r="F48" s="10">
         <v>5.5E-2</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H48" s="24">
+        <v>62</v>
+      </c>
+      <c r="H48" s="32">
         <v>-6.6000000000000003E-2</v>
       </c>
-      <c r="I48" s="24">
+      <c r="I48" s="32">
         <v>0.35799999999999998</v>
       </c>
-      <c r="J48" s="13" t="s">
-        <v>41</v>
+      <c r="J48" s="14" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="49" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D49" s="18">
+        <v>71</v>
+      </c>
+      <c r="D49" s="25">
         <v>4254</v>
       </c>
       <c r="E49" s="1">
         <v>500</v>
       </c>
-      <c r="F49" s="9">
+      <c r="F49" s="10">
         <v>0.09</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H49" s="24">
+        <v>63</v>
+      </c>
+      <c r="H49" s="32">
         <v>-1E-4</v>
       </c>
-      <c r="I49" s="24">
+      <c r="I49" s="32">
         <v>0.98699999999999999</v>
       </c>
-      <c r="J49" s="13" t="s">
+      <c r="J49" s="14" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="50" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D50" s="18">
+        <v>71</v>
+      </c>
+      <c r="D50" s="25">
         <v>4254</v>
       </c>
       <c r="E50" s="1">
         <v>500</v>
       </c>
-      <c r="F50" s="9">
+      <c r="F50" s="10">
         <v>0.11600000000000001</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H50" s="24">
+        <v>63</v>
+      </c>
+      <c r="H50" s="32">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="I50" s="24">
+      <c r="I50" s="32">
         <v>0.13900000000000001</v>
       </c>
-      <c r="J50" s="13" t="s">
+      <c r="J50" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="51" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D51" s="18">
+        <v>71</v>
+      </c>
+      <c r="D51" s="25">
         <v>4254</v>
       </c>
       <c r="E51" s="1">
         <v>500</v>
       </c>
-      <c r="F51" s="9">
+      <c r="F51" s="10">
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H51" s="24">
+        <v>63</v>
+      </c>
+      <c r="H51" s="32">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="I51" s="24">
+      <c r="I51" s="32">
         <v>0.19600000000000001</v>
       </c>
-      <c r="J51" s="13" t="s">
+      <c r="J51" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="52" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D52" s="18">
+        <v>71</v>
+      </c>
+      <c r="D52" s="25">
         <v>4254</v>
       </c>
       <c r="E52" s="1">
         <v>500</v>
       </c>
-      <c r="F52" s="9">
+      <c r="F52" s="10">
         <v>5.5E-2</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H52" s="24">
+        <v>63</v>
+      </c>
+      <c r="H52" s="32">
         <v>-8.1000000000000003E-2</v>
       </c>
-      <c r="I52" s="24">
+      <c r="I52" s="32">
         <v>0.33500000000000002</v>
       </c>
-      <c r="J52" s="13" t="s">
-        <v>41</v>
+      <c r="J52" s="14" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="2:39" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
-      <c r="T53" s="4"/>
-      <c r="U53" s="4"/>
-      <c r="V53" s="4"/>
-      <c r="W53" s="4"/>
-      <c r="X53" s="4"/>
-      <c r="Y53" s="4"/>
-      <c r="Z53" s="4"/>
-      <c r="AA53" s="4"/>
-      <c r="AB53" s="4"/>
-      <c r="AC53" s="4"/>
-      <c r="AD53" s="4"/>
-      <c r="AE53" s="4"/>
-      <c r="AF53" s="4"/>
-      <c r="AG53" s="4"/>
-      <c r="AH53" s="4"/>
-      <c r="AI53" s="4"/>
-      <c r="AJ53" s="4"/>
-      <c r="AK53" s="4"/>
-      <c r="AL53" s="4"/>
-      <c r="AM53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="5"/>
+      <c r="Q53" s="5"/>
+      <c r="R53" s="5"/>
+      <c r="S53" s="5"/>
+      <c r="T53" s="5"/>
+      <c r="U53" s="5"/>
+      <c r="V53" s="5"/>
+      <c r="W53" s="5"/>
+      <c r="X53" s="5"/>
+      <c r="Y53" s="5"/>
+      <c r="Z53" s="5"/>
+      <c r="AA53" s="5"/>
+      <c r="AB53" s="5"/>
+      <c r="AC53" s="5"/>
+      <c r="AD53" s="5"/>
+      <c r="AE53" s="5"/>
+      <c r="AF53" s="5"/>
+      <c r="AG53" s="5"/>
+      <c r="AH53" s="5"/>
+      <c r="AI53" s="5"/>
+      <c r="AJ53" s="5"/>
+      <c r="AK53" s="5"/>
+      <c r="AL53" s="5"/>
+      <c r="AM53" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8357EB15-6CE7-FA4D-A600-496010E71C22}">
+  <dimension ref="B1:AN68"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="4" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="38.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" style="10"/>
+    <col min="6" max="6" width="32.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.1640625" style="11" customWidth="1"/>
+    <col min="8" max="8" width="19.6640625" style="10" customWidth="1"/>
+    <col min="9" max="9" width="30.83203125" style="14" customWidth="1"/>
+    <col min="10" max="10" width="30.83203125" style="8" customWidth="1"/>
+    <col min="11" max="11" width="22" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.83203125" style="8" customWidth="1"/>
+    <col min="16" max="16" width="25.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="27.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="20.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="21.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="9.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:40" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="B1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="S1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="T1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="U1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="W1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="X1" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y1" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z1" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA1" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC1" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD1" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE1" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG1" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH1" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI1" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ1" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK1" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="AL1" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM1" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN1" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="2:40" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="5"/>
+      <c r="AJ2" s="5"/>
+      <c r="AK2" s="5"/>
+      <c r="AL2" s="5"/>
+      <c r="AM2" s="5"/>
+      <c r="AN2" s="6"/>
+    </row>
+    <row r="3" spans="2:40" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E3" s="19">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="20">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="H3" s="20">
+        <v>0.124</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E4" s="19">
+        <v>0.112</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="23">
+        <v>-0.187</v>
+      </c>
+      <c r="H4" s="10">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B5" s="34"/>
+      <c r="C5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="35">
+        <v>1454</v>
+      </c>
+      <c r="E5" s="21">
+        <v>9.6299999999999997E-2</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="18">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="H5" s="17">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="I5" s="36" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E6" s="19">
+        <v>9.9900000000000003E-2</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="20">
+        <v>-0.1</v>
+      </c>
+      <c r="H6" s="19">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B7" s="34"/>
+      <c r="C7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="35">
+        <v>1454</v>
+      </c>
+      <c r="E7" s="17">
+        <v>0.114</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="18">
+        <v>-0.39400000000000002</v>
+      </c>
+      <c r="H7" s="17">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="I7" s="36" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E8" s="19">
+        <v>9.35E-2</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="20">
+        <v>2.7E-2</v>
+      </c>
+      <c r="H8" s="19">
+        <v>0.88600000000000001</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E9" s="19">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G9" s="20">
+        <v>-0.255</v>
+      </c>
+      <c r="H9" s="19">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B10" s="34"/>
+      <c r="C10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="35">
+        <v>1454</v>
+      </c>
+      <c r="E10" s="17">
+        <v>0.122</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="18">
+        <v>-0.76600000000000001</v>
+      </c>
+      <c r="H10" s="17">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="I10" s="36" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E11" s="19">
+        <v>9.3899999999999997E-2</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="23">
+        <v>0.161</v>
+      </c>
+      <c r="H11" s="20">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E12" s="19">
+        <v>9.9699999999999997E-2</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="20">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H12" s="19">
+        <v>0.84799999999999998</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E13" s="19">
+        <v>0.113</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="20">
+        <v>4.7E-2</v>
+      </c>
+      <c r="H13" s="19">
+        <v>0.188</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E14" s="19">
+        <v>9.35E-2</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="20">
+        <v>-8.9999999999999993E-3</v>
+      </c>
+      <c r="H14" s="19">
+        <v>0.77300000000000002</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E15" s="19">
+        <v>9.9699999999999997E-2</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" s="20">
+        <v>-7.0000000000000001E-3</v>
+      </c>
+      <c r="H15" s="19">
+        <v>0.84699999999999998</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E16" s="19">
+        <v>0.113</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" s="20">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="H16" s="19">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E17" s="19">
+        <v>9.4500000000000001E-2</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" s="20">
+        <v>-0.05</v>
+      </c>
+      <c r="H17" s="20">
+        <v>0.23</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E18" s="19">
+        <v>9.9699999999999997E-2</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="33">
+        <v>-2.5000000000000001E-2</v>
+      </c>
+      <c r="H18" s="20">
+        <v>0.89</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="J18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
+    </row>
+    <row r="19" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E19" s="19">
+        <v>0.111</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="20">
+        <v>-6.5000000000000002E-2</v>
+      </c>
+      <c r="H19" s="19">
+        <v>0.79100000000000004</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="J19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11"/>
+    </row>
+    <row r="20" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E20" s="19">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="20">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="H20" s="19">
+        <v>0.72099999999999997</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11"/>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="11"/>
+    </row>
+    <row r="21" spans="2:40" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="5"/>
+      <c r="AA21" s="5"/>
+      <c r="AB21" s="5"/>
+      <c r="AC21" s="5"/>
+      <c r="AD21" s="5"/>
+      <c r="AE21" s="5"/>
+      <c r="AF21" s="5"/>
+      <c r="AG21" s="5"/>
+      <c r="AH21" s="5"/>
+      <c r="AI21" s="5"/>
+      <c r="AJ21" s="5"/>
+      <c r="AK21" s="5"/>
+      <c r="AL21" s="5"/>
+      <c r="AM21" s="5"/>
+      <c r="AN21" s="6"/>
+    </row>
+    <row r="22" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E22" s="16">
+        <v>5.3699999999999998E-2</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="15">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="H22" s="16">
+        <v>0.69399999999999995</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="35">
+        <v>1454</v>
+      </c>
+      <c r="E23" s="17">
+        <v>6.3399999999999998E-2</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" s="18">
+        <v>-0.17</v>
+      </c>
+      <c r="H23" s="17">
+        <v>0.23899999999999999</v>
+      </c>
+      <c r="I23" s="36" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="35">
+        <v>1454</v>
+      </c>
+      <c r="E24" s="17">
+        <v>8.2100000000000006E-2</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="18">
+        <v>-0.33</v>
+      </c>
+      <c r="H24" s="17">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="I24" s="36" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C25" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="35">
+        <v>1454</v>
+      </c>
+      <c r="E25" s="17">
+        <v>8.43E-2</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="18">
+        <v>-0.28100000000000003</v>
+      </c>
+      <c r="H25" s="17">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="I25" s="36" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C26" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="35">
+        <v>1454</v>
+      </c>
+      <c r="E26" s="17">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" s="37">
+        <v>-0.222</v>
+      </c>
+      <c r="H26" s="18">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="I26" s="36" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C27" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E27" s="16">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="32">
+        <v>-0.17100000000000001</v>
+      </c>
+      <c r="H27" s="15">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="35">
+        <v>1454</v>
+      </c>
+      <c r="E28" s="17">
+        <v>6.6600000000000006E-2</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="18">
+        <v>-0.505</v>
+      </c>
+      <c r="H28" s="17">
+        <v>1.4E-2</v>
+      </c>
+      <c r="I28" s="36" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C29" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" s="35">
+        <v>1454</v>
+      </c>
+      <c r="E29" s="17">
+        <v>8.4099999999999994E-2</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="18">
+        <v>-0.56599999999999995</v>
+      </c>
+      <c r="H29" s="18">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="I29" s="36" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C30" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" s="35">
+        <v>1454</v>
+      </c>
+      <c r="E30" s="17">
+        <v>8.4400000000000003E-2</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" s="18">
+        <v>-0.38400000000000001</v>
+      </c>
+      <c r="H30" s="17">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="I30" s="36" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C31" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D31" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E31" s="16">
+        <v>8.5500000000000007E-2</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G31" s="15">
+        <v>-0.33900000000000002</v>
+      </c>
+      <c r="H31" s="16">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="I31" s="14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C32" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E32" s="16">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G32" s="15">
+        <v>-0.33200000000000002</v>
+      </c>
+      <c r="H32" s="16">
+        <v>0.109</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C33" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33" s="35">
+        <v>1454</v>
+      </c>
+      <c r="E33" s="17">
+        <v>6.83E-2</v>
+      </c>
+      <c r="F33" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="G33" s="18">
+        <v>-0.55100000000000005</v>
+      </c>
+      <c r="H33" s="17">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="I33" s="36" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C34" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" s="35">
+        <v>1454</v>
+      </c>
+      <c r="E34" s="17">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="F34" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="G34" s="18">
+        <v>-0.56999999999999995</v>
+      </c>
+      <c r="H34" s="17">
+        <v>1E-3</v>
+      </c>
+      <c r="I34" s="36" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C35" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D35" s="35">
+        <v>1454</v>
+      </c>
+      <c r="E35" s="17">
+        <v>8.6599999999999996E-2</v>
+      </c>
+      <c r="F35" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="G35" s="18">
+        <v>-0.502</v>
+      </c>
+      <c r="H35" s="17">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="I35" s="36" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C36" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" s="35">
+        <v>1454</v>
+      </c>
+      <c r="E36" s="17">
+        <v>8.8599999999999998E-2</v>
+      </c>
+      <c r="F36" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="G36" s="37">
+        <v>-0.52100000000000002</v>
+      </c>
+      <c r="H36" s="17">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="I36" s="36" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C37" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E37" s="16">
+        <v>5.3800000000000001E-2</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G37" s="15">
+        <v>-2.4E-2</v>
+      </c>
+      <c r="H37" s="16">
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C38" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D38" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E38" s="16">
+        <v>6.2600000000000003E-2</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G38" s="15">
+        <v>-0.01</v>
+      </c>
+      <c r="H38" s="16">
+        <v>0.76200000000000001</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C39" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E39" s="16">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G39" s="15">
+        <v>1.6E-2</v>
+      </c>
+      <c r="H39" s="16">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="I39" s="14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C40" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D40" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E40" s="16">
+        <v>8.1900000000000001E-2</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G40" s="15">
+        <v>2E-3</v>
+      </c>
+      <c r="H40" s="16">
+        <v>0.94</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C41" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D41" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E41" s="16">
+        <v>8.3500000000000005E-2</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G41" s="15">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="H41" s="16">
+        <v>0.995</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C42" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D42" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E42" s="16">
+        <v>5.3600000000000002E-2</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G42" s="15">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="H42" s="16">
+        <v>0.76</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C43" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D43" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E43" s="16">
+        <v>6.3399999999999998E-2</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G43" s="15">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="H43" s="16">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C44" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D44" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E44" s="16">
+        <v>8.0500000000000002E-2</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G44" s="15">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="H44" s="16">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="I44" s="14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C45" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D45" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E45" s="16">
+        <v>8.2799999999999999E-2</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G45" s="15">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="H45" s="16">
+        <v>0.185</v>
+      </c>
+      <c r="I45" s="14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="46" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C46" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D46" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E46" s="16">
+        <v>8.4099999999999994E-2</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G46" s="15">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="H46" s="16">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C47" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D47" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E47" s="16">
+        <v>5.4300000000000001E-2</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G47" s="15">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="H47" s="16">
+        <v>0.33100000000000002</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="48" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C48" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D48" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E48" s="16">
+        <v>6.3899999999999998E-2</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G48" s="15">
+        <v>0.30199999999999999</v>
+      </c>
+      <c r="H48" s="16">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C49" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D49" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E49" s="16">
+        <v>7.9899999999999999E-2</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G49" s="15">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="H49" s="16">
+        <v>0.17</v>
+      </c>
+      <c r="I49" s="14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C50" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D50" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E50" s="16">
+        <v>8.3799999999999999E-2</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G50" s="15">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="H50" s="16">
+        <v>6.3E-2</v>
+      </c>
+      <c r="I50" s="14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="51" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C51" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D51" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E51" s="16">
+        <v>8.5599999999999996E-2</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G51" s="15">
+        <v>0.35899999999999999</v>
+      </c>
+      <c r="H51" s="10">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="I51" s="14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" spans="2:40" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="5"/>
+      <c r="Q52" s="5"/>
+      <c r="R52" s="5"/>
+      <c r="S52" s="5"/>
+      <c r="T52" s="5"/>
+      <c r="U52" s="5"/>
+      <c r="V52" s="5"/>
+      <c r="W52" s="5"/>
+      <c r="X52" s="5"/>
+      <c r="Y52" s="5"/>
+      <c r="Z52" s="5"/>
+      <c r="AA52" s="5"/>
+      <c r="AB52" s="5"/>
+      <c r="AC52" s="5"/>
+      <c r="AD52" s="5"/>
+      <c r="AE52" s="5"/>
+      <c r="AF52" s="5"/>
+      <c r="AG52" s="5"/>
+      <c r="AH52" s="5"/>
+      <c r="AI52" s="5"/>
+      <c r="AJ52" s="5"/>
+      <c r="AK52" s="5"/>
+      <c r="AL52" s="5"/>
+      <c r="AM52" s="5"/>
+      <c r="AN52" s="6"/>
+    </row>
+    <row r="53" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C53" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D53" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E53" s="10">
+        <v>0.115</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0.86699999999999999</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C54" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D54" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E54" s="10">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1.4950000000000001</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+      <c r="I54" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C55" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D55" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E55" s="10">
+        <v>9.3600000000000003E-2</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="I55" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="56" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C56" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D56" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E56" s="10">
+        <v>0.115</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="57" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C57" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D57" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E57" s="10">
+        <v>0.187</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G57" s="1">
+        <v>1.623</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+      <c r="I57" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C58" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D58" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E58" s="10">
+        <v>9.4200000000000006E-2</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="I58" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C59" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D59" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E59" s="10">
+        <v>0.125</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0.89700000000000002</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0</v>
+      </c>
+      <c r="I59" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="60" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C60" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D60" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E60" s="10">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G60" s="1">
+        <v>1.752</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+      <c r="I60" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C61" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D61" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E61" s="10">
+        <v>9.3899999999999997E-2</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0.123</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="I61" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C62" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D62" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E62" s="10">
+        <v>0.13</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0.96699999999999997</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0</v>
+      </c>
+      <c r="I62" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C63" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D63" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E63" s="10">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G63" s="1">
+        <v>2.0110000000000001</v>
+      </c>
+      <c r="H63" s="1">
+        <v>0</v>
+      </c>
+      <c r="I63" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C64" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D64" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E64" s="10">
+        <v>9.3799999999999994E-2</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G64" s="1">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="H64" s="1">
+        <v>0.495</v>
+      </c>
+      <c r="I64" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C65" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D65" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E65" s="10">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G65" s="1">
+        <v>1.0209999999999999</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0</v>
+      </c>
+      <c r="I65" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C66" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D66" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E66" s="10">
+        <v>0.249</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G66" s="1">
+        <v>2.2509999999999999</v>
+      </c>
+      <c r="H66" s="1">
+        <v>0</v>
+      </c>
+      <c r="I66" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C67" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D67" s="25">
+        <v>1454</v>
+      </c>
+      <c r="E67" s="10">
+        <v>9.35E-2</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G67" s="1">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="H67" s="1">
+        <v>0.753</v>
+      </c>
+      <c r="I67" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="2:40" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B68" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="5"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="5"/>
+      <c r="Q68" s="5"/>
+      <c r="R68" s="5"/>
+      <c r="S68" s="5"/>
+      <c r="T68" s="5"/>
+      <c r="U68" s="5"/>
+      <c r="V68" s="5"/>
+      <c r="W68" s="5"/>
+      <c r="X68" s="5"/>
+      <c r="Y68" s="5"/>
+      <c r="Z68" s="5"/>
+      <c r="AA68" s="5"/>
+      <c r="AB68" s="5"/>
+      <c r="AC68" s="5"/>
+      <c r="AD68" s="5"/>
+      <c r="AE68" s="5"/>
+      <c r="AF68" s="5"/>
+      <c r="AG68" s="5"/>
+      <c r="AH68" s="5"/>
+      <c r="AI68" s="5"/>
+      <c r="AJ68" s="5"/>
+      <c r="AK68" s="5"/>
+      <c r="AL68" s="5"/>
+      <c r="AM68" s="5"/>
+      <c r="AN68" s="6"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60C8367D-2CA8-8E4E-9926-6D7E32F6F721}">
+  <dimension ref="B1:AN26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="4" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="38.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" style="10"/>
+    <col min="6" max="6" width="32.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.1640625" style="11" customWidth="1"/>
+    <col min="8" max="8" width="19.6640625" style="10" customWidth="1"/>
+    <col min="9" max="9" width="30.83203125" style="14" customWidth="1"/>
+    <col min="10" max="10" width="30.83203125" style="8" customWidth="1"/>
+    <col min="11" max="11" width="22" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.83203125" style="8" customWidth="1"/>
+    <col min="16" max="16" width="25.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="27.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="20.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="21.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="9.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:40" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="B1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="S1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="T1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="U1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="W1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="X1" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y1" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z1" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA1" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC1" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD1" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE1" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG1" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH1" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI1" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ1" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK1" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="AL1" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM1" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN1" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="2:40" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="5"/>
+      <c r="AJ2" s="5"/>
+      <c r="AK2" s="5"/>
+      <c r="AL2" s="5"/>
+      <c r="AM2" s="5"/>
+      <c r="AN2" s="6"/>
+    </row>
+    <row r="3" spans="2:40" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C3" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="38">
+        <v>1557</v>
+      </c>
+      <c r="E3" s="19">
+        <v>9.3100000000000002E-2</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="20">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="H3" s="20">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="I3" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C4" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="38">
+        <v>1557</v>
+      </c>
+      <c r="E4" s="19">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="23">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="H4" s="24">
+        <v>0.68899999999999995</v>
+      </c>
+      <c r="I4" s="39" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B5" s="34"/>
+      <c r="C5" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="38">
+        <v>1557</v>
+      </c>
+      <c r="E5" s="24">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="20">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="H5" s="19">
+        <v>1.4E-2</v>
+      </c>
+      <c r="I5" s="39" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C6" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="38">
+        <v>1557</v>
+      </c>
+      <c r="E6" s="19"/>
+      <c r="F6" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="20"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="39" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B7" s="34"/>
+      <c r="C7" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="38">
+        <v>1557</v>
+      </c>
+      <c r="E7" s="19"/>
+      <c r="F7" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="20"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="39" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C8" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="38">
+        <v>1557</v>
+      </c>
+      <c r="E8" s="19"/>
+      <c r="F8" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="23"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="39" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="2:40" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5"/>
+      <c r="Z9" s="5"/>
+      <c r="AA9" s="5"/>
+      <c r="AB9" s="5"/>
+      <c r="AC9" s="5"/>
+      <c r="AD9" s="5"/>
+      <c r="AE9" s="5"/>
+      <c r="AF9" s="5"/>
+      <c r="AG9" s="5"/>
+      <c r="AH9" s="5"/>
+      <c r="AI9" s="5"/>
+      <c r="AJ9" s="5"/>
+      <c r="AK9" s="5"/>
+      <c r="AL9" s="5"/>
+      <c r="AM9" s="5"/>
+      <c r="AN9" s="6"/>
+    </row>
+    <row r="10" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C10" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="38">
+        <v>1557</v>
+      </c>
+      <c r="E10" s="19"/>
+      <c r="F10" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="20"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="39" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C11" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="38">
+        <v>1557</v>
+      </c>
+      <c r="E11" s="19"/>
+      <c r="F11" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="20"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="2:40" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C12" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="38">
+        <v>1557</v>
+      </c>
+      <c r="E12" s="19"/>
+      <c r="F12" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="20"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="K12" s="11"/>
+      <c r="L12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1"/>
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="1"/>
+      <c r="AD12" s="1"/>
+      <c r="AE12" s="1"/>
+      <c r="AF12" s="1"/>
+      <c r="AG12" s="1"/>
+      <c r="AH12" s="1"/>
+      <c r="AI12" s="1"/>
+      <c r="AJ12" s="1"/>
+      <c r="AK12" s="1"/>
+      <c r="AL12" s="1"/>
+      <c r="AM12" s="1"/>
+      <c r="AN12" s="10"/>
+    </row>
+    <row r="13" spans="2:40" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C13" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="38">
+        <v>1557</v>
+      </c>
+      <c r="E13" s="19"/>
+      <c r="F13" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" s="20"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="K13" s="11"/>
+      <c r="L13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
+      <c r="Y13" s="1"/>
+      <c r="Z13" s="1"/>
+      <c r="AA13" s="1"/>
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="1"/>
+      <c r="AD13" s="1"/>
+      <c r="AE13" s="1"/>
+      <c r="AF13" s="1"/>
+      <c r="AG13" s="1"/>
+      <c r="AH13" s="1"/>
+      <c r="AI13" s="1"/>
+      <c r="AJ13" s="1"/>
+      <c r="AK13" s="1"/>
+      <c r="AL13" s="1"/>
+      <c r="AM13" s="1"/>
+      <c r="AN13" s="10"/>
+    </row>
+    <row r="14" spans="2:40" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C14" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="38">
+        <v>1557</v>
+      </c>
+      <c r="E14" s="19"/>
+      <c r="F14" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" s="20"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="K14" s="11"/>
+      <c r="L14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1"/>
+      <c r="Z14" s="1"/>
+      <c r="AA14" s="1"/>
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="1"/>
+      <c r="AD14" s="1"/>
+      <c r="AE14" s="1"/>
+      <c r="AF14" s="1"/>
+      <c r="AG14" s="1"/>
+      <c r="AH14" s="1"/>
+      <c r="AI14" s="1"/>
+      <c r="AJ14" s="1"/>
+      <c r="AK14" s="1"/>
+      <c r="AL14" s="1"/>
+      <c r="AM14" s="1"/>
+      <c r="AN14" s="10"/>
+    </row>
+    <row r="15" spans="2:40" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C15" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="38">
+        <v>1557</v>
+      </c>
+      <c r="E15" s="19"/>
+      <c r="F15" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" s="20"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="K15" s="11"/>
+      <c r="L15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="10"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1"/>
+      <c r="AA15" s="1"/>
+      <c r="AB15" s="1"/>
+      <c r="AC15" s="1"/>
+      <c r="AD15" s="1"/>
+      <c r="AE15" s="1"/>
+      <c r="AF15" s="1"/>
+      <c r="AG15" s="1"/>
+      <c r="AH15" s="1"/>
+      <c r="AI15" s="1"/>
+      <c r="AJ15" s="1"/>
+      <c r="AK15" s="1"/>
+      <c r="AL15" s="1"/>
+      <c r="AM15" s="1"/>
+      <c r="AN15" s="10"/>
+    </row>
+    <row r="16" spans="2:40" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5"/>
+      <c r="Y16" s="5"/>
+      <c r="Z16" s="5"/>
+      <c r="AA16" s="5"/>
+      <c r="AB16" s="5"/>
+      <c r="AC16" s="5"/>
+      <c r="AD16" s="5"/>
+      <c r="AE16" s="5"/>
+      <c r="AF16" s="5"/>
+      <c r="AG16" s="5"/>
+      <c r="AH16" s="5"/>
+      <c r="AI16" s="5"/>
+      <c r="AJ16" s="5"/>
+      <c r="AK16" s="5"/>
+      <c r="AL16" s="5"/>
+      <c r="AM16" s="5"/>
+      <c r="AN16" s="6"/>
+    </row>
+    <row r="17" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="38">
+        <v>1557</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C18" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" s="38">
+        <v>1557</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="38">
+        <v>1557</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="38">
+        <v>1557</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C21" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="38">
+        <v>1557</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="38">
+        <v>1557</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="38">
+        <v>1557</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C24" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="38">
+        <v>1557</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="38">
+        <v>1557</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="2:40" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5"/>
+      <c r="S26" s="5"/>
+      <c r="T26" s="5"/>
+      <c r="U26" s="5"/>
+      <c r="V26" s="5"/>
+      <c r="W26" s="5"/>
+      <c r="X26" s="5"/>
+      <c r="Y26" s="5"/>
+      <c r="Z26" s="5"/>
+      <c r="AA26" s="5"/>
+      <c r="AB26" s="5"/>
+      <c r="AC26" s="5"/>
+      <c r="AD26" s="5"/>
+      <c r="AE26" s="5"/>
+      <c r="AF26" s="5"/>
+      <c r="AG26" s="5"/>
+      <c r="AH26" s="5"/>
+      <c r="AI26" s="5"/>
+      <c r="AJ26" s="5"/>
+      <c r="AK26" s="5"/>
+      <c r="AL26" s="5"/>
+      <c r="AM26" s="5"/>
+      <c r="AN26" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
 </file>
--- a/docs/working_documents/regression_building.xlsx
+++ b/docs/working_documents/regression_building.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/janlinzner/Projects/Master-Thesis-Spatial-Proximity-Venture-Capital/docs/working_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56BA057-0355-9346-A053-D54F9471E344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8309185-8B20-684A-BC94-1B5ECA193A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{181369B0-5107-194E-B3EC-08338497CAFD}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="513">
   <si>
     <t>Model No.</t>
   </si>
@@ -605,6 +605,9 @@
     <t>Lead VC in Seed Binary</t>
   </si>
   <si>
+    <t>Network Features</t>
+  </si>
+  <si>
     <t>earliest_seed_round_date</t>
   </si>
   <si>
@@ -1088,9 +1091,6 @@
     <t>max_seed_investor_pairwise_distance</t>
   </si>
   <si>
-    <t>gdp_growth_funding_year</t>
-  </si>
-  <si>
     <t>investment_volume_first_seed_year</t>
   </si>
   <si>
@@ -1485,6 +1485,99 @@
   </si>
   <si>
     <t>log_share_successful_startups_in_environment</t>
+  </si>
+  <si>
+    <t>gdp_growth_founding_year</t>
+  </si>
+  <si>
+    <t>high_local_net_median</t>
+  </si>
+  <si>
+    <t>local_portfolio</t>
+  </si>
+  <si>
+    <t>Local Portfolio Companies</t>
+  </si>
+  <si>
+    <t>Local Co-Investors</t>
+  </si>
+  <si>
+    <t>local_coinv</t>
+  </si>
+  <si>
+    <t>local_network_score</t>
+  </si>
+  <si>
+    <t>Number of Portfolio Companies of the Seed Investor inside 50km of the investee.</t>
+  </si>
+  <si>
+    <t>Number of Local Co-Investor Connections inside 50km of the invstee.</t>
+  </si>
+  <si>
+    <t>Aggregated Network Score between Local Portfolio and Local Investor.</t>
+  </si>
+  <si>
+    <t>Local Network Score</t>
+  </si>
+  <si>
+    <t>Network Score over the Median.</t>
+  </si>
+  <si>
+    <t>Network Score over Median</t>
+  </si>
+  <si>
+    <t>high_local_net_top20</t>
+  </si>
+  <si>
+    <t>Number Local Portfolio in Top 20</t>
+  </si>
+  <si>
+    <t>Network Score in Top 20</t>
+  </si>
+  <si>
+    <t>Network Score in the Top 20.</t>
+  </si>
+  <si>
+    <t>high_portfolio_top20</t>
+  </si>
+  <si>
+    <t>high_coinv_top20</t>
+  </si>
+  <si>
+    <t>Number of Local Companies in top 20.</t>
+  </si>
+  <si>
+    <t>Number of Local Co-Investors in top 20.</t>
+  </si>
+  <si>
+    <t>in_peer_top10_20km</t>
+  </si>
+  <si>
+    <t>Investee is in the Top10 of the peer group inside of 20km.</t>
+  </si>
+  <si>
+    <t>Top 10 of Local Network Score in Peer Group</t>
+  </si>
+  <si>
+    <t>Number Local Co-Investors  in Top 20</t>
+  </si>
+  <si>
+    <t>in_coinv_peer_top20_30km</t>
+  </si>
+  <si>
+    <t>in_portfolio_peer_top20_30km</t>
+  </si>
+  <si>
+    <t>Investee is in the Top10 of the co-investor network in the peer group inside of 30km.</t>
+  </si>
+  <si>
+    <t>Investee is in the Top10 of the portfolio company network in the peer group inside of 30km.</t>
+  </si>
+  <si>
+    <t>Top 10 in Local Investor Network in Peer Group</t>
+  </si>
+  <si>
+    <t>Top 10 in Local Portfolio Compay Netwrok  in Peer Group</t>
   </si>
 </sst>
 </file>
@@ -1556,7 +1649,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1602,6 +1695,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF5FBB2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0FFFC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1739,7 +1838,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1886,10 +1985,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1903,32 +2002,124 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="73">
+  <dxfs count="81">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFD0FFFC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2725,6 +2916,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFD0FFFC"/>
       <color rgb="FFCFE0FD"/>
       <color rgb="FFFFB7DA"/>
       <color rgb="FFCDFEC2"/>
@@ -2734,7 +2926,6 @@
       <color rgb="FFD1CBFE"/>
       <color rgb="FFB5B7FF"/>
       <color rgb="FFFBCEFD"/>
-      <color rgb="FFD0FFFC"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2749,128 +2940,142 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BADFB1E4-A7C4-874C-A19A-5FD297EA24A2}" name="Table1" displayName="Table1" ref="B40:F93" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BADFB1E4-A7C4-874C-A19A-5FD297EA24A2}" name="Table1" displayName="Table1" ref="B40:F93" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30" tableBorderDxfId="29">
   <autoFilter ref="B40:F93" xr:uid="{BADFB1E4-A7C4-874C-A19A-5FD297EA24A2}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E03D4D6E-868B-3040-94BC-AAAFE476C7F6}" name="Investor Features" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{9ADA0B6F-8B1B-0F4F-B7B1-0F3B920D2A58}" name="Variable Type" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{9E85F4DB-43F3-474C-93D9-C3C9A7072DD0}" name="Description" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{BB513F81-27F0-474E-951D-968976A3735F}" name="Python Name" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{9B2453CE-6F80-AA46-8C5B-8306F91B7E95}" name="Included in Regression" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{E03D4D6E-868B-3040-94BC-AAAFE476C7F6}" name="Investor Features" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{9ADA0B6F-8B1B-0F4F-B7B1-0F3B920D2A58}" name="Variable Type" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{9E85F4DB-43F3-474C-93D9-C3C9A7072DD0}" name="Description" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{BB513F81-27F0-474E-951D-968976A3735F}" name="Python Name" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{9B2453CE-6F80-AA46-8C5B-8306F91B7E95}" name="Included in Regression" dataDxfId="24"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C84D18D9-9362-E54C-A5AF-6AFDC1063900}" name="Table11" displayName="Table11" ref="B119:F129" totalsRowShown="0" headerRowDxfId="6" dataDxfId="7" tableBorderDxfId="5">
+  <autoFilter ref="B119:F129" xr:uid="{C84D18D9-9362-E54C-A5AF-6AFDC1063900}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{4E02C00A-6BF8-9745-BACF-E11A643B1EEE}" name="Network Features" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{8D1B5241-A8B2-564E-B8C3-2F886210B738}" name="Variable Type" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{F97DCEC8-EC30-324A-B0FA-D13F0F3CE3BD}" name="Description" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{1DF7C485-2E8E-7A4B-B271-2C504843FEA5}" name="Python Name" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{39138546-0198-2841-8098-4923005C4B02}" name="Included in Regression" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{625C1DBF-28AB-ED4A-8087-CF30592A3B8C}" name="Table2" displayName="Table2" ref="B29:F38" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39" tableBorderDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{625C1DBF-28AB-ED4A-8087-CF30592A3B8C}" name="Table2" displayName="Table2" ref="B29:F38" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47" tableBorderDxfId="46">
   <autoFilter ref="B29:F38" xr:uid="{625C1DBF-28AB-ED4A-8087-CF30592A3B8C}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{20474591-85CB-DC49-904A-CF74017E751E}" name="Financing Features" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{643A3B57-58F9-FA49-A71E-8AAAF9F357F4}" name="Variable Type" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{29BAC5AE-0587-8448-A26D-9A751AA6EA5F}" name="Description" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{0DC99CEA-4726-7944-B7A8-9A034F09E13E}" name="Python Name" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{9565D1F9-0041-184B-8554-0A294D69D62C}" name="Included in Regression" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{20474591-85CB-DC49-904A-CF74017E751E}" name="Financing Features" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{643A3B57-58F9-FA49-A71E-8AAAF9F357F4}" name="Variable Type" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{29BAC5AE-0587-8448-A26D-9A751AA6EA5F}" name="Description" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{0DC99CEA-4726-7944-B7A8-9A034F09E13E}" name="Python Name" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{9565D1F9-0041-184B-8554-0A294D69D62C}" name="Included in Regression" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{38B2AC38-DF34-1642-A67A-9068B8D4B9B8}" name="Table3" displayName="Table3" ref="B5:F27" totalsRowShown="0" headerRowDxfId="69" dataDxfId="70" tableBorderDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{38B2AC38-DF34-1642-A67A-9068B8D4B9B8}" name="Table3" displayName="Table3" ref="B5:F27" totalsRowShown="0" headerRowDxfId="77" dataDxfId="78" tableBorderDxfId="76">
   <autoFilter ref="B5:F27" xr:uid="{38B2AC38-DF34-1642-A67A-9068B8D4B9B8}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{91BCE79A-2728-BD48-B1E2-E0BE3627F475}" name="Company Features" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{B0E758A9-1977-FF47-9F51-CB5D5D966A07}" name="Variable Type" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{3CC6868F-603E-6F4A-963E-C8274B262C23}" name="Description" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{585F4B8D-EA90-F54D-9E4D-5B254A2FB5B4}" name="Python Name" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{97E9DD2D-1349-E84D-8FC1-1E1CA70302C2}" name="Included in Regression" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{91BCE79A-2728-BD48-B1E2-E0BE3627F475}" name="Company Features" dataDxfId="75"/>
+    <tableColumn id="2" xr3:uid="{B0E758A9-1977-FF47-9F51-CB5D5D966A07}" name="Variable Type" dataDxfId="74"/>
+    <tableColumn id="3" xr3:uid="{3CC6868F-603E-6F4A-963E-C8274B262C23}" name="Description" dataDxfId="73"/>
+    <tableColumn id="4" xr3:uid="{585F4B8D-EA90-F54D-9E4D-5B254A2FB5B4}" name="Python Name" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{97E9DD2D-1349-E84D-8FC1-1E1CA70302C2}" name="Included in Regression" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C288A2F5-FAF5-CC45-A73C-1CA5284AEB54}" name="Table4" displayName="Table4" ref="B104:F117" totalsRowShown="0" headerRowDxfId="63" dataDxfId="64" tableBorderDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C288A2F5-FAF5-CC45-A73C-1CA5284AEB54}" name="Table4" displayName="Table4" ref="B104:F117" totalsRowShown="0" headerRowDxfId="71" dataDxfId="72" tableBorderDxfId="70">
   <autoFilter ref="B104:F117" xr:uid="{C288A2F5-FAF5-CC45-A73C-1CA5284AEB54}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{AE66DA98-FE07-294A-AA12-55D5C6B9D761}" name="Distance Features (in 1000 km)" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{6C5E990C-FE6B-604E-8D81-B062F12ADAA9}" name="Variable Type" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{6F12EF53-64A3-6A48-B3C6-A4A474157490}" name="Description" dataDxfId="59"/>
-    <tableColumn id="4" xr3:uid="{3294DA05-5CD6-B645-84CF-1674E36445AC}" name="Python Name" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{4FDF6985-4069-6F4A-9349-D895903553A5}" name="Included in Regression" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{AE66DA98-FE07-294A-AA12-55D5C6B9D761}" name="Distance Features (in 1000 km)" dataDxfId="69"/>
+    <tableColumn id="2" xr3:uid="{6C5E990C-FE6B-604E-8D81-B062F12ADAA9}" name="Variable Type" dataDxfId="68"/>
+    <tableColumn id="3" xr3:uid="{6F12EF53-64A3-6A48-B3C6-A4A474157490}" name="Description" dataDxfId="67"/>
+    <tableColumn id="4" xr3:uid="{3294DA05-5CD6-B645-84CF-1674E36445AC}" name="Python Name" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{4FDF6985-4069-6F4A-9349-D895903553A5}" name="Included in Regression" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F0E04D94-3B0E-964F-A888-9EDE8C1AD5F6}" name="Table5" displayName="Table5" ref="B95:F102" totalsRowShown="0" headerRowDxfId="57" dataDxfId="58" tableBorderDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F0E04D94-3B0E-964F-A888-9EDE8C1AD5F6}" name="Table5" displayName="Table5" ref="B95:F102" totalsRowShown="0" headerRowDxfId="65" dataDxfId="66" tableBorderDxfId="64">
   <autoFilter ref="B95:F102" xr:uid="{F0E04D94-3B0E-964F-A888-9EDE8C1AD5F6}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{4BA769C3-20C7-694B-B63D-500312785390}" name="Ecosystem Features" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{C7CBBF4E-E32C-5349-BA5F-ACCF31548549}" name="Variable Type" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{0E50E825-3168-CD4E-8A02-1102911C878A}" name="Description" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{D91E7EE0-E148-C345-B2BC-7CBDAD7BBADB}" name="Python Name" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{554C6F2A-7F7F-B044-9CE9-308E8756EA24}" name="Included in Regression" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{4BA769C3-20C7-694B-B63D-500312785390}" name="Ecosystem Features" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{C7CBBF4E-E32C-5349-BA5F-ACCF31548549}" name="Variable Type" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{0E50E825-3168-CD4E-8A02-1102911C878A}" name="Description" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{D91E7EE0-E148-C345-B2BC-7CBDAD7BBADB}" name="Python Name" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{554C6F2A-7F7F-B044-9CE9-308E8756EA24}" name="Included in Regression" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2E3D645F-AC26-DF46-BD5D-EBAB2942DB82}" name="Table6" displayName="Table6" ref="B123:F131" totalsRowShown="0" headerRowDxfId="47" dataDxfId="48" tableBorderDxfId="52">
-  <autoFilter ref="B123:F131" xr:uid="{2E3D645F-AC26-DF46-BD5D-EBAB2942DB82}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2E3D645F-AC26-DF46-BD5D-EBAB2942DB82}" name="Table6" displayName="Table6" ref="B135:F143" totalsRowShown="0" headerRowDxfId="55" dataDxfId="56" tableBorderDxfId="60">
+  <autoFilter ref="B135:F143" xr:uid="{2E3D645F-AC26-DF46-BD5D-EBAB2942DB82}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B6190453-A34F-B84E-8F2A-A1D958E4DB06}" name="Outcome Features" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{634432B5-6BC9-564F-B291-C6D01B8BD2DB}" name="Variable Type" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{C237EC30-178A-9142-A609-E72AA6B75365}" name="Description" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{AD7FDDDF-AD6A-0E42-B0D5-6147F92F3B1C}" name="Python Name" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{683EFBFB-1FC6-BE47-92AE-D3D45DC2FFF9}" name="Included in Regression" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{B6190453-A34F-B84E-8F2A-A1D958E4DB06}" name="Outcome Features" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{634432B5-6BC9-564F-B291-C6D01B8BD2DB}" name="Variable Type" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{C237EC30-178A-9142-A609-E72AA6B75365}" name="Description" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{AD7FDDDF-AD6A-0E42-B0D5-6147F92F3B1C}" name="Python Name" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{683EFBFB-1FC6-BE47-92AE-D3D45DC2FFF9}" name="Included in Regression" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{44C40AD8-7805-764B-8B4F-9295490166FE}" name="Table48" displayName="Table48" ref="B119:F121" totalsRowShown="0" headerRowDxfId="41" dataDxfId="46" tableBorderDxfId="45">
-  <autoFilter ref="B119:F121" xr:uid="{44C40AD8-7805-764B-8B4F-9295490166FE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{44C40AD8-7805-764B-8B4F-9295490166FE}" name="Table48" displayName="Table48" ref="B131:F133" totalsRowShown="0" headerRowDxfId="49" dataDxfId="54" tableBorderDxfId="53">
+  <autoFilter ref="B131:F133" xr:uid="{44C40AD8-7805-764B-8B4F-9295490166FE}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9969B5D0-6C94-A14A-9C38-C48420232A9C}" name="Economical Features" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{02D99B72-6F40-A04C-9824-719B2293FF60}" name="Variable Type" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{ED9501AA-C011-0B4E-8C8B-EF6E06D6B929}" name="Description" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{31AA41E3-0659-F045-A067-096A82B81B9A}" name="Python Name" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{9F2FC2F9-C4B3-BC4D-889C-B89393759E93}" name="Included in Regression" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{9969B5D0-6C94-A14A-9C38-C48420232A9C}" name="Economical Features" dataDxfId="52"/>
+    <tableColumn id="2" xr3:uid="{02D99B72-6F40-A04C-9824-719B2293FF60}" name="Variable Type" dataDxfId="51"/>
+    <tableColumn id="3" xr3:uid="{ED9501AA-C011-0B4E-8C8B-EF6E06D6B929}" name="Description" dataDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{31AA41E3-0659-F045-A067-096A82B81B9A}" name="Python Name" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{9F2FC2F9-C4B3-BC4D-889C-B89393759E93}" name="Included in Regression" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{6DEEB368-0C4F-284A-B8BF-76292D1E564D}" name="Table310" displayName="Table310" ref="B134:F140" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" tableBorderDxfId="13">
-  <autoFilter ref="B134:F140" xr:uid="{6DEEB368-0C4F-284A-B8BF-76292D1E564D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{6DEEB368-0C4F-284A-B8BF-76292D1E564D}" name="Table310" displayName="Table310" ref="B146:F152" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
+  <autoFilter ref="B146:F152" xr:uid="{6DEEB368-0C4F-284A-B8BF-76292D1E564D}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{456BE63F-58FC-C941-82F8-F6ABD1A7C06C}" name="Features" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{F8D792A3-C29A-9F4B-843D-23EE6D488A01}" name="Variable Type" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{0512FD64-43A9-A94F-81EF-D503F7970A81}" name="Description" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{0CAA4F0C-80CE-C946-A1B7-7B769A31B90F}" name="Paper" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{78AA5131-E9A3-4944-8C53-340972E86CF5}" name="Possible?" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{456BE63F-58FC-C941-82F8-F6ABD1A7C06C}" name="Features" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{F8D792A3-C29A-9F4B-843D-23EE6D488A01}" name="Variable Type" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{0512FD64-43A9-A94F-81EF-D503F7970A81}" name="Description" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{0CAA4F0C-80CE-C946-A1B7-7B769A31B90F}" name="Paper" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{78AA5131-E9A3-4944-8C53-340972E86CF5}" name="Possible?" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{11B60FFA-95BB-1845-B1CB-5FE85587B5A7}" name="Table10" displayName="Table10" ref="H5:K29" totalsRowShown="0" headerRowDxfId="6" dataDxfId="7" tableBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{11B60FFA-95BB-1845-B1CB-5FE85587B5A7}" name="Table10" displayName="Table10" ref="H5:K29" totalsRowShown="0" headerRowDxfId="14" dataDxfId="15" tableBorderDxfId="13">
   <autoFilter ref="H5:K29" xr:uid="{11B60FFA-95BB-1845-B1CB-5FE85587B5A7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H6:K29">
     <sortCondition ref="J5:J29"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0B294427-D79A-F944-8F2E-083A1E3E7736}" name="Name" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{8BE80BC7-50DB-6241-AA19-9087A9996122}" name="Description" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{769FA72C-A617-3F45-88FD-A0F271E97179}" name="Focus" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{5CDBB43C-935F-834A-B556-90DBDCAE3C91}" name="Useful" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{0B294427-D79A-F944-8F2E-083A1E3E7736}" name="Name" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{8BE80BC7-50DB-6241-AA19-9087A9996122}" name="Description" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{769FA72C-A617-3F45-88FD-A0F271E97179}" name="Focus" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{5CDBB43C-935F-834A-B556-90DBDCAE3C91}" name="Useful" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3193,13 +3398,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D84EA5FA-74C6-FF45-8301-AF21701891F8}">
-  <dimension ref="B2:K156"/>
+  <dimension ref="B2:K168"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
     <col min="2" max="2" width="46.1640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="63" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="74" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="35.6640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="24.1640625" style="45" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.1640625" style="1" customWidth="1"/>
@@ -3244,7 +3449,7 @@
         <v>129</v>
       </c>
       <c r="F5" s="59" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H5" s="55" t="s">
         <v>366</v>
@@ -3267,14 +3472,12 @@
         <v>124</v>
       </c>
       <c r="D6" s="44" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>296</v>
-      </c>
-      <c r="F6" s="60" t="b">
-        <v>0</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="F6" s="60"/>
       <c r="H6" s="44" t="s">
         <v>371</v>
       </c>
@@ -3294,14 +3497,12 @@
         <v>162</v>
       </c>
       <c r="D7" s="44" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>297</v>
-      </c>
-      <c r="F7" s="60" t="b">
-        <v>0</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="F7" s="60"/>
       <c r="H7" s="44" t="s">
         <v>373</v>
       </c>
@@ -3321,14 +3522,12 @@
         <v>162</v>
       </c>
       <c r="D8" s="44" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>298</v>
-      </c>
-      <c r="F8" s="60" t="b">
-        <v>0</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="F8" s="60"/>
       <c r="H8" s="44" t="s">
         <v>376</v>
       </c>
@@ -3348,14 +3547,12 @@
         <v>163</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E9" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="60" t="b">
-        <v>1</v>
-      </c>
+      <c r="F9" s="60"/>
       <c r="H9" s="44" t="s">
         <v>377</v>
       </c>
@@ -3375,14 +3572,12 @@
         <v>139</v>
       </c>
       <c r="D10" s="44" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>299</v>
-      </c>
-      <c r="F10" s="60" t="b">
-        <v>1</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="F10" s="60"/>
       <c r="H10" s="44" t="s">
         <v>379</v>
       </c>
@@ -3402,14 +3597,12 @@
         <v>139</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>300</v>
-      </c>
-      <c r="F11" s="60" t="b">
-        <v>1</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="F11" s="60"/>
       <c r="H11" s="44" t="s">
         <v>383</v>
       </c>
@@ -3429,14 +3622,12 @@
         <v>124</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>301</v>
-      </c>
-      <c r="F12" s="60" t="b">
-        <v>1</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="F12" s="60"/>
       <c r="H12" s="44" t="s">
         <v>384</v>
       </c>
@@ -3456,14 +3647,12 @@
         <v>124</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E13" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="60" t="b">
-        <v>1</v>
-      </c>
+      <c r="F13" s="60"/>
       <c r="H13" s="44" t="s">
         <v>395</v>
       </c>
@@ -3483,14 +3672,12 @@
         <v>123</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E14" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="60" t="b">
-        <v>1</v>
-      </c>
+      <c r="F14" s="60"/>
       <c r="H14" s="44" t="s">
         <v>386</v>
       </c>
@@ -3510,14 +3697,12 @@
         <v>123</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E15" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="60" t="b">
-        <v>1</v>
-      </c>
+      <c r="F15" s="60"/>
       <c r="H15" s="44" t="s">
         <v>388</v>
       </c>
@@ -3537,14 +3722,12 @@
         <v>123</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E16" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="60" t="b">
-        <v>1</v>
-      </c>
+      <c r="F16" s="60"/>
       <c r="H16" s="44" t="s">
         <v>389</v>
       </c>
@@ -3564,14 +3747,12 @@
         <v>123</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E17" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="60" t="b">
-        <v>1</v>
-      </c>
+      <c r="F17" s="60"/>
       <c r="H17" s="44" t="s">
         <v>394</v>
       </c>
@@ -3591,14 +3772,12 @@
         <v>123</v>
       </c>
       <c r="D18" s="44" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E18" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="F18" s="60" t="b">
-        <v>1</v>
-      </c>
+      <c r="F18" s="60"/>
       <c r="H18" s="44" t="s">
         <v>370</v>
       </c>
@@ -3618,14 +3797,12 @@
         <v>123</v>
       </c>
       <c r="D19" s="44" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E19" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="F19" s="60" t="b">
-        <v>1</v>
-      </c>
+      <c r="F19" s="60"/>
       <c r="H19" s="44" t="s">
         <v>374</v>
       </c>
@@ -3645,14 +3822,12 @@
         <v>123</v>
       </c>
       <c r="D20" s="44" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E20" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="F20" s="60" t="b">
-        <v>1</v>
-      </c>
+      <c r="F20" s="60"/>
       <c r="H20" s="44" t="s">
         <v>375</v>
       </c>
@@ -3672,14 +3847,12 @@
         <v>123</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E21" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="F21" s="60" t="b">
-        <v>1</v>
-      </c>
+      <c r="F21" s="60"/>
       <c r="H21" s="44" t="s">
         <v>378</v>
       </c>
@@ -3699,14 +3872,12 @@
         <v>123</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E22" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="F22" s="60" t="b">
-        <v>1</v>
-      </c>
+      <c r="F22" s="60"/>
       <c r="H22" s="44" t="s">
         <v>380</v>
       </c>
@@ -3726,14 +3897,12 @@
         <v>123</v>
       </c>
       <c r="D23" s="44" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E23" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="F23" s="60" t="b">
-        <v>1</v>
-      </c>
+      <c r="F23" s="60"/>
       <c r="H23" s="44" t="s">
         <v>381</v>
       </c>
@@ -3753,14 +3922,12 @@
         <v>123</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E24" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="F24" s="60" t="b">
-        <v>1</v>
-      </c>
+      <c r="F24" s="60"/>
       <c r="H24" s="44" t="s">
         <v>382</v>
       </c>
@@ -3780,14 +3947,12 @@
         <v>123</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E25" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="F25" s="60" t="b">
-        <v>1</v>
-      </c>
+      <c r="F25" s="60"/>
       <c r="H25" s="44" t="s">
         <v>385</v>
       </c>
@@ -3807,14 +3972,12 @@
         <v>123</v>
       </c>
       <c r="D26" s="44" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E26" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="F26" s="60" t="b">
-        <v>1</v>
-      </c>
+      <c r="F26" s="60"/>
       <c r="H26" s="44" t="s">
         <v>387</v>
       </c>
@@ -3834,14 +3997,12 @@
         <v>123</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E27" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="F27" s="60" t="b">
-        <v>1</v>
-      </c>
+      <c r="F27" s="60"/>
       <c r="H27" s="44" t="s">
         <v>391</v>
       </c>
@@ -3884,7 +4045,7 @@
         <v>129</v>
       </c>
       <c r="F29" s="61" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H29" s="44" t="s">
         <v>393</v>
@@ -3910,9 +4071,7 @@
       <c r="E30" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="F30" s="60" t="b">
-        <v>1</v>
-      </c>
+      <c r="F30" s="60"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B31" s="44" t="s">
@@ -3922,14 +4081,12 @@
         <v>124</v>
       </c>
       <c r="D31" s="44" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E31" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="F31" s="60" t="b">
-        <v>1</v>
-      </c>
+      <c r="F31" s="60"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B32" s="44" t="s">
@@ -3939,14 +4096,12 @@
         <v>124</v>
       </c>
       <c r="D32" s="44" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E32" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="F32" s="60" t="b">
-        <v>1</v>
-      </c>
+      <c r="F32" s="60"/>
       <c r="H32" s="2" t="s">
         <v>424</v>
       </c>
@@ -3959,14 +4114,12 @@
         <v>124</v>
       </c>
       <c r="D33" s="44" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>302</v>
-      </c>
-      <c r="F33" s="60" t="b">
-        <v>0</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="F33" s="60"/>
       <c r="H33" s="1" t="s">
         <v>420</v>
       </c>
@@ -3979,54 +4132,48 @@
         <v>139</v>
       </c>
       <c r="D34" s="44" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E34" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="F34" s="60" t="b">
-        <v>0</v>
-      </c>
+      <c r="F34" s="60"/>
       <c r="H34" s="1" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="44" t="s">
+        <v>190</v>
+      </c>
+      <c r="C35" s="44" t="s">
+        <v>191</v>
+      </c>
+      <c r="D35" s="44" t="s">
+        <v>230</v>
+      </c>
+      <c r="E35" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="C35" s="44" t="s">
-        <v>190</v>
-      </c>
-      <c r="D35" s="44" t="s">
-        <v>229</v>
-      </c>
-      <c r="E35" s="44" t="s">
-        <v>188</v>
-      </c>
-      <c r="F35" s="60" t="b">
-        <v>0</v>
-      </c>
+      <c r="F35" s="60"/>
       <c r="H35" s="1" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="44" t="s">
+        <v>192</v>
+      </c>
+      <c r="C36" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="C36" s="44" t="s">
-        <v>190</v>
-      </c>
       <c r="D36" s="44" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>303</v>
-      </c>
-      <c r="F36" s="60" t="b">
-        <v>0</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="F36" s="60"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="44" t="s">
@@ -4041,9 +4188,7 @@
       <c r="E37" s="44" t="s">
         <v>434</v>
       </c>
-      <c r="F37" s="60" t="b">
-        <v>0</v>
-      </c>
+      <c r="F37" s="60"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="44" t="s">
@@ -4058,9 +4203,7 @@
       <c r="E38" s="44" t="s">
         <v>427</v>
       </c>
-      <c r="F38" s="60" t="b">
-        <v>1</v>
-      </c>
+      <c r="F38" s="60"/>
       <c r="H38" s="1" t="s">
         <v>428</v>
       </c>
@@ -4079,7 +4222,7 @@
         <v>129</v>
       </c>
       <c r="F40" s="62" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>429</v>
@@ -4093,14 +4236,12 @@
         <v>124</v>
       </c>
       <c r="D41" s="67" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E41" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="F41" s="68" t="b">
-        <v>0</v>
-      </c>
+      <c r="F41" s="68"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="44" t="s">
@@ -4110,13 +4251,10 @@
         <v>123</v>
       </c>
       <c r="D42" s="44" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="F42" s="45" t="b">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>430</v>
@@ -4130,13 +4268,10 @@
         <v>123</v>
       </c>
       <c r="D43" s="44" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="F43" s="45" t="b">
-        <v>0</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
@@ -4147,13 +4282,10 @@
         <v>123</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="F44" s="45" t="b">
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>431</v>
@@ -4167,13 +4299,10 @@
         <v>123</v>
       </c>
       <c r="D45" s="44" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="F45" s="45" t="b">
-        <v>0</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
@@ -4184,13 +4313,10 @@
         <v>124</v>
       </c>
       <c r="D46" s="44" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="F46" s="45" t="b">
-        <v>1</v>
+        <v>309</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>432</v>
@@ -4204,13 +4330,10 @@
         <v>124</v>
       </c>
       <c r="D47" s="44" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="F47" s="45" t="b">
-        <v>0</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
@@ -4221,19 +4344,16 @@
         <v>123</v>
       </c>
       <c r="D48" s="44" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F48" s="45" t="b">
-        <v>1</v>
-      </c>
       <c r="H48" s="1" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B49" s="44" t="s">
         <v>121</v>
       </c>
@@ -4241,16 +4361,13 @@
         <v>123</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="F49" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B50" s="44" t="s">
         <v>122</v>
       </c>
@@ -4258,16 +4375,13 @@
         <v>123</v>
       </c>
       <c r="D50" s="44" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F50" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
         <v>125</v>
       </c>
@@ -4275,16 +4389,13 @@
         <v>123</v>
       </c>
       <c r="D51" s="44" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="F51" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
         <v>126</v>
       </c>
@@ -4292,16 +4403,13 @@
         <v>123</v>
       </c>
       <c r="D52" s="44" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F52" s="45" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
         <v>127</v>
       </c>
@@ -4309,16 +4417,13 @@
         <v>123</v>
       </c>
       <c r="D53" s="44" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="F53" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
         <v>128</v>
       </c>
@@ -4326,16 +4431,13 @@
         <v>123</v>
       </c>
       <c r="D54" s="69" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="F54" s="45" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
         <v>132</v>
       </c>
@@ -4343,16 +4445,13 @@
         <v>123</v>
       </c>
       <c r="D55" s="69" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="F55" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
         <v>130</v>
       </c>
@@ -4360,16 +4459,13 @@
         <v>123</v>
       </c>
       <c r="D56" s="69" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="F56" s="45" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B57" s="1" t="s">
         <v>131</v>
       </c>
@@ -4377,16 +4473,13 @@
         <v>123</v>
       </c>
       <c r="D57" s="69" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="F57" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
         <v>133</v>
       </c>
@@ -4394,16 +4487,13 @@
         <v>123</v>
       </c>
       <c r="D58" s="69" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="F58" s="45" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
         <v>134</v>
       </c>
@@ -4411,16 +4501,13 @@
         <v>123</v>
       </c>
       <c r="D59" s="69" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F59" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
         <v>153</v>
       </c>
@@ -4428,16 +4515,13 @@
         <v>124</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="F60" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
         <v>154</v>
       </c>
@@ -4445,16 +4529,13 @@
         <v>124</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F61" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B62" s="1" t="s">
         <v>155</v>
       </c>
@@ -4462,16 +4543,13 @@
         <v>123</v>
       </c>
       <c r="D62" s="44" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F62" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B63" s="1" t="s">
         <v>156</v>
       </c>
@@ -4479,33 +4557,27 @@
         <v>123</v>
       </c>
       <c r="D63" s="44" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="F63" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F64" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B65" s="1" t="s">
         <v>456</v>
       </c>
@@ -4513,16 +4585,13 @@
         <v>123</v>
       </c>
       <c r="D65" s="44" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="F65" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B66" s="1" t="s">
         <v>462</v>
       </c>
@@ -4530,16 +4599,13 @@
         <v>123</v>
       </c>
       <c r="D66" s="44" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="F66" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B67" s="1" t="s">
         <v>457</v>
       </c>
@@ -4552,11 +4618,8 @@
       <c r="E67" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="F67" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B68" s="1" t="s">
         <v>463</v>
       </c>
@@ -4569,11 +4632,8 @@
       <c r="E68" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="F68" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B69" s="71" t="s">
         <v>458</v>
       </c>
@@ -4586,11 +4646,8 @@
       <c r="E69" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="F69" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B70" s="71" t="s">
         <v>464</v>
       </c>
@@ -4603,11 +4660,8 @@
       <c r="E70" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="F70" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B71" s="71" t="s">
         <v>459</v>
       </c>
@@ -4620,11 +4674,8 @@
       <c r="E71" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="F71" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B72" s="71" t="s">
         <v>465</v>
       </c>
@@ -4637,11 +4688,8 @@
       <c r="E72" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="F72" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B73" s="71" t="s">
         <v>460</v>
       </c>
@@ -4654,11 +4702,8 @@
       <c r="E73" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="F73" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B74" s="71" t="s">
         <v>466</v>
       </c>
@@ -4671,11 +4716,8 @@
       <c r="E74" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="F74" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B75" s="71" t="s">
         <v>461</v>
       </c>
@@ -4688,11 +4730,8 @@
       <c r="E75" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="F75" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B76" s="71" t="s">
         <v>467</v>
       </c>
@@ -4705,11 +4744,8 @@
       <c r="E76" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="F76" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B77" s="1" t="s">
         <v>157</v>
       </c>
@@ -4717,16 +4753,13 @@
         <v>124</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="F77" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B78" s="1" t="s">
         <v>158</v>
       </c>
@@ -4734,16 +4767,13 @@
         <v>124</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="F78" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.2">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>159</v>
       </c>
@@ -4751,16 +4781,13 @@
         <v>123</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F79" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="80" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B80" s="1" t="s">
         <v>160</v>
       </c>
@@ -4768,13 +4795,10 @@
         <v>123</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="F80" s="45" t="b">
-        <v>0</v>
+        <v>325</v>
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.2">
@@ -4790,9 +4814,6 @@
       <c r="E81" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="F81" s="45" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B82" s="1" t="s">
@@ -4802,13 +4823,10 @@
         <v>123</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="F82" s="45" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.2">
@@ -4819,13 +4837,10 @@
         <v>123</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="F83" s="45" t="b">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.2">
@@ -4836,12 +4851,10 @@
         <v>123</v>
       </c>
       <c r="D84" s="57" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E84" s="57"/>
-      <c r="F84" s="57" t="b">
-        <v>0</v>
-      </c>
+      <c r="F84" s="57"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B85" s="57" t="s">
@@ -4851,147 +4864,121 @@
         <v>123</v>
       </c>
       <c r="D85" s="57" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E85" s="57"/>
-      <c r="F85" s="57" t="b">
-        <v>0</v>
-      </c>
+      <c r="F85" s="57"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B86" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="F86" s="45" t="b">
-        <v>0</v>
+        <v>193</v>
       </c>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B87" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F87" s="45" t="b">
-        <v>0</v>
+        <v>195</v>
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B88" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="F88" s="45" t="b">
-        <v>0</v>
+        <v>197</v>
       </c>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B89" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="F89" s="45" t="b">
-        <v>0</v>
+        <v>199</v>
       </c>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B90" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F90" s="45" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B91" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F91" s="45" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B92" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="F92" s="45" t="b">
-        <v>0</v>
+        <v>331</v>
       </c>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B93" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="F93" s="45" t="b">
-        <v>0</v>
+        <v>332</v>
       </c>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.2">
@@ -5008,7 +4995,7 @@
         <v>129</v>
       </c>
       <c r="F95" s="63" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.2">
@@ -5019,13 +5006,10 @@
         <v>124</v>
       </c>
       <c r="D96" s="44" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E96" s="44" t="s">
-        <v>332</v>
-      </c>
-      <c r="F96" s="45" t="b">
-        <v>0</v>
+        <v>333</v>
       </c>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.2">
@@ -5036,14 +5020,12 @@
         <v>139</v>
       </c>
       <c r="D97" s="44" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E97" s="44" t="s">
-        <v>333</v>
-      </c>
-      <c r="F97" s="60" t="b">
-        <v>0</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="F97" s="60"/>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B98" s="1" t="s">
@@ -5053,13 +5035,10 @@
         <v>123</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="F98" s="45" t="b">
-        <v>1</v>
+        <v>335</v>
       </c>
     </row>
     <row r="99" spans="2:6" x14ac:dyDescent="0.2">
@@ -5073,10 +5052,7 @@
         <v>358</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="F99" s="45" t="b">
-        <v>0</v>
+        <v>336</v>
       </c>
     </row>
     <row r="100" spans="2:6" x14ac:dyDescent="0.2">
@@ -5087,13 +5063,10 @@
         <v>139</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="F100" s="45" t="b">
-        <v>0</v>
+        <v>337</v>
       </c>
     </row>
     <row r="101" spans="2:6" x14ac:dyDescent="0.2">
@@ -5104,13 +5077,10 @@
         <v>139</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="F101" s="45" t="b">
-        <v>0</v>
+        <v>338</v>
       </c>
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.2">
@@ -5126,9 +5096,6 @@
       <c r="E102" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="F102" s="45" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B104" s="53" t="s">
@@ -5144,7 +5111,7 @@
         <v>129</v>
       </c>
       <c r="F104" s="64" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.2">
@@ -5155,14 +5122,12 @@
         <v>139</v>
       </c>
       <c r="D105" s="44" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E105" s="44" t="s">
-        <v>338</v>
-      </c>
-      <c r="F105" s="60" t="b">
-        <v>0</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="F105" s="60"/>
     </row>
     <row r="106" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B106" s="44" t="s">
@@ -5172,14 +5137,12 @@
         <v>139</v>
       </c>
       <c r="D106" s="44" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E106" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="F106" s="60" t="b">
-        <v>0</v>
-      </c>
+      <c r="F106" s="60"/>
     </row>
     <row r="107" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B107" s="44" t="s">
@@ -5189,14 +5152,12 @@
         <v>139</v>
       </c>
       <c r="D107" s="44" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E107" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="F107" s="60" t="b">
-        <v>0</v>
-      </c>
+      <c r="F107" s="60"/>
     </row>
     <row r="108" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B108" s="1" t="s">
@@ -5206,14 +5167,12 @@
         <v>139</v>
       </c>
       <c r="D108" s="44" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="F108" s="60" t="b">
-        <v>0</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="F108" s="60"/>
     </row>
     <row r="109" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B109" s="1" t="s">
@@ -5223,14 +5182,12 @@
         <v>139</v>
       </c>
       <c r="D109" s="44" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="F109" s="60" t="b">
-        <v>0</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="F109" s="60"/>
     </row>
     <row r="110" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B110" s="1" t="s">
@@ -5240,14 +5197,12 @@
         <v>139</v>
       </c>
       <c r="D110" s="44" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="F110" s="60" t="b">
-        <v>0</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="F110" s="60"/>
     </row>
     <row r="111" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B111" s="1" t="s">
@@ -5257,14 +5212,12 @@
         <v>139</v>
       </c>
       <c r="D111" s="44" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="F111" s="60" t="b">
-        <v>0</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="F111" s="60"/>
     </row>
     <row r="112" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B112" s="1" t="s">
@@ -5274,14 +5227,12 @@
         <v>139</v>
       </c>
       <c r="D112" s="44" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="F112" s="60" t="b">
-        <v>0</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="F112" s="60"/>
     </row>
     <row r="113" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B113" s="1" t="s">
@@ -5291,14 +5242,12 @@
         <v>139</v>
       </c>
       <c r="D113" s="44" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="F113" s="60" t="b">
-        <v>0</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="F113" s="60"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B114" s="1" t="s">
@@ -5308,14 +5257,12 @@
         <v>139</v>
       </c>
       <c r="D114" s="44" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="F114" s="60" t="b">
-        <v>0</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="F114" s="60"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B115" s="1" t="s">
@@ -5325,14 +5272,12 @@
         <v>139</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="F115" s="60" t="b">
-        <v>0</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="F115" s="60"/>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B116" s="1" t="s">
@@ -5342,14 +5287,12 @@
         <v>139</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="F116" s="60" t="b">
-        <v>0</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="F116" s="60"/>
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B117" s="1" t="s">
@@ -5359,328 +5302,384 @@
         <v>139</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="F117" s="60" t="b">
-        <v>0</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="F117" s="60"/>
+    </row>
+    <row r="118" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F118" s="60"/>
     </row>
     <row r="119" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B119" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="C119" s="56" t="s">
+      <c r="B119" s="72" t="s">
+        <v>188</v>
+      </c>
+      <c r="C119" s="72" t="s">
         <v>112</v>
       </c>
-      <c r="D119" s="56" t="s">
+      <c r="D119" s="72" t="s">
         <v>113</v>
       </c>
-      <c r="E119" s="56" t="s">
+      <c r="E119" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="F119" s="66" t="s">
-        <v>247</v>
+      <c r="F119" s="73" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B120" s="44" t="s">
-        <v>166</v>
+        <v>485</v>
       </c>
       <c r="C120" s="44" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="D120" s="44" t="s">
-        <v>294</v>
+        <v>489</v>
       </c>
       <c r="E120" s="44" t="s">
-        <v>349</v>
-      </c>
-      <c r="F120" s="60" t="b">
-        <v>0</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="F120" s="60"/>
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B121" s="44" t="s">
-        <v>202</v>
+        <v>486</v>
       </c>
       <c r="C121" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="D121" s="44" t="s">
+        <v>490</v>
+      </c>
+      <c r="E121" s="44" t="s">
+        <v>487</v>
+      </c>
+      <c r="F121" s="60"/>
+    </row>
+    <row r="122" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B122" s="44" t="s">
+        <v>492</v>
+      </c>
+      <c r="C122" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="D121" s="44" t="s">
-        <v>295</v>
-      </c>
-      <c r="E121" s="44" t="s">
-        <v>350</v>
-      </c>
-      <c r="F121" s="60" t="b">
-        <v>0</v>
-      </c>
+      <c r="D122" s="44" t="s">
+        <v>491</v>
+      </c>
+      <c r="E122" s="44" t="s">
+        <v>488</v>
+      </c>
+      <c r="F122" s="60"/>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B123" s="55" t="s">
-        <v>100</v>
-      </c>
-      <c r="C123" s="55" t="s">
-        <v>112</v>
-      </c>
-      <c r="D123" s="55" t="s">
-        <v>113</v>
-      </c>
-      <c r="E123" s="55" t="s">
-        <v>129</v>
-      </c>
-      <c r="F123" s="65" t="s">
-        <v>247</v>
-      </c>
+      <c r="B123" s="44" t="s">
+        <v>494</v>
+      </c>
+      <c r="C123" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="D123" s="44" t="s">
+        <v>493</v>
+      </c>
+      <c r="E123" s="44" t="s">
+        <v>483</v>
+      </c>
+      <c r="F123" s="60"/>
     </row>
     <row r="124" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B124" s="44" t="s">
-        <v>135</v>
+        <v>497</v>
       </c>
       <c r="C124" s="44" t="s">
         <v>123</v>
       </c>
       <c r="D124" s="44" t="s">
-        <v>289</v>
+        <v>498</v>
       </c>
       <c r="E124" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="F124" s="45" t="b">
-        <v>0</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="F124" s="60"/>
     </row>
     <row r="125" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B125" s="44" t="s">
-        <v>136</v>
+        <v>496</v>
       </c>
       <c r="C125" s="44" t="s">
         <v>123</v>
       </c>
       <c r="D125" s="44" t="s">
-        <v>290</v>
+        <v>501</v>
       </c>
       <c r="E125" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="F125" s="45" t="b">
-        <v>0</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="F125" s="60"/>
     </row>
     <row r="126" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B126" s="44" t="s">
-        <v>436</v>
+        <v>506</v>
       </c>
       <c r="C126" s="44" t="s">
         <v>123</v>
       </c>
       <c r="D126" s="44" t="s">
-        <v>437</v>
+        <v>502</v>
       </c>
       <c r="E126" s="44" t="s">
-        <v>438</v>
-      </c>
-      <c r="F126" s="45" t="b">
-        <v>0</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="F126" s="60"/>
     </row>
     <row r="127" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B127" s="44" t="s">
-        <v>439</v>
-      </c>
-      <c r="C127" s="44" t="s">
+        <v>505</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D127" s="44" t="s">
-        <v>291</v>
-      </c>
-      <c r="E127" s="44" t="s">
-        <v>440</v>
-      </c>
-      <c r="F127" s="45" t="b">
-        <v>0</v>
-      </c>
+      <c r="D127" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F127" s="60"/>
     </row>
     <row r="128" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B128" s="44" t="s">
-        <v>442</v>
+        <v>511</v>
       </c>
       <c r="C128" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="D128" s="44" t="s">
+      <c r="D128" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="E128" s="44" t="s">
+        <v>507</v>
+      </c>
+      <c r="F128" s="60"/>
+    </row>
+    <row r="129" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B129" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="F129" s="60"/>
+    </row>
+    <row r="131" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B131" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="C131" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D131" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="E131" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="F131" s="66" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="132" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B132" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="C132" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="D132" s="44" t="s">
+        <v>295</v>
+      </c>
+      <c r="E132" s="44" t="s">
+        <v>482</v>
+      </c>
+      <c r="F132" s="60"/>
+    </row>
+    <row r="133" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B133" s="44" t="s">
+        <v>203</v>
+      </c>
+      <c r="C133" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="D133" s="44" t="s">
+        <v>296</v>
+      </c>
+      <c r="E133" s="44" t="s">
+        <v>350</v>
+      </c>
+      <c r="F133" s="60"/>
+    </row>
+    <row r="135" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B135" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="C135" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D135" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="E135" s="55" t="s">
+        <v>129</v>
+      </c>
+      <c r="F135" s="65" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="136" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B136" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="C136" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="D136" s="44" t="s">
+        <v>290</v>
+      </c>
+      <c r="E136" s="44" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="137" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B137" s="44" t="s">
+        <v>136</v>
+      </c>
+      <c r="C137" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="D137" s="44" t="s">
+        <v>291</v>
+      </c>
+      <c r="E137" s="44" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="138" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B138" s="44" t="s">
+        <v>436</v>
+      </c>
+      <c r="C138" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="D138" s="44" t="s">
+        <v>437</v>
+      </c>
+      <c r="E138" s="44" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="139" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B139" s="44" t="s">
+        <v>439</v>
+      </c>
+      <c r="C139" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="D139" s="44" t="s">
+        <v>292</v>
+      </c>
+      <c r="E139" s="44" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="140" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B140" s="44" t="s">
+        <v>442</v>
+      </c>
+      <c r="C140" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="D140" s="44" t="s">
         <v>443</v>
       </c>
-      <c r="E128" s="44" t="s">
+      <c r="E140" s="44" t="s">
         <v>441</v>
       </c>
-      <c r="F128" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B129" s="44" t="s">
+    </row>
+    <row r="141" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B141" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="C129" s="44" t="s">
+      <c r="C141" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="D129" s="44" t="s">
+      <c r="D141" s="44" t="s">
         <v>478</v>
       </c>
-      <c r="E129" s="44" t="s">
+      <c r="E141" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="F129" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B130" s="44" t="s">
+    </row>
+    <row r="142" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B142" s="44" t="s">
         <v>352</v>
       </c>
-      <c r="C130" s="44" t="s">
+      <c r="C142" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="D130" s="44" t="s">
-        <v>292</v>
-      </c>
-      <c r="E130" s="44" t="s">
+      <c r="D142" s="44" t="s">
+        <v>293</v>
+      </c>
+      <c r="E142" s="44" t="s">
         <v>351</v>
       </c>
-      <c r="F130" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B131" s="44" t="s">
+    </row>
+    <row r="143" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B143" s="44" t="s">
         <v>167</v>
       </c>
-      <c r="C131" s="44" t="s">
+      <c r="C143" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="D131" s="44" t="s">
-        <v>293</v>
-      </c>
-      <c r="E131" s="44" t="s">
+      <c r="D143" s="44" t="s">
+        <v>294</v>
+      </c>
+      <c r="E143" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="F131" s="45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="2:6" ht="22" x14ac:dyDescent="0.3">
-      <c r="B133" s="49" t="s">
+    </row>
+    <row r="145" spans="2:6" ht="22" x14ac:dyDescent="0.3">
+      <c r="B145" s="49" t="s">
         <v>354</v>
       </c>
-      <c r="C133" s="50"/>
-      <c r="D133" s="50"/>
-      <c r="E133" s="50"/>
-      <c r="F133" s="51"/>
-    </row>
-    <row r="134" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B134" s="52" t="s">
+      <c r="C145" s="50"/>
+      <c r="D145" s="50"/>
+      <c r="E145" s="50"/>
+      <c r="F145" s="51"/>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B146" s="52" t="s">
         <v>355</v>
       </c>
-      <c r="C134" s="52" t="s">
+      <c r="C146" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="D134" s="52" t="s">
+      <c r="D146" s="52" t="s">
         <v>113</v>
       </c>
-      <c r="E134" s="52" t="s">
+      <c r="E146" s="52" t="s">
         <v>356</v>
       </c>
-      <c r="F134" s="59" t="s">
+      <c r="F146" s="59" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="135" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B135" s="44"/>
-      <c r="C135" s="44"/>
-      <c r="D135" s="44"/>
-      <c r="E135" s="44"/>
-      <c r="F135" s="60"/>
-    </row>
-    <row r="136" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B136" s="44"/>
-      <c r="C136" s="44"/>
-      <c r="D136" s="44"/>
-      <c r="E136" s="44"/>
-      <c r="F136" s="60"/>
-    </row>
-    <row r="137" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B137" s="44"/>
-      <c r="C137" s="44"/>
-      <c r="D137" s="44"/>
-      <c r="E137" s="44"/>
-      <c r="F137" s="60"/>
-    </row>
-    <row r="138" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B138" s="44"/>
-      <c r="C138" s="44"/>
-      <c r="D138" s="44"/>
-      <c r="E138" s="44"/>
-      <c r="F138" s="60"/>
-    </row>
-    <row r="139" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B139" s="44"/>
-      <c r="C139" s="44"/>
-      <c r="D139" s="44"/>
-      <c r="E139" s="44"/>
-      <c r="F139" s="60"/>
-    </row>
-    <row r="140" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B140" s="44"/>
-      <c r="C140" s="44"/>
-      <c r="D140" s="44"/>
-      <c r="E140" s="44"/>
-      <c r="F140" s="60"/>
-    </row>
-    <row r="141" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B141" s="44"/>
-      <c r="C141" s="44"/>
-      <c r="D141" s="44"/>
-      <c r="E141" s="44"/>
-      <c r="F141" s="60"/>
-    </row>
-    <row r="142" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B142" s="44"/>
-      <c r="C142" s="44"/>
-      <c r="D142" s="44"/>
-      <c r="E142" s="44"/>
-      <c r="F142" s="60"/>
-    </row>
-    <row r="143" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B143" s="44"/>
-      <c r="C143" s="44"/>
-      <c r="D143" s="44"/>
-      <c r="E143" s="44"/>
-      <c r="F143" s="60"/>
-    </row>
-    <row r="144" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B144" s="44"/>
-      <c r="C144" s="44"/>
-      <c r="D144" s="44"/>
-      <c r="E144" s="44"/>
-      <c r="F144" s="60"/>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B145" s="44"/>
-      <c r="C145" s="44"/>
-      <c r="D145" s="44"/>
-      <c r="E145" s="44"/>
-      <c r="F145" s="60"/>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B146" s="44"/>
-      <c r="C146" s="44"/>
-      <c r="D146" s="44"/>
-      <c r="E146" s="44"/>
-      <c r="F146" s="60"/>
     </row>
     <row r="147" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B147" s="44"/>
@@ -5752,15 +5751,99 @@
       <c r="E156" s="44"/>
       <c r="F156" s="60"/>
     </row>
+    <row r="157" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B157" s="44"/>
+      <c r="C157" s="44"/>
+      <c r="D157" s="44"/>
+      <c r="E157" s="44"/>
+      <c r="F157" s="60"/>
+    </row>
+    <row r="158" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B158" s="44"/>
+      <c r="C158" s="44"/>
+      <c r="D158" s="44"/>
+      <c r="E158" s="44"/>
+      <c r="F158" s="60"/>
+    </row>
+    <row r="159" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B159" s="44"/>
+      <c r="C159" s="44"/>
+      <c r="D159" s="44"/>
+      <c r="E159" s="44"/>
+      <c r="F159" s="60"/>
+    </row>
+    <row r="160" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B160" s="44"/>
+      <c r="C160" s="44"/>
+      <c r="D160" s="44"/>
+      <c r="E160" s="44"/>
+      <c r="F160" s="60"/>
+    </row>
+    <row r="161" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B161" s="44"/>
+      <c r="C161" s="44"/>
+      <c r="D161" s="44"/>
+      <c r="E161" s="44"/>
+      <c r="F161" s="60"/>
+    </row>
+    <row r="162" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B162" s="44"/>
+      <c r="C162" s="44"/>
+      <c r="D162" s="44"/>
+      <c r="E162" s="44"/>
+      <c r="F162" s="60"/>
+    </row>
+    <row r="163" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B163" s="44"/>
+      <c r="C163" s="44"/>
+      <c r="D163" s="44"/>
+      <c r="E163" s="44"/>
+      <c r="F163" s="60"/>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B164" s="44"/>
+      <c r="C164" s="44"/>
+      <c r="D164" s="44"/>
+      <c r="E164" s="44"/>
+      <c r="F164" s="60"/>
+    </row>
+    <row r="165" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B165" s="44"/>
+      <c r="C165" s="44"/>
+      <c r="D165" s="44"/>
+      <c r="E165" s="44"/>
+      <c r="F165" s="60"/>
+    </row>
+    <row r="166" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B166" s="44"/>
+      <c r="C166" s="44"/>
+      <c r="D166" s="44"/>
+      <c r="E166" s="44"/>
+      <c r="F166" s="60"/>
+    </row>
+    <row r="167" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B167" s="44"/>
+      <c r="C167" s="44"/>
+      <c r="D167" s="44"/>
+      <c r="E167" s="44"/>
+      <c r="F167" s="60"/>
+    </row>
+    <row r="168" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B168" s="44"/>
+      <c r="C168" s="44"/>
+      <c r="D168" s="44"/>
+      <c r="E168" s="44"/>
+      <c r="F168" s="60"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="B145:F145"/>
     <mergeCell ref="H4:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-  <tableParts count="9">
+  <tableParts count="10">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
@@ -5770,6 +5853,7 @@
     <tablePart r:id="rId7"/>
     <tablePart r:id="rId8"/>
     <tablePart r:id="rId9"/>
+    <tablePart r:id="rId10"/>
   </tableParts>
 </worksheet>
 </file>

--- a/docs/working_documents/regression_building.xlsx
+++ b/docs/working_documents/regression_building.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/janlinzner/Projects/Master-Thesis-Spatial-Proximity-Venture-Capital/docs/working_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8309185-8B20-684A-BC94-1B5ECA193A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE49A37-20FC-E94D-B455-543D4C6311F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{181369B0-5107-194E-B3EC-08338497CAFD}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="531">
   <si>
     <t>Model No.</t>
   </si>
@@ -1556,9 +1556,6 @@
     <t>Investee is in the Top10 of the peer group inside of 20km.</t>
   </si>
   <si>
-    <t>Top 10 of Local Network Score in Peer Group</t>
-  </si>
-  <si>
     <t>Number Local Co-Investors  in Top 20</t>
   </si>
   <si>
@@ -1574,10 +1571,67 @@
     <t>Investee is in the Top10 of the portfolio company network in the peer group inside of 30km.</t>
   </si>
   <si>
-    <t>Top 10 in Local Investor Network in Peer Group</t>
-  </si>
-  <si>
-    <t>Top 10 in Local Portfolio Compay Netwrok  in Peer Group</t>
+    <t>Only One Seed Investor</t>
+  </si>
+  <si>
+    <t>True if there is only one investor in the Seed Phase.</t>
+  </si>
+  <si>
+    <t>one_seed_investor_binary</t>
+  </si>
+  <si>
+    <t>Has Pre-Seed</t>
+  </si>
+  <si>
+    <t>True if the company raised a Pre-Seed round</t>
+  </si>
+  <si>
+    <t>pre_seed_binary</t>
+  </si>
+  <si>
+    <t>Top 10% of Local Network Score in Peer Group</t>
+  </si>
+  <si>
+    <t>Top 10% in Local Investor Network in Peer Group</t>
+  </si>
+  <si>
+    <t>Top 10% in Local Portfolio Compay Netwrok  in Peer Group</t>
+  </si>
+  <si>
+    <t>Low Seed Financing</t>
+  </si>
+  <si>
+    <t>True if the company raised 50,000 EUR or less in the Seed round.</t>
+  </si>
+  <si>
+    <t>low_seed_financing_binary</t>
+  </si>
+  <si>
+    <t>mixed_syndicate</t>
+  </si>
+  <si>
+    <t>True if the company has a primary Co-Investor and primary Lead investor.</t>
+  </si>
+  <si>
+    <t>Mixed Seed Syndicate</t>
+  </si>
+  <si>
+    <t>single_lead_investor</t>
+  </si>
+  <si>
+    <t>True if there is only one investor in the Seed Phase that primary acts as a lead investor.</t>
+  </si>
+  <si>
+    <t>Only One Seed Investor with Lead Capabilities</t>
+  </si>
+  <si>
+    <t>lead_investor_in_seed</t>
+  </si>
+  <si>
+    <t>True if there is a lead investor</t>
+  </si>
+  <si>
+    <t>Existing Lead Investor</t>
   </si>
 </sst>
 </file>
@@ -1585,7 +1639,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -1838,7 +1892,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1872,10 +1926,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1884,31 +1935,28 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1917,28 +1965,19 @@
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1950,9 +1989,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1960,9 +1996,56 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1974,64 +2057,11 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="81">
+  <dxfs count="79">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2090,6 +2120,14 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -2111,23 +2149,6 @@
           <bgColor rgb="FFD0FFFC"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -2178,6 +2199,14 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b/>
       </font>
@@ -2196,6 +2225,7 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -2204,15 +2234,6 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -2369,15 +2390,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFF5FBB2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
+          <bgColor rgb="FFFFB7DA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2413,13 +2426,59 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFCFE0FD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2447,6 +2506,77 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFCDFEC2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2464,7 +2594,174 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -2538,25 +2835,19 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFFFB7DA"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2627,288 +2918,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFCFE0FD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFCDFEC2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFF5FBB2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2940,22 +2950,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BADFB1E4-A7C4-874C-A19A-5FD297EA24A2}" name="Table1" displayName="Table1" ref="B40:F93" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30" tableBorderDxfId="29">
-  <autoFilter ref="B40:F93" xr:uid="{BADFB1E4-A7C4-874C-A19A-5FD297EA24A2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BADFB1E4-A7C4-874C-A19A-5FD297EA24A2}" name="Table1" displayName="Table1" ref="B46:F99" totalsRowShown="0" headerRowDxfId="78" dataDxfId="77" tableBorderDxfId="76">
+  <autoFilter ref="B46:F99" xr:uid="{BADFB1E4-A7C4-874C-A19A-5FD297EA24A2}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E03D4D6E-868B-3040-94BC-AAAFE476C7F6}" name="Investor Features" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{9ADA0B6F-8B1B-0F4F-B7B1-0F3B920D2A58}" name="Variable Type" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{9E85F4DB-43F3-474C-93D9-C3C9A7072DD0}" name="Description" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{BB513F81-27F0-474E-951D-968976A3735F}" name="Python Name" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{9B2453CE-6F80-AA46-8C5B-8306F91B7E95}" name="Included in Regression" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{E03D4D6E-868B-3040-94BC-AAAFE476C7F6}" name="Investor Features" dataDxfId="75"/>
+    <tableColumn id="2" xr3:uid="{9ADA0B6F-8B1B-0F4F-B7B1-0F3B920D2A58}" name="Variable Type" dataDxfId="74"/>
+    <tableColumn id="3" xr3:uid="{9E85F4DB-43F3-474C-93D9-C3C9A7072DD0}" name="Description" dataDxfId="73"/>
+    <tableColumn id="4" xr3:uid="{BB513F81-27F0-474E-951D-968976A3735F}" name="Python Name" dataDxfId="72"/>
+    <tableColumn id="5" xr3:uid="{9B2453CE-6F80-AA46-8C5B-8306F91B7E95}" name="Included in Regression" dataDxfId="71"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C84D18D9-9362-E54C-A5AF-6AFDC1063900}" name="Table11" displayName="Table11" ref="B119:F129" totalsRowShown="0" headerRowDxfId="6" dataDxfId="7" tableBorderDxfId="5">
-  <autoFilter ref="B119:F129" xr:uid="{C84D18D9-9362-E54C-A5AF-6AFDC1063900}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C84D18D9-9362-E54C-A5AF-6AFDC1063900}" name="Table11" displayName="Table11" ref="B125:F135" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" tableBorderDxfId="5">
+  <autoFilter ref="B125:F135" xr:uid="{C84D18D9-9362-E54C-A5AF-6AFDC1063900}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{4E02C00A-6BF8-9745-BACF-E11A643B1EEE}" name="Network Features" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{8D1B5241-A8B2-564E-B8C3-2F886210B738}" name="Variable Type" dataDxfId="3"/>
@@ -2968,114 +2978,114 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{625C1DBF-28AB-ED4A-8087-CF30592A3B8C}" name="Table2" displayName="Table2" ref="B29:F38" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47" tableBorderDxfId="46">
-  <autoFilter ref="B29:F38" xr:uid="{625C1DBF-28AB-ED4A-8087-CF30592A3B8C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{625C1DBF-28AB-ED4A-8087-CF30592A3B8C}" name="Table2" displayName="Table2" ref="B29:F44" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69" tableBorderDxfId="68">
+  <autoFilter ref="B29:F44" xr:uid="{625C1DBF-28AB-ED4A-8087-CF30592A3B8C}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{20474591-85CB-DC49-904A-CF74017E751E}" name="Financing Features" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{643A3B57-58F9-FA49-A71E-8AAAF9F357F4}" name="Variable Type" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{29BAC5AE-0587-8448-A26D-9A751AA6EA5F}" name="Description" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{0DC99CEA-4726-7944-B7A8-9A034F09E13E}" name="Python Name" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{9565D1F9-0041-184B-8554-0A294D69D62C}" name="Included in Regression" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{20474591-85CB-DC49-904A-CF74017E751E}" name="Financing Features" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{643A3B57-58F9-FA49-A71E-8AAAF9F357F4}" name="Variable Type" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{29BAC5AE-0587-8448-A26D-9A751AA6EA5F}" name="Description" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{0DC99CEA-4726-7944-B7A8-9A034F09E13E}" name="Python Name" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{9565D1F9-0041-184B-8554-0A294D69D62C}" name="Included in Regression" dataDxfId="63"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{38B2AC38-DF34-1642-A67A-9068B8D4B9B8}" name="Table3" displayName="Table3" ref="B5:F27" totalsRowShown="0" headerRowDxfId="77" dataDxfId="78" tableBorderDxfId="76">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{38B2AC38-DF34-1642-A67A-9068B8D4B9B8}" name="Table3" displayName="Table3" ref="B5:F27" totalsRowShown="0" headerRowDxfId="62" dataDxfId="61" tableBorderDxfId="60">
   <autoFilter ref="B5:F27" xr:uid="{38B2AC38-DF34-1642-A67A-9068B8D4B9B8}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{91BCE79A-2728-BD48-B1E2-E0BE3627F475}" name="Company Features" dataDxfId="75"/>
-    <tableColumn id="2" xr3:uid="{B0E758A9-1977-FF47-9F51-CB5D5D966A07}" name="Variable Type" dataDxfId="74"/>
-    <tableColumn id="3" xr3:uid="{3CC6868F-603E-6F4A-963E-C8274B262C23}" name="Description" dataDxfId="73"/>
-    <tableColumn id="4" xr3:uid="{585F4B8D-EA90-F54D-9E4D-5B254A2FB5B4}" name="Python Name" dataDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{97E9DD2D-1349-E84D-8FC1-1E1CA70302C2}" name="Included in Regression" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{91BCE79A-2728-BD48-B1E2-E0BE3627F475}" name="Company Features" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{B0E758A9-1977-FF47-9F51-CB5D5D966A07}" name="Variable Type" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{3CC6868F-603E-6F4A-963E-C8274B262C23}" name="Description" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{585F4B8D-EA90-F54D-9E4D-5B254A2FB5B4}" name="Python Name" dataDxfId="56"/>
+    <tableColumn id="5" xr3:uid="{97E9DD2D-1349-E84D-8FC1-1E1CA70302C2}" name="Included in Regression" dataDxfId="55"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C288A2F5-FAF5-CC45-A73C-1CA5284AEB54}" name="Table4" displayName="Table4" ref="B104:F117" totalsRowShown="0" headerRowDxfId="71" dataDxfId="72" tableBorderDxfId="70">
-  <autoFilter ref="B104:F117" xr:uid="{C288A2F5-FAF5-CC45-A73C-1CA5284AEB54}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C288A2F5-FAF5-CC45-A73C-1CA5284AEB54}" name="Table4" displayName="Table4" ref="B110:F123" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53" tableBorderDxfId="52">
+  <autoFilter ref="B110:F123" xr:uid="{C288A2F5-FAF5-CC45-A73C-1CA5284AEB54}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{AE66DA98-FE07-294A-AA12-55D5C6B9D761}" name="Distance Features (in 1000 km)" dataDxfId="69"/>
-    <tableColumn id="2" xr3:uid="{6C5E990C-FE6B-604E-8D81-B062F12ADAA9}" name="Variable Type" dataDxfId="68"/>
-    <tableColumn id="3" xr3:uid="{6F12EF53-64A3-6A48-B3C6-A4A474157490}" name="Description" dataDxfId="67"/>
-    <tableColumn id="4" xr3:uid="{3294DA05-5CD6-B645-84CF-1674E36445AC}" name="Python Name" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{4FDF6985-4069-6F4A-9349-D895903553A5}" name="Included in Regression" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{AE66DA98-FE07-294A-AA12-55D5C6B9D761}" name="Distance Features (in 1000 km)" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{6C5E990C-FE6B-604E-8D81-B062F12ADAA9}" name="Variable Type" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{6F12EF53-64A3-6A48-B3C6-A4A474157490}" name="Description" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{3294DA05-5CD6-B645-84CF-1674E36445AC}" name="Python Name" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{4FDF6985-4069-6F4A-9349-D895903553A5}" name="Included in Regression" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F0E04D94-3B0E-964F-A888-9EDE8C1AD5F6}" name="Table5" displayName="Table5" ref="B95:F102" totalsRowShown="0" headerRowDxfId="65" dataDxfId="66" tableBorderDxfId="64">
-  <autoFilter ref="B95:F102" xr:uid="{F0E04D94-3B0E-964F-A888-9EDE8C1AD5F6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F0E04D94-3B0E-964F-A888-9EDE8C1AD5F6}" name="Table5" displayName="Table5" ref="B101:F108" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45" tableBorderDxfId="44">
+  <autoFilter ref="B101:F108" xr:uid="{F0E04D94-3B0E-964F-A888-9EDE8C1AD5F6}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{4BA769C3-20C7-694B-B63D-500312785390}" name="Ecosystem Features" dataDxfId="63"/>
-    <tableColumn id="2" xr3:uid="{C7CBBF4E-E32C-5349-BA5F-ACCF31548549}" name="Variable Type" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{0E50E825-3168-CD4E-8A02-1102911C878A}" name="Description" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{D91E7EE0-E148-C345-B2BC-7CBDAD7BBADB}" name="Python Name" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{554C6F2A-7F7F-B044-9CE9-308E8756EA24}" name="Included in Regression" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{4BA769C3-20C7-694B-B63D-500312785390}" name="Ecosystem Features" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{C7CBBF4E-E32C-5349-BA5F-ACCF31548549}" name="Variable Type" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{0E50E825-3168-CD4E-8A02-1102911C878A}" name="Description" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{D91E7EE0-E148-C345-B2BC-7CBDAD7BBADB}" name="Python Name" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{554C6F2A-7F7F-B044-9CE9-308E8756EA24}" name="Included in Regression" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2E3D645F-AC26-DF46-BD5D-EBAB2942DB82}" name="Table6" displayName="Table6" ref="B135:F143" totalsRowShown="0" headerRowDxfId="55" dataDxfId="56" tableBorderDxfId="60">
-  <autoFilter ref="B135:F143" xr:uid="{2E3D645F-AC26-DF46-BD5D-EBAB2942DB82}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2E3D645F-AC26-DF46-BD5D-EBAB2942DB82}" name="Table6" displayName="Table6" ref="B141:F149" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37" tableBorderDxfId="36">
+  <autoFilter ref="B141:F149" xr:uid="{2E3D645F-AC26-DF46-BD5D-EBAB2942DB82}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B6190453-A34F-B84E-8F2A-A1D958E4DB06}" name="Outcome Features" dataDxfId="59"/>
-    <tableColumn id="2" xr3:uid="{634432B5-6BC9-564F-B291-C6D01B8BD2DB}" name="Variable Type" dataDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{C237EC30-178A-9142-A609-E72AA6B75365}" name="Description" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{AD7FDDDF-AD6A-0E42-B0D5-6147F92F3B1C}" name="Python Name" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{683EFBFB-1FC6-BE47-92AE-D3D45DC2FFF9}" name="Included in Regression" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{B6190453-A34F-B84E-8F2A-A1D958E4DB06}" name="Outcome Features" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{634432B5-6BC9-564F-B291-C6D01B8BD2DB}" name="Variable Type" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{C237EC30-178A-9142-A609-E72AA6B75365}" name="Description" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{AD7FDDDF-AD6A-0E42-B0D5-6147F92F3B1C}" name="Python Name" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{683EFBFB-1FC6-BE47-92AE-D3D45DC2FFF9}" name="Included in Regression" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{44C40AD8-7805-764B-8B4F-9295490166FE}" name="Table48" displayName="Table48" ref="B131:F133" totalsRowShown="0" headerRowDxfId="49" dataDxfId="54" tableBorderDxfId="53">
-  <autoFilter ref="B131:F133" xr:uid="{44C40AD8-7805-764B-8B4F-9295490166FE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{44C40AD8-7805-764B-8B4F-9295490166FE}" name="Table48" displayName="Table48" ref="B137:F139" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29" tableBorderDxfId="28">
+  <autoFilter ref="B137:F139" xr:uid="{44C40AD8-7805-764B-8B4F-9295490166FE}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9969B5D0-6C94-A14A-9C38-C48420232A9C}" name="Economical Features" dataDxfId="52"/>
-    <tableColumn id="2" xr3:uid="{02D99B72-6F40-A04C-9824-719B2293FF60}" name="Variable Type" dataDxfId="51"/>
-    <tableColumn id="3" xr3:uid="{ED9501AA-C011-0B4E-8C8B-EF6E06D6B929}" name="Description" dataDxfId="50"/>
-    <tableColumn id="4" xr3:uid="{31AA41E3-0659-F045-A067-096A82B81B9A}" name="Python Name" dataDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{9F2FC2F9-C4B3-BC4D-889C-B89393759E93}" name="Included in Regression" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{9969B5D0-6C94-A14A-9C38-C48420232A9C}" name="Economical Features" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{02D99B72-6F40-A04C-9824-719B2293FF60}" name="Variable Type" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{ED9501AA-C011-0B4E-8C8B-EF6E06D6B929}" name="Description" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{31AA41E3-0659-F045-A067-096A82B81B9A}" name="Python Name" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{9F2FC2F9-C4B3-BC4D-889C-B89393759E93}" name="Included in Regression" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{6DEEB368-0C4F-284A-B8BF-76292D1E564D}" name="Table310" displayName="Table310" ref="B146:F152" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
-  <autoFilter ref="B146:F152" xr:uid="{6DEEB368-0C4F-284A-B8BF-76292D1E564D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{6DEEB368-0C4F-284A-B8BF-76292D1E564D}" name="Table310" displayName="Table310" ref="B152:F158" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21" tableBorderDxfId="20">
+  <autoFilter ref="B152:F158" xr:uid="{6DEEB368-0C4F-284A-B8BF-76292D1E564D}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{456BE63F-58FC-C941-82F8-F6ABD1A7C06C}" name="Features" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{F8D792A3-C29A-9F4B-843D-23EE6D488A01}" name="Variable Type" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{0512FD64-43A9-A94F-81EF-D503F7970A81}" name="Description" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{456BE63F-58FC-C941-82F8-F6ABD1A7C06C}" name="Features" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{F8D792A3-C29A-9F4B-843D-23EE6D488A01}" name="Variable Type" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{0512FD64-43A9-A94F-81EF-D503F7970A81}" name="Description" dataDxfId="17"/>
     <tableColumn id="4" xr3:uid="{0CAA4F0C-80CE-C946-A1B7-7B769A31B90F}" name="Paper" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{78AA5131-E9A3-4944-8C53-340972E86CF5}" name="Possible?" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{78AA5131-E9A3-4944-8C53-340972E86CF5}" name="Possible?" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{11B60FFA-95BB-1845-B1CB-5FE85587B5A7}" name="Table10" displayName="Table10" ref="H5:K29" totalsRowShown="0" headerRowDxfId="14" dataDxfId="15" tableBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{11B60FFA-95BB-1845-B1CB-5FE85587B5A7}" name="Table10" displayName="Table10" ref="H5:K29" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" tableBorderDxfId="12">
   <autoFilter ref="H5:K29" xr:uid="{11B60FFA-95BB-1845-B1CB-5FE85587B5A7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H6:K29">
     <sortCondition ref="J5:J29"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0B294427-D79A-F944-8F2E-083A1E3E7736}" name="Name" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{8BE80BC7-50DB-6241-AA19-9087A9996122}" name="Description" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{769FA72C-A617-3F45-88FD-A0F271E97179}" name="Focus" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{5CDBB43C-935F-834A-B556-90DBDCAE3C91}" name="Useful" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{0B294427-D79A-F944-8F2E-083A1E3E7736}" name="Name" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{8BE80BC7-50DB-6241-AA19-9087A9996122}" name="Description" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{769FA72C-A617-3F45-88FD-A0F271E97179}" name="Focus" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{5CDBB43C-935F-834A-B556-90DBDCAE3C91}" name="Useful" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3398,7 +3408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D84EA5FA-74C6-FF45-8301-AF21701891F8}">
-  <dimension ref="B2:K168"/>
+  <dimension ref="B2:K152"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -3406,7 +3416,7 @@
     <col min="3" max="3" width="14.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="74" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="35.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="24.1640625" style="45" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.1640625" style="37" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.1640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="27.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="38.83203125" style="1" customWidth="1"/>
@@ -3416,2429 +3426,2274 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="43" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="4" spans="2:11" ht="22" x14ac:dyDescent="0.3">
-      <c r="B4" s="49" t="s">
+      <c r="B4" s="58" t="s">
         <v>140</v>
       </c>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="51"/>
-      <c r="H4" s="46" t="s">
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="60"/>
+      <c r="H4" s="61" t="s">
         <v>365</v>
       </c>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="48"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="63"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="E5" s="52" t="s">
+      <c r="E5" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="F5" s="59" t="s">
+      <c r="F5" s="45" t="s">
         <v>248</v>
       </c>
-      <c r="H5" s="55" t="s">
+      <c r="H5" s="41" t="s">
         <v>366</v>
       </c>
-      <c r="I5" s="70" t="s">
+      <c r="I5" s="54" t="s">
         <v>113</v>
       </c>
-      <c r="J5" s="55" t="s">
+      <c r="J5" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="K5" s="55" t="s">
+      <c r="K5" s="41" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="F6" s="60"/>
-      <c r="H6" s="44" t="s">
+      <c r="H6" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="I6" s="44" t="s">
+      <c r="I6" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="J6" s="44" t="s">
+      <c r="J6" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="K6" s="44"/>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E7" s="44" t="s">
+      <c r="E7" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="F7" s="60"/>
-      <c r="H7" s="44" t="s">
+      <c r="H7" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="I7" s="44" t="s">
+      <c r="I7" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="J7" s="44" t="s">
+      <c r="J7" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="K7" s="44"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D8" s="44" t="s">
+      <c r="D8" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="E8" s="44" t="s">
+      <c r="E8" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="F8" s="60"/>
-      <c r="H8" s="44" t="s">
+      <c r="H8" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="I8" s="44" t="s">
+      <c r="I8" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="J8" s="44" t="s">
+      <c r="J8" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="K8" s="44"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D9" s="44" t="s">
+      <c r="D9" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="60"/>
-      <c r="H9" s="44" t="s">
+      <c r="H9" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="I9" s="44" t="s">
+      <c r="I9" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="J9" s="44" t="s">
+      <c r="J9" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="K9" s="44"/>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="D10" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="F10" s="60"/>
-      <c r="H10" s="44" t="s">
+      <c r="H10" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="I10" s="44" t="s">
+      <c r="I10" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="J10" s="44" t="s">
+      <c r="J10" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="K10" s="44"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B11" s="44" t="s">
+      <c r="B11" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C11" s="44" t="s">
+      <c r="C11" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D11" s="44" t="s">
+      <c r="D11" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="F11" s="60"/>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="I11" s="44" t="s">
+      <c r="I11" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="J11" s="44" t="s">
+      <c r="J11" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="K11" s="44"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="44" t="s">
+      <c r="C12" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="F12" s="60"/>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="I12" s="44" t="s">
+      <c r="I12" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="J12" s="44" t="s">
+      <c r="J12" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="K12" s="44"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="44" t="s">
+      <c r="C13" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="44" t="s">
+      <c r="D13" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E13" s="44" t="s">
+      <c r="E13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="60"/>
-      <c r="H13" s="44" t="s">
+      <c r="H13" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="I13" s="44" t="s">
+      <c r="I13" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="J13" s="44" t="s">
+      <c r="J13" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="K13" s="44"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D14" s="44" t="s">
+      <c r="D14" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E14" s="44" t="s">
+      <c r="E14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="60"/>
-      <c r="H14" s="44" t="s">
+      <c r="H14" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="I14" s="44" t="s">
+      <c r="I14" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="J14" s="44" t="s">
+      <c r="J14" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="K14" s="44"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="44" t="s">
+      <c r="C15" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D15" s="44" t="s">
+      <c r="D15" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E15" s="44" t="s">
+      <c r="E15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="60"/>
-      <c r="H15" s="44" t="s">
+      <c r="H15" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="I15" s="44" t="s">
+      <c r="I15" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="J15" s="44" t="s">
+      <c r="J15" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="K15" s="44"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B16" s="44" t="s">
+      <c r="B16" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C16" s="44" t="s">
+      <c r="C16" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D16" s="44" t="s">
+      <c r="D16" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E16" s="44" t="s">
+      <c r="E16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="60"/>
-      <c r="H16" s="44" t="s">
+      <c r="H16" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="I16" s="44" t="s">
+      <c r="I16" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="J16" s="44" t="s">
+      <c r="J16" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="K16" s="44"/>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B17" s="44" t="s">
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B17" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C17" s="44" t="s">
+      <c r="C17" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D17" s="44" t="s">
+      <c r="D17" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E17" s="44" t="s">
+      <c r="E17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="60"/>
-      <c r="H17" s="44" t="s">
+      <c r="H17" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="I17" s="44" t="s">
+      <c r="I17" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="J17" s="44" t="s">
+      <c r="J17" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="K17" s="44"/>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B18" s="44" t="s">
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B18" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C18" s="44" t="s">
+      <c r="C18" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="44" t="s">
+      <c r="D18" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="E18" s="44" t="s">
+      <c r="E18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F18" s="60"/>
-      <c r="H18" s="44" t="s">
+      <c r="H18" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="I18" s="44" t="s">
+      <c r="I18" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="J18" s="44" t="s">
+      <c r="J18" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="K18" s="44"/>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B19" s="44" t="s">
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B19" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C19" s="44" t="s">
+      <c r="C19" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D19" s="44" t="s">
+      <c r="D19" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E19" s="44" t="s">
+      <c r="E19" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F19" s="60"/>
-      <c r="H19" s="44" t="s">
+      <c r="H19" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="I19" s="44" t="s">
+      <c r="I19" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="J19" s="44" t="s">
+      <c r="J19" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="K19" s="44"/>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B20" s="44" t="s">
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B20" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C20" s="44" t="s">
+      <c r="C20" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D20" s="44" t="s">
+      <c r="D20" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="E20" s="44" t="s">
+      <c r="E20" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F20" s="60"/>
-      <c r="H20" s="44" t="s">
+      <c r="H20" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="I20" s="44" t="s">
+      <c r="I20" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="J20" s="44" t="s">
+      <c r="J20" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="K20" s="44"/>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B21" s="44" t="s">
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B21" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C21" s="44" t="s">
+      <c r="C21" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D21" s="44" t="s">
+      <c r="D21" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="E21" s="44" t="s">
+      <c r="E21" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F21" s="60"/>
-      <c r="H21" s="44" t="s">
+      <c r="H21" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="I21" s="44" t="s">
+      <c r="I21" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="J21" s="44" t="s">
+      <c r="J21" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="K21" s="44"/>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B22" s="44" t="s">
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B22" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C22" s="44" t="s">
+      <c r="C22" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D22" s="44" t="s">
+      <c r="D22" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E22" s="44" t="s">
+      <c r="E22" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F22" s="60"/>
-      <c r="H22" s="44" t="s">
+      <c r="H22" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="I22" s="44" t="s">
+      <c r="I22" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="J22" s="44" t="s">
+      <c r="J22" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="K22" s="44"/>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B23" s="44" t="s">
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B23" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C23" s="44" t="s">
+      <c r="C23" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D23" s="44" t="s">
+      <c r="D23" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="E23" s="44" t="s">
+      <c r="E23" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F23" s="60"/>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="I23" s="44" t="s">
+      <c r="I23" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="J23" s="44" t="s">
+      <c r="J23" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="K23" s="44"/>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B24" s="44" t="s">
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B24" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C24" s="44" t="s">
+      <c r="C24" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D24" s="44" t="s">
+      <c r="D24" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="E24" s="44" t="s">
+      <c r="E24" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F24" s="60"/>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="I24" s="44" t="s">
+      <c r="I24" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="J24" s="44" t="s">
+      <c r="J24" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="K24" s="44"/>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B25" s="44" t="s">
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B25" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C25" s="44" t="s">
+      <c r="C25" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D25" s="44" t="s">
+      <c r="D25" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E25" s="44" t="s">
+      <c r="E25" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F25" s="60"/>
-      <c r="H25" s="44" t="s">
+      <c r="H25" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="I25" s="44" t="s">
+      <c r="I25" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="J25" s="44" t="s">
+      <c r="J25" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="K25" s="44"/>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B26" s="44" t="s">
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B26" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C26" s="44" t="s">
+      <c r="C26" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D26" s="44" t="s">
+      <c r="D26" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="E26" s="44" t="s">
+      <c r="E26" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F26" s="60"/>
-      <c r="H26" s="44" t="s">
+      <c r="H26" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="I26" s="44" t="s">
+      <c r="I26" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="J26" s="44" t="s">
+      <c r="J26" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="K26" s="44"/>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B27" s="44" t="s">
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B27" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C27" s="44" t="s">
+      <c r="C27" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D27" s="44" t="s">
+      <c r="D27" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="E27" s="44" t="s">
+      <c r="E27" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F27" s="60"/>
-      <c r="H27" s="44" t="s">
+      <c r="H27" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="I27" s="44" t="s">
+      <c r="I27" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="J27" s="44" t="s">
+      <c r="J27" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="K27" s="44"/>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B28" s="44"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="60"/>
-      <c r="H28" s="44" t="s">
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H28" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="I28" s="44" t="s">
+      <c r="I28" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="J28" s="44" t="s">
+      <c r="J28" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="K28" s="44"/>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B29" s="58" t="s">
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B29" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="C29" s="58" t="s">
+      <c r="C29" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="D29" s="58" t="s">
+      <c r="D29" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="E29" s="58" t="s">
+      <c r="E29" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="F29" s="61" t="s">
+      <c r="F29" s="46" t="s">
         <v>248</v>
       </c>
-      <c r="H29" s="44" t="s">
+      <c r="H29" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="I29" s="44" t="s">
+      <c r="I29" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="J29" s="44" t="s">
+      <c r="J29" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="K29" s="44"/>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B30" s="44" t="s">
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B30" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="C30" s="44" t="s">
+      <c r="C30" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D30" s="44" t="s">
+      <c r="D30" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="E30" s="44" t="s">
+      <c r="E30" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F30" s="60"/>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B31" s="44" t="s">
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B31" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C31" s="44" t="s">
+      <c r="C31" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D31" s="44" t="s">
+      <c r="D31" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="E31" s="44" t="s">
+      <c r="E31" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F31" s="60"/>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B32" s="44" t="s">
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B32" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C32" s="44" t="s">
+      <c r="C32" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D32" s="44" t="s">
+      <c r="D32" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="E32" s="44" t="s">
+      <c r="E32" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F32" s="60"/>
       <c r="H32" s="2" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="44" t="s">
+      <c r="B33" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B34" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B35" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B36" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B37" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C33" s="44" t="s">
+      <c r="C37" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D33" s="44" t="s">
+      <c r="D37" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="E33" s="44" t="s">
+      <c r="E37" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="F33" s="60"/>
-      <c r="H33" s="1" t="s">
+      <c r="H37" s="1" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B34" s="44" t="s">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B38" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B39" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C34" s="44" t="s">
+      <c r="C39" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D34" s="44" t="s">
+      <c r="D39" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="E34" s="44" t="s">
+      <c r="E39" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F34" s="60"/>
-      <c r="H34" s="1" t="s">
+      <c r="H39" s="1" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B35" s="44" t="s">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B40" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B41" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C35" s="44" t="s">
+      <c r="C41" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D35" s="44" t="s">
+      <c r="D41" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E35" s="44" t="s">
+      <c r="E41" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F35" s="60"/>
-      <c r="H35" s="1" t="s">
+      <c r="H41" s="1" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B36" s="44" t="s">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B42" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C36" s="44" t="s">
+      <c r="C42" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D36" s="44" t="s">
+      <c r="D42" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="E36" s="44" t="s">
+      <c r="E42" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="F36" s="60"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B37" s="44" t="s">
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B43" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C37" s="44" t="s">
+      <c r="C43" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D37" s="44" t="s">
+      <c r="D43" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="E37" s="44" t="s">
+      <c r="E43" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="F37" s="60"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B38" s="44" t="s">
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="C38" s="44" t="s">
+      <c r="C44" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D38" s="44" t="s">
+      <c r="D44" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="E38" s="44" t="s">
+      <c r="E44" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="F38" s="60"/>
-      <c r="H38" s="1" t="s">
+      <c r="H44" s="1" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B40" s="43" t="s">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B46" s="36" t="s">
         <v>110</v>
       </c>
-      <c r="C40" s="43" t="s">
+      <c r="C46" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="D40" s="43" t="s">
+      <c r="D46" s="36" t="s">
         <v>113</v>
       </c>
-      <c r="E40" s="42" t="s">
+      <c r="E46" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="F40" s="62" t="s">
+      <c r="F46" s="47" t="s">
         <v>248</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H46" s="1" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B41" s="67" t="s">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B47" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="C41" s="67" t="s">
+      <c r="C47" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="D41" s="67" t="s">
+      <c r="D47" s="43" t="s">
         <v>232</v>
       </c>
-      <c r="E41" s="57" t="s">
+      <c r="E47" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="F41" s="68"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="44" t="s">
+      <c r="F47" s="52"/>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B48" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C42" s="44" t="s">
+      <c r="C48" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D42" s="44" t="s">
+      <c r="D48" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H48" s="1" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B43" s="44" t="s">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B49" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C43" s="44" t="s">
+      <c r="C49" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D43" s="44" t="s">
+      <c r="D49" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E49" s="1" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B44" s="44" t="s">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B50" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C44" s="44" t="s">
+      <c r="C50" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E50" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H50" s="1" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B45" s="44" t="s">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B51" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="C45" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="D45" s="44" t="s">
-        <v>243</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="C46" s="44" t="s">
-        <v>124</v>
-      </c>
-      <c r="D46" s="44" t="s">
-        <v>244</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B47" s="44" t="s">
-        <v>119</v>
-      </c>
-      <c r="C47" s="44" t="s">
-        <v>124</v>
-      </c>
-      <c r="D47" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B48" s="44" t="s">
-        <v>120</v>
-      </c>
-      <c r="C48" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="D48" s="44" t="s">
-        <v>246</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B49" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="C49" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="D49" s="44" t="s">
-        <v>247</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B50" s="44" t="s">
-        <v>122</v>
-      </c>
-      <c r="C50" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="D50" s="44" t="s">
-        <v>249</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B51" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D51" s="44" t="s">
-        <v>250</v>
+      <c r="D51" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D52" s="44" t="s">
-        <v>251</v>
+        <v>124</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.2">
+        <v>309</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D53" s="44" t="s">
-        <v>252</v>
+        <v>124</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D54" s="69" t="s">
-        <v>253</v>
+      <c r="D54" s="1" t="s">
+        <v>246</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D55" s="69" t="s">
-        <v>254</v>
+      <c r="D55" s="1" t="s">
+        <v>247</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D56" s="69" t="s">
-        <v>255</v>
+      <c r="D56" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D57" s="69" t="s">
-        <v>256</v>
+      <c r="D57" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.2">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D58" s="69" t="s">
-        <v>257</v>
+      <c r="D58" s="1" t="s">
+        <v>251</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D59" s="69" t="s">
-        <v>258</v>
+      <c r="D59" s="1" t="s">
+        <v>252</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>259</v>
+        <v>123</v>
+      </c>
+      <c r="D60" s="53" t="s">
+        <v>253</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>260</v>
+        <v>123</v>
+      </c>
+      <c r="D61" s="53" t="s">
+        <v>254</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B62" s="1" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D62" s="44" t="s">
-        <v>235</v>
+      <c r="D62" s="53" t="s">
+        <v>255</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B63" s="1" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D63" s="44" t="s">
-        <v>236</v>
+      <c r="D63" s="53" t="s">
+        <v>256</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
-        <v>237</v>
+        <v>133</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>238</v>
+      <c r="D64" s="53" t="s">
+        <v>257</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>74</v>
+        <v>318</v>
       </c>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B65" s="1" t="s">
-        <v>456</v>
+        <v>134</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D65" s="44" t="s">
-        <v>233</v>
+      <c r="D65" s="53" t="s">
+        <v>258</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>444</v>
+        <v>319</v>
       </c>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B66" s="1" t="s">
-        <v>462</v>
+        <v>153</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D66" s="44" t="s">
-        <v>234</v>
+        <v>124</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>259</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>445</v>
+        <v>320</v>
       </c>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B67" s="1" t="s">
-        <v>457</v>
+        <v>154</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D67" s="44" t="s">
-        <v>468</v>
+        <v>124</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>260</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>446</v>
+        <v>321</v>
       </c>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B68" s="1" t="s">
-        <v>463</v>
+        <v>155</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D68" s="44" t="s">
-        <v>469</v>
+      <c r="D68" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>447</v>
+        <v>32</v>
       </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B69" s="71" t="s">
-        <v>458</v>
+      <c r="B69" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D69" s="44" t="s">
-        <v>471</v>
+      <c r="D69" s="1" t="s">
+        <v>236</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>448</v>
+        <v>322</v>
       </c>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B70" s="71" t="s">
-        <v>464</v>
+      <c r="B70" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D70" s="44" t="s">
-        <v>472</v>
+      <c r="D70" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>449</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B71" s="71" t="s">
-        <v>459</v>
+      <c r="B71" s="1" t="s">
+        <v>456</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D71" s="44" t="s">
-        <v>473</v>
+      <c r="D71" s="1" t="s">
+        <v>233</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B72" s="71" t="s">
-        <v>465</v>
+      <c r="B72" s="1" t="s">
+        <v>462</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D72" s="44" t="s">
-        <v>474</v>
+      <c r="D72" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B73" s="71" t="s">
-        <v>460</v>
+      <c r="B73" s="1" t="s">
+        <v>457</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D73" s="44" t="s">
-        <v>475</v>
+      <c r="D73" s="1" t="s">
+        <v>468</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B74" s="71" t="s">
-        <v>466</v>
+      <c r="B74" s="1" t="s">
+        <v>463</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D74" s="44" t="s">
-        <v>476</v>
+      <c r="D74" s="1" t="s">
+        <v>469</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B75" s="71" t="s">
-        <v>461</v>
+      <c r="B75" s="55" t="s">
+        <v>458</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D75" s="44" t="s">
-        <v>477</v>
+      <c r="D75" s="1" t="s">
+        <v>471</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B76" s="71" t="s">
-        <v>467</v>
+      <c r="B76" s="55" t="s">
+        <v>464</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D76" s="44" t="s">
-        <v>470</v>
+      <c r="D76" s="1" t="s">
+        <v>472</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B77" s="1" t="s">
-        <v>157</v>
+      <c r="B77" s="55" t="s">
+        <v>459</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>239</v>
+        <v>473</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>323</v>
+        <v>450</v>
       </c>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B78" s="1" t="s">
-        <v>158</v>
+      <c r="B78" s="55" t="s">
+        <v>465</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>240</v>
+        <v>474</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>324</v>
+        <v>451</v>
       </c>
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B79" s="1" t="s">
-        <v>159</v>
+      <c r="B79" s="55" t="s">
+        <v>460</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>241</v>
+        <v>475</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>33</v>
+        <v>452</v>
       </c>
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B80" s="1" t="s">
-        <v>160</v>
+      <c r="B80" s="55" t="s">
+        <v>466</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>261</v>
+        <v>476</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>325</v>
+        <v>453</v>
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B81" s="1" t="s">
-        <v>360</v>
+      <c r="B81" s="55" t="s">
+        <v>461</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>361</v>
+        <v>477</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>362</v>
+        <v>454</v>
       </c>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B82" s="1" t="s">
-        <v>179</v>
+      <c r="B82" s="55" t="s">
+        <v>467</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>262</v>
+        <v>470</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>64</v>
+        <v>455</v>
       </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B83" s="1" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="C83" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B84" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B85" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D83" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B84" s="57" t="s">
-        <v>186</v>
-      </c>
-      <c r="C84" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="D84" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="E84" s="57"/>
-      <c r="F84" s="57"/>
-    </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B85" s="57" t="s">
-        <v>187</v>
-      </c>
-      <c r="C85" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="D85" s="57" t="s">
-        <v>271</v>
-      </c>
-      <c r="E85" s="57"/>
-      <c r="F85" s="57"/>
+      <c r="D85" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B86" s="1" t="s">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>193</v>
+        <v>325</v>
       </c>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B87" s="1" t="s">
-        <v>196</v>
+        <v>360</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>264</v>
+        <v>361</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>195</v>
+        <v>362</v>
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B88" s="1" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>197</v>
+        <v>64</v>
       </c>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B89" s="1" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>199</v>
+        <v>326</v>
       </c>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B90" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C90" s="1" t="s">
+      <c r="B90" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="C90" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="D90" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="D90" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="E90" s="43"/>
+      <c r="F90" s="43"/>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B91" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C91" s="1" t="s">
+      <c r="B91" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="C91" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>91</v>
-      </c>
+      <c r="D91" s="43" t="s">
+        <v>271</v>
+      </c>
+      <c r="E91" s="43"/>
+      <c r="F91" s="43"/>
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B92" s="1" t="s">
-        <v>327</v>
+        <v>194</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>329</v>
+        <v>265</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>331</v>
+        <v>193</v>
       </c>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B93" s="1" t="s">
-        <v>328</v>
+        <v>196</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>330</v>
+        <v>264</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>332</v>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="94" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B94" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B95" s="54" t="s">
-        <v>161</v>
-      </c>
-      <c r="C95" s="54" t="s">
-        <v>112</v>
-      </c>
-      <c r="D95" s="54" t="s">
-        <v>113</v>
-      </c>
-      <c r="E95" s="54" t="s">
-        <v>129</v>
-      </c>
-      <c r="F95" s="63" t="s">
-        <v>248</v>
+      <c r="B95" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B96" s="44" t="s">
-        <v>164</v>
-      </c>
-      <c r="C96" s="44" t="s">
-        <v>124</v>
-      </c>
-      <c r="D96" s="44" t="s">
-        <v>272</v>
-      </c>
-      <c r="E96" s="44" t="s">
-        <v>333</v>
+      <c r="B96" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B97" s="1" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D97" s="44" t="s">
-        <v>273</v>
-      </c>
-      <c r="E97" s="44" t="s">
-        <v>334</v>
-      </c>
-      <c r="F97" s="60"/>
+        <v>123</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B98" s="1" t="s">
-        <v>182</v>
+        <v>327</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>274</v>
+        <v>329</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="99" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B99" s="1" t="s">
-        <v>183</v>
+        <v>328</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>358</v>
+        <v>330</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B100" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="101" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B101" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>338</v>
+      <c r="B101" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="C101" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="D101" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="E101" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="F101" s="48" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B102" s="1" t="s">
-        <v>479</v>
+        <v>164</v>
       </c>
       <c r="C102" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B103" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D102" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>481</v>
+      <c r="D103" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B104" s="53" t="s">
-        <v>359</v>
-      </c>
-      <c r="C104" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="D104" s="53" t="s">
-        <v>113</v>
-      </c>
-      <c r="E104" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="F104" s="64" t="s">
-        <v>248</v>
+      <c r="B104" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B105" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="C105" s="44" t="s">
+      <c r="B105" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D105" s="44" t="s">
-        <v>275</v>
-      </c>
-      <c r="E105" s="44" t="s">
-        <v>339</v>
-      </c>
-      <c r="F105" s="60"/>
+      <c r="D105" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="106" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B106" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="C106" s="44" t="s">
+      <c r="B106" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D106" s="44" t="s">
-        <v>276</v>
-      </c>
-      <c r="E106" s="44" t="s">
-        <v>28</v>
-      </c>
-      <c r="F106" s="60"/>
+      <c r="D106" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="107" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B107" s="44" t="s">
-        <v>168</v>
-      </c>
-      <c r="C107" s="44" t="s">
+      <c r="B107" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D107" s="44" t="s">
-        <v>279</v>
-      </c>
-      <c r="E107" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="F107" s="60"/>
+      <c r="D107" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="108" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B108" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C108" s="44" t="s">
+        <v>479</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D108" s="44" t="s">
-        <v>280</v>
+      <c r="D108" s="1" t="s">
+        <v>480</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="F108" s="60"/>
-    </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B109" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C109" s="44" t="s">
-        <v>139</v>
-      </c>
-      <c r="D109" s="44" t="s">
-        <v>281</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="F109" s="60"/>
+        <v>481</v>
+      </c>
     </row>
     <row r="110" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B110" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C110" s="44" t="s">
-        <v>139</v>
-      </c>
-      <c r="D110" s="44" t="s">
-        <v>282</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="F110" s="60"/>
+      <c r="B110" s="39" t="s">
+        <v>359</v>
+      </c>
+      <c r="C110" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D110" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="E110" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="F110" s="49" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="111" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B111" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C111" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D111" s="44" t="s">
-        <v>283</v>
+      <c r="D111" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="F111" s="60"/>
+        <v>339</v>
+      </c>
     </row>
     <row r="112" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B112" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C112" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D112" s="44" t="s">
-        <v>284</v>
+      <c r="D112" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="F112" s="60"/>
+        <v>28</v>
+      </c>
     </row>
     <row r="113" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B113" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C113" s="44" t="s">
+        <v>168</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D113" s="44" t="s">
-        <v>285</v>
+      <c r="D113" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="F113" s="60"/>
+        <v>78</v>
+      </c>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B114" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C114" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="C114" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D114" s="44" t="s">
-        <v>286</v>
+      <c r="D114" s="1" t="s">
+        <v>280</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="F114" s="60"/>
+        <v>340</v>
+      </c>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B115" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>139</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="F115" s="60"/>
+        <v>341</v>
+      </c>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B116" s="1" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>139</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="F116" s="60"/>
+        <v>343</v>
+      </c>
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B117" s="1" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>139</v>
       </c>
       <c r="D117" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="118" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B118" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="119" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B119" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="120" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B120" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="121" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B121" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B122" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="123" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B123" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="E123" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="F117" s="60"/>
-    </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F118" s="60"/>
-    </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B119" s="72" t="s">
+    </row>
+    <row r="125" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B125" s="56" t="s">
         <v>188</v>
       </c>
-      <c r="C119" s="72" t="s">
+      <c r="C125" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="D119" s="72" t="s">
+      <c r="D125" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="E119" s="72" t="s">
+      <c r="E125" s="56" t="s">
         <v>129</v>
       </c>
-      <c r="F119" s="73" t="s">
+      <c r="F125" s="57" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B120" s="44" t="s">
+    <row r="126" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B126" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="C120" s="44" t="s">
+      <c r="C126" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D120" s="44" t="s">
+      <c r="D126" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="E120" s="44" t="s">
+      <c r="E126" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="F120" s="60"/>
-    </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B121" s="44" t="s">
+    </row>
+    <row r="127" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B127" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="C121" s="44" t="s">
+      <c r="C127" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D121" s="44" t="s">
+      <c r="D127" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="E121" s="44" t="s">
+      <c r="E127" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="F121" s="60"/>
-    </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B122" s="44" t="s">
+    </row>
+    <row r="128" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B128" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="C122" s="44" t="s">
+      <c r="C128" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D122" s="44" t="s">
+      <c r="D128" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="E122" s="44" t="s">
+      <c r="E128" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="F122" s="60"/>
-    </row>
-    <row r="123" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B123" s="44" t="s">
-        <v>494</v>
-      </c>
-      <c r="C123" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="D123" s="44" t="s">
-        <v>493</v>
-      </c>
-      <c r="E123" s="44" t="s">
-        <v>483</v>
-      </c>
-      <c r="F123" s="60"/>
-    </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B124" s="44" t="s">
-        <v>497</v>
-      </c>
-      <c r="C124" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="D124" s="44" t="s">
-        <v>498</v>
-      </c>
-      <c r="E124" s="44" t="s">
-        <v>495</v>
-      </c>
-      <c r="F124" s="60"/>
-    </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B125" s="44" t="s">
-        <v>496</v>
-      </c>
-      <c r="C125" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="D125" s="44" t="s">
-        <v>501</v>
-      </c>
-      <c r="E125" s="44" t="s">
-        <v>499</v>
-      </c>
-      <c r="F125" s="60"/>
-    </row>
-    <row r="126" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B126" s="44" t="s">
-        <v>506</v>
-      </c>
-      <c r="C126" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="D126" s="44" t="s">
-        <v>502</v>
-      </c>
-      <c r="E126" s="44" t="s">
-        <v>500</v>
-      </c>
-      <c r="F126" s="60"/>
-    </row>
-    <row r="127" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B127" s="44" t="s">
-        <v>505</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="F127" s="60"/>
-    </row>
-    <row r="128" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B128" s="44" t="s">
-        <v>511</v>
-      </c>
-      <c r="C128" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="E128" s="44" t="s">
-        <v>507</v>
-      </c>
-      <c r="F128" s="60"/>
     </row>
     <row r="129" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B129" s="1" t="s">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>510</v>
+        <v>493</v>
       </c>
       <c r="E129" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="130" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B130" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="131" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B131" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="132" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B132" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="133" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B133" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="134" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B134" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="F129" s="60"/>
-    </row>
-    <row r="131" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B131" s="56" t="s">
+      <c r="E134" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="135" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B135" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="137" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B137" s="42" t="s">
         <v>165</v>
       </c>
-      <c r="C131" s="56" t="s">
+      <c r="C137" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="D131" s="56" t="s">
+      <c r="D137" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="E131" s="56" t="s">
+      <c r="E137" s="42" t="s">
         <v>129</v>
       </c>
-      <c r="F131" s="66" t="s">
+      <c r="F137" s="51" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="132" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B132" s="44" t="s">
+    <row r="138" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B138" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C132" s="44" t="s">
+      <c r="C138" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D132" s="44" t="s">
+      <c r="D138" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="E132" s="44" t="s">
+      <c r="E138" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="F132" s="60"/>
-    </row>
-    <row r="133" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B133" s="44" t="s">
+    </row>
+    <row r="139" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B139" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C133" s="44" t="s">
+      <c r="C139" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D133" s="44" t="s">
+      <c r="D139" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="E133" s="44" t="s">
+      <c r="E139" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="F133" s="60"/>
-    </row>
-    <row r="135" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B135" s="55" t="s">
+    </row>
+    <row r="141" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B141" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="C135" s="55" t="s">
+      <c r="C141" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="D135" s="55" t="s">
+      <c r="D141" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="E135" s="55" t="s">
+      <c r="E141" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="F135" s="65" t="s">
+      <c r="F141" s="50" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="136" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B136" s="44" t="s">
+    <row r="142" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B142" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C136" s="44" t="s">
+      <c r="C142" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D136" s="44" t="s">
+      <c r="D142" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E136" s="44" t="s">
+      <c r="E142" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="137" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B137" s="44" t="s">
+    <row r="143" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B143" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C137" s="44" t="s">
+      <c r="C143" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D137" s="44" t="s">
+      <c r="D143" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="E137" s="44" t="s">
+      <c r="E143" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="138" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B138" s="44" t="s">
+    <row r="144" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B144" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="C138" s="44" t="s">
+      <c r="C144" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D138" s="44" t="s">
+      <c r="D144" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E138" s="44" t="s">
+      <c r="E144" s="1" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="139" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B139" s="44" t="s">
+    <row r="145" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B145" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C139" s="44" t="s">
+      <c r="C145" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D139" s="44" t="s">
+      <c r="D145" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E139" s="44" t="s">
+      <c r="E145" s="1" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="140" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B140" s="44" t="s">
+    <row r="146" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B146" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="C140" s="44" t="s">
+      <c r="C146" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D140" s="44" t="s">
+      <c r="D146" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E140" s="44" t="s">
+      <c r="E146" s="1" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="141" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B141" s="44" t="s">
+    <row r="147" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B147" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C141" s="44" t="s">
+      <c r="C147" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D141" s="44" t="s">
+      <c r="D147" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="E141" s="44" t="s">
+      <c r="E147" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="142" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B142" s="44" t="s">
+    <row r="148" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B148" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C142" s="44" t="s">
+      <c r="C148" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D142" s="44" t="s">
+      <c r="D148" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="E142" s="44" t="s">
+      <c r="E148" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="143" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B143" s="44" t="s">
+    <row r="149" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B149" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C143" s="44" t="s">
+      <c r="C149" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D143" s="44" t="s">
+      <c r="D149" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="E143" s="44" t="s">
+      <c r="E149" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="145" spans="2:6" ht="22" x14ac:dyDescent="0.3">
-      <c r="B145" s="49" t="s">
+    <row r="151" spans="2:6" ht="22" x14ac:dyDescent="0.3">
+      <c r="B151" s="58" t="s">
         <v>354</v>
       </c>
-      <c r="C145" s="50"/>
-      <c r="D145" s="50"/>
-      <c r="E145" s="50"/>
-      <c r="F145" s="51"/>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B146" s="52" t="s">
+      <c r="C151" s="59"/>
+      <c r="D151" s="59"/>
+      <c r="E151" s="59"/>
+      <c r="F151" s="60"/>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B152" s="38" t="s">
         <v>355</v>
       </c>
-      <c r="C146" s="52" t="s">
+      <c r="C152" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="D146" s="52" t="s">
+      <c r="D152" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="E146" s="52" t="s">
+      <c r="E152" s="38" t="s">
         <v>356</v>
       </c>
-      <c r="F146" s="59" t="s">
+      <c r="F152" s="45" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B147" s="44"/>
-      <c r="C147" s="44"/>
-      <c r="D147" s="44"/>
-      <c r="E147" s="44"/>
-      <c r="F147" s="60"/>
-    </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B148" s="44"/>
-      <c r="C148" s="44"/>
-      <c r="D148" s="44"/>
-      <c r="E148" s="44"/>
-      <c r="F148" s="60"/>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B149" s="44"/>
-      <c r="C149" s="44"/>
-      <c r="D149" s="44"/>
-      <c r="E149" s="44"/>
-      <c r="F149" s="60"/>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B150" s="44"/>
-      <c r="C150" s="44"/>
-      <c r="D150" s="44"/>
-      <c r="E150" s="44"/>
-      <c r="F150" s="60"/>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B151" s="44"/>
-      <c r="C151" s="44"/>
-      <c r="D151" s="44"/>
-      <c r="E151" s="44"/>
-      <c r="F151" s="60"/>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B152" s="44"/>
-      <c r="C152" s="44"/>
-      <c r="D152" s="44"/>
-      <c r="E152" s="44"/>
-      <c r="F152" s="60"/>
-    </row>
-    <row r="153" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B153" s="44"/>
-      <c r="C153" s="44"/>
-      <c r="D153" s="44"/>
-      <c r="E153" s="44"/>
-      <c r="F153" s="60"/>
-    </row>
-    <row r="154" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B154" s="44"/>
-      <c r="C154" s="44"/>
-      <c r="D154" s="44"/>
-      <c r="E154" s="44"/>
-      <c r="F154" s="60"/>
-    </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B155" s="44"/>
-      <c r="C155" s="44"/>
-      <c r="D155" s="44"/>
-      <c r="E155" s="44"/>
-      <c r="F155" s="60"/>
-    </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B156" s="44"/>
-      <c r="C156" s="44"/>
-      <c r="D156" s="44"/>
-      <c r="E156" s="44"/>
-      <c r="F156" s="60"/>
-    </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B157" s="44"/>
-      <c r="C157" s="44"/>
-      <c r="D157" s="44"/>
-      <c r="E157" s="44"/>
-      <c r="F157" s="60"/>
-    </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B158" s="44"/>
-      <c r="C158" s="44"/>
-      <c r="D158" s="44"/>
-      <c r="E158" s="44"/>
-      <c r="F158" s="60"/>
-    </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B159" s="44"/>
-      <c r="C159" s="44"/>
-      <c r="D159" s="44"/>
-      <c r="E159" s="44"/>
-      <c r="F159" s="60"/>
-    </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B160" s="44"/>
-      <c r="C160" s="44"/>
-      <c r="D160" s="44"/>
-      <c r="E160" s="44"/>
-      <c r="F160" s="60"/>
-    </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B161" s="44"/>
-      <c r="C161" s="44"/>
-      <c r="D161" s="44"/>
-      <c r="E161" s="44"/>
-      <c r="F161" s="60"/>
-    </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B162" s="44"/>
-      <c r="C162" s="44"/>
-      <c r="D162" s="44"/>
-      <c r="E162" s="44"/>
-      <c r="F162" s="60"/>
-    </row>
-    <row r="163" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B163" s="44"/>
-      <c r="C163" s="44"/>
-      <c r="D163" s="44"/>
-      <c r="E163" s="44"/>
-      <c r="F163" s="60"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B164" s="44"/>
-      <c r="C164" s="44"/>
-      <c r="D164" s="44"/>
-      <c r="E164" s="44"/>
-      <c r="F164" s="60"/>
-    </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B165" s="44"/>
-      <c r="C165" s="44"/>
-      <c r="D165" s="44"/>
-      <c r="E165" s="44"/>
-      <c r="F165" s="60"/>
-    </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B166" s="44"/>
-      <c r="C166" s="44"/>
-      <c r="D166" s="44"/>
-      <c r="E166" s="44"/>
-      <c r="F166" s="60"/>
-    </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B167" s="44"/>
-      <c r="C167" s="44"/>
-      <c r="D167" s="44"/>
-      <c r="E167" s="44"/>
-      <c r="F167" s="60"/>
-    </row>
-    <row r="168" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B168" s="44"/>
-      <c r="C168" s="44"/>
-      <c r="D168" s="44"/>
-      <c r="E168" s="44"/>
-      <c r="F168" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B145:F145"/>
+    <mergeCell ref="B151:F151"/>
     <mergeCell ref="H4:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5868,17 +5723,17 @@
     <col min="3" max="3" width="38.5" style="3" customWidth="1"/>
     <col min="4" max="5" width="8.83203125" style="3" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" style="12"/>
-    <col min="7" max="7" width="32.6640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.1640625" style="13" customWidth="1"/>
+    <col min="7" max="7" width="32.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.1640625" style="3" customWidth="1"/>
     <col min="9" max="9" width="19.6640625" style="12" customWidth="1"/>
-    <col min="10" max="10" width="30.83203125" style="16" customWidth="1"/>
+    <col min="10" max="10" width="30.83203125" style="15" customWidth="1"/>
     <col min="11" max="11" width="30.83203125" style="10" customWidth="1"/>
-    <col min="12" max="12" width="22" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22" style="3" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="22.5" style="12" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="28.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="26.33203125" style="12" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="30.83203125" style="10" customWidth="1"/>
-    <col min="17" max="17" width="25.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="20.6640625" style="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="27.33203125" style="10" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="24.6640625" style="12" bestFit="1" customWidth="1"/>
@@ -5907,34 +5762,34 @@
       <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>76</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="14" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="13" t="s">
         <v>8</v>
       </c>
       <c r="M1" s="11" t="s">
@@ -5949,7 +5804,7 @@
       <c r="P1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="13" t="s">
         <v>8</v>
       </c>
       <c r="R1" s="11" t="s">
@@ -5961,61 +5816,61 @@
       <c r="T1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="14" t="s">
+      <c r="U1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="V1" s="14" t="s">
+      <c r="V1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="W1" s="14" t="s">
+      <c r="W1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="X1" s="14" t="s">
+      <c r="X1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" s="14" t="s">
+      <c r="Y1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" s="14" t="s">
+      <c r="Z1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="AA1" s="14" t="s">
+      <c r="AA1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="AB1" s="14" t="s">
+      <c r="AB1" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="AC1" s="14" t="s">
+      <c r="AC1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="14" t="s">
+      <c r="AD1" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="AE1" s="14" t="s">
+      <c r="AE1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="AF1" s="14" t="s">
+      <c r="AF1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="AG1" s="14" t="s">
+      <c r="AG1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="AH1" s="14" t="s">
+      <c r="AH1" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="AI1" s="14" t="s">
+      <c r="AI1" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="AJ1" s="14" t="s">
+      <c r="AJ1" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="AK1" s="14" t="s">
+      <c r="AK1" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="AL1" s="14" t="s">
+      <c r="AL1" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="AM1" s="14" t="s">
+      <c r="AM1" s="13" t="s">
         <v>70</v>
       </c>
     </row>
@@ -6065,25 +5920,25 @@
       <c r="C3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="25">
         <v>4254</v>
       </c>
       <c r="E3" s="3">
         <v>500</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="20">
         <v>9.3200000000000005E-2</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="29">
+      <c r="H3" s="27">
         <v>0.16</v>
       </c>
-      <c r="I3" s="28">
+      <c r="I3" s="26">
         <v>5.5E-2</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="15" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6091,7 +5946,7 @@
       <c r="C4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="25">
         <v>4254</v>
       </c>
       <c r="E4" s="3">
@@ -6100,16 +5955,16 @@
       <c r="F4" s="12">
         <v>0.16200000000000001</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="31">
+      <c r="H4" s="29">
         <v>-7.0000000000000001E-3</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="30">
         <v>6.8000000000000005E-2</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="J4" s="15" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6117,7 +5972,7 @@
       <c r="C5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="25">
         <v>4254</v>
       </c>
       <c r="E5" s="3">
@@ -6126,16 +5981,16 @@
       <c r="F5" s="12">
         <v>5.1799999999999999E-2</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="16">
         <v>0.113</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="17">
         <v>0.26200000000000001</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="15" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6143,25 +5998,25 @@
       <c r="C6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="25">
         <v>587</v>
       </c>
       <c r="E6" s="3">
         <v>500</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="20">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="21">
         <v>-0.318</v>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="20">
         <v>0.217</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="J6" s="15" t="s">
         <v>61</v>
       </c>
     </row>
@@ -6169,25 +6024,25 @@
       <c r="C7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="25">
         <v>4254</v>
       </c>
       <c r="E7" s="3">
         <v>500</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="20">
         <v>9.1999999999999998E-2</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="21">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="20">
         <v>0.40100000000000002</v>
       </c>
-      <c r="J7" s="16" t="s">
+      <c r="J7" s="15" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6195,25 +6050,25 @@
       <c r="C8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="25">
         <v>4254</v>
       </c>
       <c r="E8" s="3">
         <v>500</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="20">
         <v>0.16200000000000001</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="21">
         <v>0.23100000000000001</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="20">
         <v>3.9E-2</v>
       </c>
-      <c r="J8" s="16" t="s">
+      <c r="J8" s="15" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6221,25 +6076,25 @@
       <c r="C9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="25">
         <v>4254</v>
       </c>
       <c r="E9" s="3">
         <v>500</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="20">
         <v>5.16E-2</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="21">
         <v>-9.2999999999999999E-2</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="20">
         <v>0.373</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="J9" s="15" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6247,25 +6102,25 @@
       <c r="C10" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="25">
         <v>587</v>
       </c>
       <c r="E10" s="3">
         <v>500</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="20">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="G10" s="30" t="s">
+      <c r="G10" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="27">
         <v>0.97899999999999998</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="26">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="J10" s="16" t="s">
+      <c r="J10" s="15" t="s">
         <v>61</v>
       </c>
     </row>
@@ -6273,25 +6128,25 @@
       <c r="C11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="25">
         <v>4254</v>
       </c>
       <c r="E11" s="3">
         <v>500</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="20">
         <v>9.1999999999999998E-2</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="21">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="I11" s="21">
+      <c r="I11" s="20">
         <v>0.39600000000000002</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="J11" s="15" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6299,25 +6154,25 @@
       <c r="C12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="25">
         <v>4254</v>
       </c>
       <c r="E12" s="3">
         <v>500</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="20">
         <v>0.16200000000000001</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="21">
         <v>0.13100000000000001</v>
       </c>
-      <c r="I12" s="21">
+      <c r="I12" s="20">
         <v>0.20799999999999999</v>
       </c>
-      <c r="J12" s="16" t="s">
+      <c r="J12" s="15" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6325,25 +6180,25 @@
       <c r="C13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="25">
         <v>4254</v>
       </c>
       <c r="E13" s="3">
         <v>500</v>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="20">
         <v>5.1499999999999997E-2</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="21">
         <v>-6.6000000000000003E-2</v>
       </c>
-      <c r="I13" s="22">
+      <c r="I13" s="21">
         <v>0.53100000000000003</v>
       </c>
-      <c r="J13" s="16" t="s">
+      <c r="J13" s="15" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6351,25 +6206,25 @@
       <c r="C14" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="25">
         <v>587</v>
       </c>
       <c r="E14" s="3">
         <v>500</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="20">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="21">
         <v>0.35099999999999998</v>
       </c>
-      <c r="I14" s="21">
+      <c r="I14" s="20">
         <v>0.17899999999999999</v>
       </c>
-      <c r="J14" s="16" t="s">
+      <c r="J14" s="15" t="s">
         <v>61</v>
       </c>
     </row>
@@ -6377,25 +6232,25 @@
       <c r="C15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="25">
         <v>4254</v>
       </c>
       <c r="E15" s="3">
         <v>500</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="20">
         <v>9.2100000000000001E-2</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="22">
+      <c r="H15" s="21">
         <v>-3.0000000000000001E-3</v>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="20">
         <v>0.25800000000000001</v>
       </c>
-      <c r="J15" s="16" t="s">
+      <c r="J15" s="15" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6403,25 +6258,25 @@
       <c r="C16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="25">
         <v>4254</v>
       </c>
       <c r="E16" s="3">
         <v>500</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="20">
         <v>0.16200000000000001</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="27">
         <v>-7.0000000000000001E-3</v>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="26">
         <v>6.8000000000000005E-2</v>
       </c>
-      <c r="J16" s="16" t="s">
+      <c r="J16" s="15" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6429,25 +6284,25 @@
       <c r="C17" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="25">
         <v>4254</v>
       </c>
       <c r="E17" s="3">
         <v>500</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="20">
         <v>5.1400000000000001E-2</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="21">
         <v>1E-3</v>
       </c>
-      <c r="I17" s="21">
+      <c r="I17" s="20">
         <v>0.75800000000000001</v>
       </c>
-      <c r="J17" s="16" t="s">
+      <c r="J17" s="15" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6455,25 +6310,25 @@
       <c r="C18" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="25">
         <v>587</v>
       </c>
       <c r="E18" s="3">
         <v>500</v>
       </c>
-      <c r="F18" s="21">
+      <c r="F18" s="20">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="27">
         <v>-2.4E-2</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="26">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="J18" s="16" t="s">
+      <c r="J18" s="15" t="s">
         <v>61</v>
       </c>
     </row>
@@ -6523,7 +6378,7 @@
       <c r="C20" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="25">
         <v>4254</v>
       </c>
       <c r="E20" s="3">
@@ -6532,16 +6387,16 @@
       <c r="F20" s="12">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="17">
+      <c r="H20" s="16">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="I20" s="18">
+      <c r="I20" s="17">
         <v>0</v>
       </c>
-      <c r="J20" s="16" t="s">
+      <c r="J20" s="15" t="s">
         <v>66</v>
       </c>
     </row>
@@ -6549,7 +6404,7 @@
       <c r="C21" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="25">
         <v>4254</v>
       </c>
       <c r="E21" s="3">
@@ -6558,16 +6413,16 @@
       <c r="F21" s="12">
         <v>0.14099999999999999</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="G21" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H21" s="17">
+      <c r="H21" s="16">
         <v>0.05</v>
       </c>
-      <c r="I21" s="18">
+      <c r="I21" s="17">
         <v>0</v>
       </c>
-      <c r="J21" s="16" t="s">
+      <c r="J21" s="15" t="s">
         <v>67</v>
       </c>
     </row>
@@ -6575,7 +6430,7 @@
       <c r="C22" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="25">
         <v>4254</v>
       </c>
       <c r="E22" s="3">
@@ -6584,16 +6439,16 @@
       <c r="F22" s="12">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="G22" s="13" t="s">
+      <c r="G22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="29">
         <v>0.313</v>
       </c>
-      <c r="I22" s="32">
+      <c r="I22" s="30">
         <v>0</v>
       </c>
-      <c r="J22" s="16" t="s">
+      <c r="J22" s="15" t="s">
         <v>68</v>
       </c>
     </row>
@@ -6601,7 +6456,7 @@
       <c r="C23" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="25">
         <v>4254</v>
       </c>
       <c r="E23" s="3">
@@ -6610,16 +6465,16 @@
       <c r="F23" s="12">
         <v>0.20100000000000001</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="G23" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="31">
+      <c r="H23" s="29">
         <v>0.61499999999999999</v>
       </c>
-      <c r="I23" s="32">
+      <c r="I23" s="30">
         <v>0</v>
       </c>
-      <c r="J23" s="16" t="s">
+      <c r="J23" s="15" t="s">
         <v>69</v>
       </c>
     </row>
@@ -6627,7 +6482,7 @@
       <c r="C24" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="25">
         <v>4254</v>
       </c>
       <c r="E24" s="3">
@@ -6636,16 +6491,16 @@
       <c r="F24" s="12">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="G24" s="13" t="s">
+      <c r="G24" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="16">
         <v>-1.2E-2</v>
       </c>
-      <c r="I24" s="18">
+      <c r="I24" s="17">
         <v>0</v>
       </c>
-      <c r="J24" s="16" t="s">
+      <c r="J24" s="15" t="s">
         <v>66</v>
       </c>
     </row>
@@ -6653,7 +6508,7 @@
       <c r="C25" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="25">
         <v>4254</v>
       </c>
       <c r="E25" s="3">
@@ -6662,16 +6517,16 @@
       <c r="F25" s="12">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="G25" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H25" s="17">
+      <c r="H25" s="16">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I25" s="18">
+      <c r="I25" s="17">
         <v>0.30599999999999999</v>
       </c>
-      <c r="J25" s="16" t="s">
+      <c r="J25" s="15" t="s">
         <v>67</v>
       </c>
     </row>
@@ -6679,7 +6534,7 @@
       <c r="C26" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="25">
         <v>4254</v>
       </c>
       <c r="E26" s="3">
@@ -6688,16 +6543,16 @@
       <c r="F26" s="12">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="G26" s="13" t="s">
+      <c r="G26" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H26" s="17">
+      <c r="H26" s="16">
         <v>-0.58899999999999997</v>
       </c>
-      <c r="I26" s="18">
+      <c r="I26" s="17">
         <v>0</v>
       </c>
-      <c r="J26" s="16" t="s">
+      <c r="J26" s="15" t="s">
         <v>68</v>
       </c>
     </row>
@@ -6705,7 +6560,7 @@
       <c r="C27" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="25">
         <v>4254</v>
       </c>
       <c r="E27" s="3">
@@ -6714,16 +6569,16 @@
       <c r="F27" s="12">
         <v>0.17299999999999999</v>
       </c>
-      <c r="G27" s="13" t="s">
+      <c r="G27" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H27" s="17">
+      <c r="H27" s="16">
         <v>-0.19700000000000001</v>
       </c>
-      <c r="I27" s="18">
+      <c r="I27" s="17">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="J27" s="16" t="s">
+      <c r="J27" s="15" t="s">
         <v>69</v>
       </c>
     </row>
@@ -6731,7 +6586,7 @@
       <c r="C28" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="25">
         <v>4254</v>
       </c>
       <c r="E28" s="3">
@@ -6740,16 +6595,16 @@
       <c r="F28" s="12">
         <v>0.159</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="G28" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H28" s="17">
+      <c r="H28" s="16">
         <v>-3.9E-2</v>
       </c>
-      <c r="I28" s="18">
+      <c r="I28" s="17">
         <v>0</v>
       </c>
-      <c r="J28" s="16" t="s">
+      <c r="J28" s="15" t="s">
         <v>66</v>
       </c>
     </row>
@@ -6757,7 +6612,7 @@
       <c r="C29" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="25">
         <v>4254</v>
       </c>
       <c r="E29" s="3">
@@ -6766,16 +6621,16 @@
       <c r="F29" s="12">
         <v>0.107</v>
       </c>
-      <c r="G29" s="13" t="s">
+      <c r="G29" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H29" s="17">
+      <c r="H29" s="16">
         <v>-3.4000000000000002E-2</v>
       </c>
-      <c r="I29" s="18">
+      <c r="I29" s="17">
         <v>0</v>
       </c>
-      <c r="J29" s="16" t="s">
+      <c r="J29" s="15" t="s">
         <v>67</v>
       </c>
     </row>
@@ -6783,7 +6638,7 @@
       <c r="C30" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="25">
         <v>4254</v>
       </c>
       <c r="E30" s="3">
@@ -6792,16 +6647,16 @@
       <c r="F30" s="12">
         <v>0.20699999999999999</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H30" s="17">
+      <c r="H30" s="16">
         <v>-1.3819999999999999</v>
       </c>
-      <c r="I30" s="18">
+      <c r="I30" s="17">
         <v>0</v>
       </c>
-      <c r="J30" s="16" t="s">
+      <c r="J30" s="15" t="s">
         <v>68</v>
       </c>
     </row>
@@ -6809,7 +6664,7 @@
       <c r="C31" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="25">
         <v>4254</v>
       </c>
       <c r="E31" s="3">
@@ -6818,16 +6673,16 @@
       <c r="F31" s="12">
         <v>0.185</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="16">
         <v>-0.46600000000000003</v>
       </c>
-      <c r="I31" s="18">
+      <c r="I31" s="17">
         <v>0</v>
       </c>
-      <c r="J31" s="16" t="s">
+      <c r="J31" s="15" t="s">
         <v>69</v>
       </c>
     </row>
@@ -6835,7 +6690,7 @@
       <c r="C32" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="25">
         <v>4254</v>
       </c>
       <c r="E32" s="3">
@@ -6844,16 +6699,16 @@
       <c r="F32" s="12">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="G32" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H32" s="17">
+      <c r="H32" s="16">
         <v>1E-3</v>
       </c>
-      <c r="I32" s="18">
+      <c r="I32" s="17">
         <v>0</v>
       </c>
-      <c r="J32" s="16" t="s">
+      <c r="J32" s="15" t="s">
         <v>66</v>
       </c>
     </row>
@@ -6861,7 +6716,7 @@
       <c r="C33" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="25">
         <v>4254</v>
       </c>
       <c r="E33" s="3">
@@ -6870,16 +6725,16 @@
       <c r="F33" s="12">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="G33" s="13" t="s">
+      <c r="G33" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H33" s="17">
+      <c r="H33" s="16">
         <v>-4.0000000000000002E-4</v>
       </c>
-      <c r="I33" s="18">
+      <c r="I33" s="17">
         <v>2E-3</v>
       </c>
-      <c r="J33" s="16" t="s">
+      <c r="J33" s="15" t="s">
         <v>67</v>
       </c>
     </row>
@@ -6887,7 +6742,7 @@
       <c r="C34" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="25">
         <v>4254</v>
       </c>
       <c r="E34" s="3">
@@ -6896,16 +6751,16 @@
       <c r="F34" s="12">
         <v>0.14499999999999999</v>
       </c>
-      <c r="G34" s="13" t="s">
+      <c r="G34" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H34" s="17">
+      <c r="H34" s="16">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="I34" s="18">
+      <c r="I34" s="17">
         <v>0</v>
       </c>
-      <c r="J34" s="16" t="s">
+      <c r="J34" s="15" t="s">
         <v>68</v>
       </c>
     </row>
@@ -6913,7 +6768,7 @@
       <c r="C35" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="25">
         <v>4254</v>
       </c>
       <c r="E35" s="3">
@@ -6922,16 +6777,16 @@
       <c r="F35" s="12">
         <v>0.17</v>
       </c>
-      <c r="G35" s="13" t="s">
+      <c r="G35" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H35" s="17">
+      <c r="H35" s="16">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I35" s="18">
+      <c r="I35" s="17">
         <v>0.13100000000000001</v>
       </c>
-      <c r="J35" s="16" t="s">
+      <c r="J35" s="15" t="s">
         <v>69</v>
       </c>
     </row>
@@ -6981,7 +6836,7 @@
       <c r="C37" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="25">
         <v>4254</v>
       </c>
       <c r="E37" s="3">
@@ -6993,13 +6848,13 @@
       <c r="G37" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H37" s="33">
+      <c r="H37" s="29">
         <v>0.39400000000000002</v>
       </c>
-      <c r="I37" s="33">
+      <c r="I37" s="29">
         <v>2E-3</v>
       </c>
-      <c r="J37" s="16" t="s">
+      <c r="J37" s="15" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7007,7 +6862,7 @@
       <c r="C38" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D38" s="27">
+      <c r="D38" s="25">
         <v>4254</v>
       </c>
       <c r="E38" s="3">
@@ -7019,13 +6874,13 @@
       <c r="G38" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H38" s="34">
+      <c r="H38" s="16">
         <v>0.21199999999999999</v>
       </c>
-      <c r="I38" s="34">
+      <c r="I38" s="16">
         <v>2.4E-2</v>
       </c>
-      <c r="J38" s="16" t="s">
+      <c r="J38" s="15" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7033,7 +6888,7 @@
       <c r="C39" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D39" s="27">
+      <c r="D39" s="25">
         <v>4254</v>
       </c>
       <c r="E39" s="3">
@@ -7045,13 +6900,13 @@
       <c r="G39" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H39" s="33">
+      <c r="H39" s="29">
         <v>0.214</v>
       </c>
-      <c r="I39" s="33">
+      <c r="I39" s="29">
         <v>0.03</v>
       </c>
-      <c r="J39" s="16" t="s">
+      <c r="J39" s="15" t="s">
         <v>31</v>
       </c>
     </row>
@@ -7059,7 +6914,7 @@
       <c r="C40" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D40" s="27">
+      <c r="D40" s="25">
         <v>4254</v>
       </c>
       <c r="E40" s="3">
@@ -7071,13 +6926,13 @@
       <c r="G40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H40" s="34">
+      <c r="H40" s="16">
         <v>-0.16200000000000001</v>
       </c>
-      <c r="I40" s="34">
+      <c r="I40" s="16">
         <v>0.94499999999999995</v>
       </c>
-      <c r="J40" s="16" t="s">
+      <c r="J40" s="15" t="s">
         <v>61</v>
       </c>
     </row>
@@ -7085,7 +6940,7 @@
       <c r="C41" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="27">
+      <c r="D41" s="25">
         <v>4254</v>
       </c>
       <c r="E41" s="3">
@@ -7097,13 +6952,13 @@
       <c r="G41" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H41" s="33">
+      <c r="H41" s="29">
         <v>0.122</v>
       </c>
-      <c r="I41" s="33">
+      <c r="I41" s="29">
         <v>0.08</v>
       </c>
-      <c r="J41" s="16" t="s">
+      <c r="J41" s="15" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7111,7 +6966,7 @@
       <c r="C42" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D42" s="27">
+      <c r="D42" s="25">
         <v>4254</v>
       </c>
       <c r="E42" s="3">
@@ -7123,13 +6978,13 @@
       <c r="G42" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H42" s="34">
+      <c r="H42" s="16">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="I42" s="34">
+      <c r="I42" s="16">
         <v>0.495</v>
       </c>
-      <c r="J42" s="16" t="s">
+      <c r="J42" s="15" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7137,7 +6992,7 @@
       <c r="C43" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D43" s="27">
+      <c r="D43" s="25">
         <v>4254</v>
       </c>
       <c r="E43" s="3">
@@ -7149,13 +7004,13 @@
       <c r="G43" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H43" s="34">
+      <c r="H43" s="16">
         <v>6.3E-2</v>
       </c>
-      <c r="I43" s="34">
+      <c r="I43" s="16">
         <v>0.106</v>
       </c>
-      <c r="J43" s="16" t="s">
+      <c r="J43" s="15" t="s">
         <v>31</v>
       </c>
     </row>
@@ -7163,7 +7018,7 @@
       <c r="C44" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D44" s="27">
+      <c r="D44" s="25">
         <v>4254</v>
       </c>
       <c r="E44" s="3">
@@ -7175,13 +7030,13 @@
       <c r="G44" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H44" s="34">
+      <c r="H44" s="16">
         <v>0.71499999999999997</v>
       </c>
-      <c r="I44" s="34">
+      <c r="I44" s="16">
         <v>-0.47699999999999998</v>
       </c>
-      <c r="J44" s="16" t="s">
+      <c r="J44" s="15" t="s">
         <v>61</v>
       </c>
     </row>
@@ -7189,7 +7044,7 @@
       <c r="C45" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D45" s="27">
+      <c r="D45" s="25">
         <v>4254</v>
       </c>
       <c r="E45" s="3">
@@ -7201,13 +7056,13 @@
       <c r="G45" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H45" s="33">
+      <c r="H45" s="29">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="I45" s="33">
+      <c r="I45" s="29">
         <v>6.8000000000000005E-2</v>
       </c>
-      <c r="J45" s="16" t="s">
+      <c r="J45" s="15" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7215,7 +7070,7 @@
       <c r="C46" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D46" s="27">
+      <c r="D46" s="25">
         <v>4254</v>
       </c>
       <c r="E46" s="3">
@@ -7227,13 +7082,13 @@
       <c r="G46" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H46" s="34">
+      <c r="H46" s="16">
         <v>1E-3</v>
       </c>
-      <c r="I46" s="34">
+      <c r="I46" s="16">
         <v>0.84199999999999997</v>
       </c>
-      <c r="J46" s="16" t="s">
+      <c r="J46" s="15" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7241,7 +7096,7 @@
       <c r="C47" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D47" s="27">
+      <c r="D47" s="25">
         <v>4254</v>
       </c>
       <c r="E47" s="3">
@@ -7253,13 +7108,13 @@
       <c r="G47" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H47" s="33">
+      <c r="H47" s="29">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="I47" s="33">
+      <c r="I47" s="29">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J47" s="16" t="s">
+      <c r="J47" s="15" t="s">
         <v>31</v>
       </c>
     </row>
@@ -7267,7 +7122,7 @@
       <c r="C48" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D48" s="27">
+      <c r="D48" s="25">
         <v>4254</v>
       </c>
       <c r="E48" s="3">
@@ -7279,13 +7134,13 @@
       <c r="G48" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H48" s="34">
+      <c r="H48" s="16">
         <v>-6.6000000000000003E-2</v>
       </c>
-      <c r="I48" s="34">
+      <c r="I48" s="16">
         <v>0.35799999999999998</v>
       </c>
-      <c r="J48" s="16" t="s">
+      <c r="J48" s="15" t="s">
         <v>61</v>
       </c>
     </row>
@@ -7293,7 +7148,7 @@
       <c r="C49" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D49" s="27">
+      <c r="D49" s="25">
         <v>4254</v>
       </c>
       <c r="E49" s="3">
@@ -7305,13 +7160,13 @@
       <c r="G49" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H49" s="34">
+      <c r="H49" s="16">
         <v>-1E-4</v>
       </c>
-      <c r="I49" s="34">
+      <c r="I49" s="16">
         <v>0.98699999999999999</v>
       </c>
-      <c r="J49" s="16" t="s">
+      <c r="J49" s="15" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7319,7 +7174,7 @@
       <c r="C50" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D50" s="27">
+      <c r="D50" s="25">
         <v>4254</v>
       </c>
       <c r="E50" s="3">
@@ -7331,13 +7186,13 @@
       <c r="G50" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H50" s="34">
+      <c r="H50" s="16">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="I50" s="34">
+      <c r="I50" s="16">
         <v>0.13900000000000001</v>
       </c>
-      <c r="J50" s="16" t="s">
+      <c r="J50" s="15" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7345,7 +7200,7 @@
       <c r="C51" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D51" s="27">
+      <c r="D51" s="25">
         <v>4254</v>
       </c>
       <c r="E51" s="3">
@@ -7357,13 +7212,13 @@
       <c r="G51" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H51" s="34">
+      <c r="H51" s="16">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="I51" s="34">
+      <c r="I51" s="16">
         <v>0.19600000000000001</v>
       </c>
-      <c r="J51" s="16" t="s">
+      <c r="J51" s="15" t="s">
         <v>31</v>
       </c>
     </row>
@@ -7371,7 +7226,7 @@
       <c r="C52" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D52" s="27">
+      <c r="D52" s="25">
         <v>4254</v>
       </c>
       <c r="E52" s="3">
@@ -7383,13 +7238,13 @@
       <c r="G52" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H52" s="34">
+      <c r="H52" s="16">
         <v>-8.1000000000000003E-2</v>
       </c>
-      <c r="I52" s="34">
+      <c r="I52" s="16">
         <v>0.33500000000000002</v>
       </c>
-      <c r="J52" s="16" t="s">
+      <c r="J52" s="15" t="s">
         <v>61</v>
       </c>
     </row>
@@ -7452,17 +7307,17 @@
     <col min="3" max="3" width="38.5" style="3" customWidth="1"/>
     <col min="4" max="4" width="8.83203125" style="3" customWidth="1"/>
     <col min="5" max="5" width="10.83203125" style="12"/>
-    <col min="6" max="6" width="32.6640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.1640625" style="13" customWidth="1"/>
+    <col min="6" max="6" width="32.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.1640625" style="3" customWidth="1"/>
     <col min="8" max="8" width="19.6640625" style="12" customWidth="1"/>
-    <col min="9" max="9" width="30.83203125" style="16" customWidth="1"/>
+    <col min="9" max="9" width="30.83203125" style="15" customWidth="1"/>
     <col min="10" max="10" width="30.83203125" style="10" customWidth="1"/>
-    <col min="11" max="11" width="22" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22" style="3" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22.5" style="12" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="28.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="26.33203125" style="12" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="30.83203125" style="10" customWidth="1"/>
-    <col min="16" max="16" width="25.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20.6640625" style="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="27.33203125" style="10" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="24.6640625" style="12" bestFit="1" customWidth="1"/>
@@ -7492,31 +7347,31 @@
       <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>75</v>
       </c>
       <c r="E1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="14" t="s">
         <v>6</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="13" t="s">
         <v>8</v>
       </c>
       <c r="L1" s="11" t="s">
@@ -7531,7 +7386,7 @@
       <c r="O1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="P1" s="13" t="s">
         <v>8</v>
       </c>
       <c r="Q1" s="11" t="s">
@@ -7543,67 +7398,67 @@
       <c r="S1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="T1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="U1" s="14" t="s">
+      <c r="U1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="V1" s="14" t="s">
+      <c r="V1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="W1" s="14" t="s">
+      <c r="W1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="X1" s="14" t="s">
+      <c r="X1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="Y1" s="14" t="s">
+      <c r="Y1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="Z1" s="14" t="s">
+      <c r="Z1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="AA1" s="14" t="s">
+      <c r="AA1" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="AB1" s="14" t="s">
+      <c r="AB1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="AC1" s="14" t="s">
+      <c r="AC1" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="AD1" s="14" t="s">
+      <c r="AD1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="AE1" s="14" t="s">
+      <c r="AE1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="AF1" s="14" t="s">
+      <c r="AF1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="AG1" s="14" t="s">
+      <c r="AG1" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="AH1" s="14" t="s">
+      <c r="AH1" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="AI1" s="14" t="s">
+      <c r="AI1" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="AJ1" s="14" t="s">
+      <c r="AJ1" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="AK1" s="14" t="s">
+      <c r="AK1" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="AL1" s="14" t="s">
+      <c r="AL1" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AM1" s="14" t="s">
+      <c r="AM1" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="AN1" s="14" t="s">
+      <c r="AN1" s="13" t="s">
         <v>86</v>
       </c>
     </row>
@@ -7654,22 +7509,22 @@
       <c r="C3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="25">
         <v>1454</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="20">
         <v>0.10100000000000001</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="21">
         <v>0.20100000000000001</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="21">
         <v>0.124</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="15" t="s">
         <v>29</v>
       </c>
       <c r="T3" s="3" t="s">
@@ -7734,46 +7589,46 @@
       <c r="C4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="25">
         <v>1454</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="20">
         <v>0.112</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="23">
         <v>-0.187</v>
       </c>
       <c r="H4" s="12">
         <v>0.28699999999999998</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="15" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="2:40" x14ac:dyDescent="0.2">
-      <c r="B5" s="36"/>
+      <c r="B5" s="31"/>
       <c r="C5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="37">
+      <c r="D5" s="32">
         <v>1454</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="22">
         <v>9.6299999999999997E-2</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="F5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="19">
         <v>0.30399999999999999</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="18">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="33" t="s">
         <v>31</v>
       </c>
     </row>
@@ -7781,46 +7636,46 @@
       <c r="C6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="25">
         <v>1454</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="20">
         <v>9.9900000000000003E-2</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="21">
         <v>-0.1</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="20">
         <v>0.55600000000000005</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="I6" s="15" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" spans="2:40" x14ac:dyDescent="0.2">
-      <c r="B7" s="36"/>
+      <c r="B7" s="31"/>
       <c r="C7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="32">
         <v>1454</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="18">
         <v>0.114</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="19">
         <v>-0.39400000000000002</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="18">
         <v>0.10199999999999999</v>
       </c>
-      <c r="I7" s="38" t="s">
+      <c r="I7" s="33" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7828,22 +7683,22 @@
       <c r="C8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="25">
         <v>1454</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="20">
         <v>9.35E-2</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="21">
         <v>2.7E-2</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="20">
         <v>0.88600000000000001</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="15" t="s">
         <v>31</v>
       </c>
     </row>
@@ -7851,46 +7706,46 @@
       <c r="C9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="25">
         <v>1454</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="20">
         <v>0.10100000000000001</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="21">
         <v>-0.255</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="20">
         <v>0.13900000000000001</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="I9" s="15" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" spans="2:40" x14ac:dyDescent="0.2">
-      <c r="B10" s="36"/>
+      <c r="B10" s="31"/>
       <c r="C10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="37">
+      <c r="D10" s="32">
         <v>1454</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="18">
         <v>0.122</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="19">
         <v>-0.76600000000000001</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="18">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="I10" s="38" t="s">
+      <c r="I10" s="33" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7898,22 +7753,22 @@
       <c r="C11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="25">
         <v>1454</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="20">
         <v>9.3899999999999997E-2</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="23">
         <v>0.161</v>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="21">
         <v>0.41099999999999998</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="15" t="s">
         <v>31</v>
       </c>
     </row>
@@ -7921,22 +7776,22 @@
       <c r="C12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="25">
         <v>1454</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="20">
         <v>9.9699999999999997E-2</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="21">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="20">
         <v>0.84799999999999998</v>
       </c>
-      <c r="I12" s="16" t="s">
+      <c r="I12" s="15" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7944,22 +7799,22 @@
       <c r="C13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="25">
         <v>1454</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="20">
         <v>0.113</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="21">
         <v>4.7E-2</v>
       </c>
-      <c r="H13" s="21">
+      <c r="H13" s="20">
         <v>0.188</v>
       </c>
-      <c r="I13" s="16" t="s">
+      <c r="I13" s="15" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7967,22 +7822,22 @@
       <c r="C14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="25">
         <v>1454</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="20">
         <v>9.35E-2</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="21">
         <v>-8.9999999999999993E-3</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="20">
         <v>0.77300000000000002</v>
       </c>
-      <c r="I14" s="16" t="s">
+      <c r="I14" s="15" t="s">
         <v>31</v>
       </c>
     </row>
@@ -7990,22 +7845,22 @@
       <c r="C15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="25">
         <v>1454</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="20">
         <v>9.9699999999999997E-2</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="21">
         <v>-7.0000000000000001E-3</v>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="20">
         <v>0.84699999999999998</v>
       </c>
-      <c r="I15" s="16" t="s">
+      <c r="I15" s="15" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8013,22 +7868,22 @@
       <c r="C16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="25">
         <v>1454</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="20">
         <v>0.113</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="21">
         <v>5.8000000000000003E-2</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="20">
         <v>0.16600000000000001</v>
       </c>
-      <c r="I16" s="16" t="s">
+      <c r="I16" s="15" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8036,22 +7891,22 @@
       <c r="C17" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="25">
         <v>1454</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="20">
         <v>9.4500000000000001E-2</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="21">
         <v>-0.05</v>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="21">
         <v>0.23</v>
       </c>
-      <c r="I17" s="16" t="s">
+      <c r="I17" s="15" t="s">
         <v>31</v>
       </c>
     </row>
@@ -8059,94 +7914,94 @@
       <c r="C18" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="25">
         <v>1454</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="20">
         <v>9.9699999999999997E-2</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="35">
+      <c r="G18" s="23">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="H18" s="22">
+      <c r="H18" s="21">
         <v>0.89</v>
       </c>
-      <c r="I18" s="16" t="s">
+      <c r="I18" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="J18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="13"/>
-      <c r="S18" s="13"/>
+      <c r="J18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
     </row>
     <row r="19" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C19" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="25">
         <v>1454</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="20">
         <v>0.111</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F19" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="21">
         <v>-6.5000000000000002E-2</v>
       </c>
-      <c r="H19" s="21">
+      <c r="H19" s="20">
         <v>0.79100000000000004</v>
       </c>
-      <c r="I19" s="16" t="s">
+      <c r="I19" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="J19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="S19" s="13"/>
+      <c r="J19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
     </row>
     <row r="20" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C20" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="25">
         <v>1454</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="20">
         <v>9.3600000000000003E-2</v>
       </c>
-      <c r="F20" s="13" t="s">
+      <c r="F20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="21">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="H20" s="21">
+      <c r="H20" s="20">
         <v>0.72099999999999997</v>
       </c>
-      <c r="I20" s="16" t="s">
+      <c r="I20" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="J20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
-      <c r="S20" s="13"/>
+      <c r="J20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
     </row>
     <row r="21" spans="2:40" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="6" t="s">
@@ -8195,22 +8050,22 @@
       <c r="C22" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="25">
         <v>1454</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="17">
         <v>5.3699999999999998E-2</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="F22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="16">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="H22" s="18">
+      <c r="H22" s="17">
         <v>0.69399999999999995</v>
       </c>
-      <c r="I22" s="16" t="s">
+      <c r="I22" s="15" t="s">
         <v>79</v>
       </c>
     </row>
@@ -8218,22 +8073,22 @@
       <c r="C23" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="37">
+      <c r="D23" s="32">
         <v>1454</v>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="18">
         <v>6.3399999999999998E-2</v>
       </c>
-      <c r="F23" s="24" t="s">
+      <c r="F23" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G23" s="20">
+      <c r="G23" s="19">
         <v>-0.17</v>
       </c>
-      <c r="H23" s="19">
+      <c r="H23" s="18">
         <v>0.23899999999999999</v>
       </c>
-      <c r="I23" s="38" t="s">
+      <c r="I23" s="33" t="s">
         <v>80</v>
       </c>
     </row>
@@ -8241,22 +8096,22 @@
       <c r="C24" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="37">
+      <c r="D24" s="32">
         <v>1454</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="18">
         <v>8.2100000000000006E-2</v>
       </c>
-      <c r="F24" s="24" t="s">
+      <c r="F24" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="19">
         <v>-0.33</v>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="18">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="I24" s="38" t="s">
+      <c r="I24" s="33" t="s">
         <v>81</v>
       </c>
     </row>
@@ -8264,22 +8119,22 @@
       <c r="C25" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D25" s="37">
+      <c r="D25" s="32">
         <v>1454</v>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="18">
         <v>8.43E-2</v>
       </c>
-      <c r="F25" s="24" t="s">
+      <c r="F25" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G25" s="20">
+      <c r="G25" s="19">
         <v>-0.28100000000000003</v>
       </c>
-      <c r="H25" s="19">
+      <c r="H25" s="18">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="I25" s="38" t="s">
+      <c r="I25" s="33" t="s">
         <v>82</v>
       </c>
     </row>
@@ -8287,22 +8142,22 @@
       <c r="C26" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="37">
+      <c r="D26" s="32">
         <v>1454</v>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="18">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="F26" s="24" t="s">
+      <c r="F26" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G26" s="39">
+      <c r="G26" s="19">
         <v>-0.222</v>
       </c>
-      <c r="H26" s="20">
+      <c r="H26" s="19">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="I26" s="38" t="s">
+      <c r="I26" s="33" t="s">
         <v>83</v>
       </c>
     </row>
@@ -8310,22 +8165,22 @@
       <c r="C27" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="25">
         <v>1454</v>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="17">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="F27" s="13" t="s">
+      <c r="F27" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="16">
         <v>-0.17100000000000001</v>
       </c>
-      <c r="H27" s="17">
+      <c r="H27" s="16">
         <v>0.46300000000000002</v>
       </c>
-      <c r="I27" s="16" t="s">
+      <c r="I27" s="15" t="s">
         <v>79</v>
       </c>
     </row>
@@ -8333,22 +8188,22 @@
       <c r="C28" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D28" s="37">
+      <c r="D28" s="32">
         <v>1454</v>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="18">
         <v>6.6600000000000006E-2</v>
       </c>
-      <c r="F28" s="24" t="s">
+      <c r="F28" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G28" s="20">
+      <c r="G28" s="19">
         <v>-0.505</v>
       </c>
-      <c r="H28" s="19">
+      <c r="H28" s="18">
         <v>1.4E-2</v>
       </c>
-      <c r="I28" s="38" t="s">
+      <c r="I28" s="33" t="s">
         <v>80</v>
       </c>
     </row>
@@ -8356,22 +8211,22 @@
       <c r="C29" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="37">
+      <c r="D29" s="32">
         <v>1454</v>
       </c>
-      <c r="E29" s="19">
+      <c r="E29" s="18">
         <v>8.4099999999999994E-2</v>
       </c>
-      <c r="F29" s="24" t="s">
+      <c r="F29" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G29" s="20">
+      <c r="G29" s="19">
         <v>-0.56599999999999995</v>
       </c>
-      <c r="H29" s="20">
+      <c r="H29" s="19">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="I29" s="38" t="s">
+      <c r="I29" s="33" t="s">
         <v>81</v>
       </c>
     </row>
@@ -8379,22 +8234,22 @@
       <c r="C30" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D30" s="37">
+      <c r="D30" s="32">
         <v>1454</v>
       </c>
-      <c r="E30" s="19">
+      <c r="E30" s="18">
         <v>8.4400000000000003E-2</v>
       </c>
-      <c r="F30" s="24" t="s">
+      <c r="F30" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G30" s="20">
+      <c r="G30" s="19">
         <v>-0.38400000000000001</v>
       </c>
-      <c r="H30" s="19">
+      <c r="H30" s="18">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="I30" s="38" t="s">
+      <c r="I30" s="33" t="s">
         <v>82</v>
       </c>
     </row>
@@ -8402,22 +8257,22 @@
       <c r="C31" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="25">
         <v>1454</v>
       </c>
-      <c r="E31" s="18">
+      <c r="E31" s="17">
         <v>8.5500000000000007E-2</v>
       </c>
-      <c r="F31" s="13" t="s">
+      <c r="F31" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="16">
         <v>-0.33900000000000002</v>
       </c>
-      <c r="H31" s="18">
+      <c r="H31" s="17">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="I31" s="16" t="s">
+      <c r="I31" s="15" t="s">
         <v>83</v>
       </c>
     </row>
@@ -8425,22 +8280,22 @@
       <c r="C32" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="25">
         <v>1454</v>
       </c>
-      <c r="E32" s="18">
+      <c r="E32" s="17">
         <v>5.5599999999999997E-2</v>
       </c>
-      <c r="F32" s="13" t="s">
+      <c r="F32" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="16">
         <v>-0.33200000000000002</v>
       </c>
-      <c r="H32" s="18">
+      <c r="H32" s="17">
         <v>0.109</v>
       </c>
-      <c r="I32" s="16" t="s">
+      <c r="I32" s="15" t="s">
         <v>79</v>
       </c>
     </row>
@@ -8448,22 +8303,22 @@
       <c r="C33" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D33" s="37">
+      <c r="D33" s="32">
         <v>1454</v>
       </c>
-      <c r="E33" s="19">
+      <c r="E33" s="18">
         <v>6.83E-2</v>
       </c>
-      <c r="F33" s="24" t="s">
+      <c r="F33" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G33" s="20">
+      <c r="G33" s="19">
         <v>-0.55100000000000005</v>
       </c>
-      <c r="H33" s="19">
+      <c r="H33" s="18">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I33" s="38" t="s">
+      <c r="I33" s="33" t="s">
         <v>80</v>
       </c>
     </row>
@@ -8471,22 +8326,22 @@
       <c r="C34" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D34" s="37">
+      <c r="D34" s="32">
         <v>1454</v>
       </c>
-      <c r="E34" s="19">
+      <c r="E34" s="18">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="F34" s="24" t="s">
+      <c r="F34" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G34" s="20">
+      <c r="G34" s="19">
         <v>-0.56999999999999995</v>
       </c>
-      <c r="H34" s="19">
+      <c r="H34" s="18">
         <v>1E-3</v>
       </c>
-      <c r="I34" s="38" t="s">
+      <c r="I34" s="33" t="s">
         <v>81</v>
       </c>
     </row>
@@ -8494,22 +8349,22 @@
       <c r="C35" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="37">
+      <c r="D35" s="32">
         <v>1454</v>
       </c>
-      <c r="E35" s="19">
+      <c r="E35" s="18">
         <v>8.6599999999999996E-2</v>
       </c>
-      <c r="F35" s="24" t="s">
+      <c r="F35" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G35" s="20">
+      <c r="G35" s="19">
         <v>-0.502</v>
       </c>
-      <c r="H35" s="19">
+      <c r="H35" s="18">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="I35" s="38" t="s">
+      <c r="I35" s="33" t="s">
         <v>82</v>
       </c>
     </row>
@@ -8517,22 +8372,22 @@
       <c r="C36" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="37">
+      <c r="D36" s="32">
         <v>1454</v>
       </c>
-      <c r="E36" s="19">
+      <c r="E36" s="18">
         <v>8.8599999999999998E-2</v>
       </c>
-      <c r="F36" s="24" t="s">
+      <c r="F36" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G36" s="39">
+      <c r="G36" s="19">
         <v>-0.52100000000000002</v>
       </c>
-      <c r="H36" s="19">
+      <c r="H36" s="18">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I36" s="38" t="s">
+      <c r="I36" s="33" t="s">
         <v>83</v>
       </c>
     </row>
@@ -8540,22 +8395,22 @@
       <c r="C37" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="25">
         <v>1454</v>
       </c>
-      <c r="E37" s="18">
+      <c r="E37" s="17">
         <v>5.3800000000000001E-2</v>
       </c>
-      <c r="F37" s="13" t="s">
+      <c r="F37" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G37" s="17">
+      <c r="G37" s="16">
         <v>-2.4E-2</v>
       </c>
-      <c r="H37" s="18">
+      <c r="H37" s="17">
         <v>0.54100000000000004</v>
       </c>
-      <c r="I37" s="16" t="s">
+      <c r="I37" s="15" t="s">
         <v>79</v>
       </c>
     </row>
@@ -8563,22 +8418,22 @@
       <c r="C38" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D38" s="27">
+      <c r="D38" s="25">
         <v>1454</v>
       </c>
-      <c r="E38" s="18">
+      <c r="E38" s="17">
         <v>6.2600000000000003E-2</v>
       </c>
-      <c r="F38" s="13" t="s">
+      <c r="F38" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G38" s="17">
+      <c r="G38" s="16">
         <v>-0.01</v>
       </c>
-      <c r="H38" s="18">
+      <c r="H38" s="17">
         <v>0.76200000000000001</v>
       </c>
-      <c r="I38" s="16" t="s">
+      <c r="I38" s="15" t="s">
         <v>80</v>
       </c>
     </row>
@@ -8586,22 +8441,22 @@
       <c r="C39" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D39" s="27">
+      <c r="D39" s="25">
         <v>1454</v>
       </c>
-      <c r="E39" s="18">
+      <c r="E39" s="17">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="F39" s="13" t="s">
+      <c r="F39" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G39" s="17">
+      <c r="G39" s="16">
         <v>1.6E-2</v>
       </c>
-      <c r="H39" s="18">
+      <c r="H39" s="17">
         <v>0.58599999999999997</v>
       </c>
-      <c r="I39" s="16" t="s">
+      <c r="I39" s="15" t="s">
         <v>81</v>
       </c>
     </row>
@@ -8609,22 +8464,22 @@
       <c r="C40" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D40" s="27">
+      <c r="D40" s="25">
         <v>1454</v>
       </c>
-      <c r="E40" s="18">
+      <c r="E40" s="17">
         <v>8.1900000000000001E-2</v>
       </c>
-      <c r="F40" s="13" t="s">
+      <c r="F40" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G40" s="17">
+      <c r="G40" s="16">
         <v>2E-3</v>
       </c>
-      <c r="H40" s="18">
+      <c r="H40" s="17">
         <v>0.94</v>
       </c>
-      <c r="I40" s="16" t="s">
+      <c r="I40" s="15" t="s">
         <v>82</v>
       </c>
     </row>
@@ -8632,22 +8487,22 @@
       <c r="C41" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D41" s="27">
+      <c r="D41" s="25">
         <v>1454</v>
       </c>
-      <c r="E41" s="18">
+      <c r="E41" s="17">
         <v>8.3500000000000005E-2</v>
       </c>
-      <c r="F41" s="13" t="s">
+      <c r="F41" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G41" s="17">
+      <c r="G41" s="16">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="H41" s="18">
+      <c r="H41" s="17">
         <v>0.995</v>
       </c>
-      <c r="I41" s="16" t="s">
+      <c r="I41" s="15" t="s">
         <v>83</v>
       </c>
     </row>
@@ -8655,22 +8510,22 @@
       <c r="C42" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D42" s="27">
+      <c r="D42" s="25">
         <v>1454</v>
       </c>
-      <c r="E42" s="18">
+      <c r="E42" s="17">
         <v>5.3600000000000002E-2</v>
       </c>
-      <c r="F42" s="13" t="s">
+      <c r="F42" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G42" s="17">
+      <c r="G42" s="16">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="H42" s="18">
+      <c r="H42" s="17">
         <v>0.76</v>
       </c>
-      <c r="I42" s="16" t="s">
+      <c r="I42" s="15" t="s">
         <v>79</v>
       </c>
     </row>
@@ -8678,22 +8533,22 @@
       <c r="C43" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D43" s="27">
+      <c r="D43" s="25">
         <v>1454</v>
       </c>
-      <c r="E43" s="18">
+      <c r="E43" s="17">
         <v>6.3399999999999998E-2</v>
       </c>
-      <c r="F43" s="13" t="s">
+      <c r="F43" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G43" s="17">
+      <c r="G43" s="16">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="H43" s="18">
+      <c r="H43" s="17">
         <v>0.23100000000000001</v>
       </c>
-      <c r="I43" s="16" t="s">
+      <c r="I43" s="15" t="s">
         <v>80</v>
       </c>
     </row>
@@ -8701,22 +8556,22 @@
       <c r="C44" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D44" s="27">
+      <c r="D44" s="25">
         <v>1454</v>
       </c>
-      <c r="E44" s="18">
+      <c r="E44" s="17">
         <v>8.0500000000000002E-2</v>
       </c>
-      <c r="F44" s="13" t="s">
+      <c r="F44" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G44" s="17">
+      <c r="G44" s="16">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="H44" s="18">
+      <c r="H44" s="17">
         <v>7.6999999999999999E-2</v>
       </c>
-      <c r="I44" s="16" t="s">
+      <c r="I44" s="15" t="s">
         <v>81</v>
       </c>
     </row>
@@ -8724,22 +8579,22 @@
       <c r="C45" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D45" s="27">
+      <c r="D45" s="25">
         <v>1454</v>
       </c>
-      <c r="E45" s="18">
+      <c r="E45" s="17">
         <v>8.2799999999999999E-2</v>
       </c>
-      <c r="F45" s="13" t="s">
+      <c r="F45" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G45" s="17">
+      <c r="G45" s="16">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="H45" s="18">
+      <c r="H45" s="17">
         <v>0.185</v>
       </c>
-      <c r="I45" s="16" t="s">
+      <c r="I45" s="15" t="s">
         <v>82</v>
       </c>
     </row>
@@ -8747,22 +8602,22 @@
       <c r="C46" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D46" s="27">
+      <c r="D46" s="25">
         <v>1454</v>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="17">
         <v>8.4099999999999994E-2</v>
       </c>
-      <c r="F46" s="13" t="s">
+      <c r="F46" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G46" s="17">
+      <c r="G46" s="16">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="H46" s="18">
+      <c r="H46" s="17">
         <v>0.27500000000000002</v>
       </c>
-      <c r="I46" s="16" t="s">
+      <c r="I46" s="15" t="s">
         <v>83</v>
       </c>
     </row>
@@ -8770,22 +8625,22 @@
       <c r="C47" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D47" s="27">
+      <c r="D47" s="25">
         <v>1454</v>
       </c>
-      <c r="E47" s="18">
+      <c r="E47" s="17">
         <v>5.4300000000000001E-2</v>
       </c>
-      <c r="F47" s="13" t="s">
+      <c r="F47" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G47" s="17">
+      <c r="G47" s="16">
         <v>0.23799999999999999</v>
       </c>
-      <c r="H47" s="18">
+      <c r="H47" s="17">
         <v>0.33100000000000002</v>
       </c>
-      <c r="I47" s="16" t="s">
+      <c r="I47" s="15" t="s">
         <v>79</v>
       </c>
     </row>
@@ -8793,22 +8648,22 @@
       <c r="C48" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D48" s="27">
+      <c r="D48" s="25">
         <v>1454</v>
       </c>
-      <c r="E48" s="18">
+      <c r="E48" s="17">
         <v>6.3899999999999998E-2</v>
       </c>
-      <c r="F48" s="13" t="s">
+      <c r="F48" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G48" s="17">
+      <c r="G48" s="16">
         <v>0.30199999999999999</v>
       </c>
-      <c r="H48" s="18">
+      <c r="H48" s="17">
         <v>0.14599999999999999</v>
       </c>
-      <c r="I48" s="16" t="s">
+      <c r="I48" s="15" t="s">
         <v>80</v>
       </c>
     </row>
@@ -8816,22 +8671,22 @@
       <c r="C49" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D49" s="27">
+      <c r="D49" s="25">
         <v>1454</v>
       </c>
-      <c r="E49" s="18">
+      <c r="E49" s="17">
         <v>7.9899999999999999E-2</v>
       </c>
-      <c r="F49" s="13" t="s">
+      <c r="F49" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G49" s="17">
+      <c r="G49" s="16">
         <v>0.26500000000000001</v>
       </c>
-      <c r="H49" s="18">
+      <c r="H49" s="17">
         <v>0.17</v>
       </c>
-      <c r="I49" s="16" t="s">
+      <c r="I49" s="15" t="s">
         <v>81</v>
       </c>
     </row>
@@ -8839,22 +8694,22 @@
       <c r="C50" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D50" s="27">
+      <c r="D50" s="25">
         <v>1454</v>
       </c>
-      <c r="E50" s="18">
+      <c r="E50" s="17">
         <v>8.3799999999999999E-2</v>
       </c>
-      <c r="F50" s="13" t="s">
+      <c r="F50" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G50" s="17">
+      <c r="G50" s="16">
         <v>0.35399999999999998</v>
       </c>
-      <c r="H50" s="18">
+      <c r="H50" s="17">
         <v>6.3E-2</v>
       </c>
-      <c r="I50" s="16" t="s">
+      <c r="I50" s="15" t="s">
         <v>82</v>
       </c>
     </row>
@@ -8862,22 +8717,22 @@
       <c r="C51" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D51" s="27">
+      <c r="D51" s="25">
         <v>1454</v>
       </c>
-      <c r="E51" s="18">
+      <c r="E51" s="17">
         <v>8.5599999999999996E-2</v>
       </c>
-      <c r="F51" s="13" t="s">
+      <c r="F51" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G51" s="17">
+      <c r="G51" s="16">
         <v>0.35899999999999999</v>
       </c>
       <c r="H51" s="12">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="I51" s="16" t="s">
+      <c r="I51" s="15" t="s">
         <v>83</v>
       </c>
     </row>
@@ -8928,7 +8783,7 @@
       <c r="C53" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D53" s="27">
+      <c r="D53" s="25">
         <v>1454</v>
       </c>
       <c r="E53" s="12">
@@ -8943,7 +8798,7 @@
       <c r="H53" s="3">
         <v>0</v>
       </c>
-      <c r="I53" s="16" t="s">
+      <c r="I53" s="15" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8951,7 +8806,7 @@
       <c r="C54" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D54" s="27">
+      <c r="D54" s="25">
         <v>1454</v>
       </c>
       <c r="E54" s="12">
@@ -8966,7 +8821,7 @@
       <c r="H54" s="3">
         <v>0</v>
       </c>
-      <c r="I54" s="16" t="s">
+      <c r="I54" s="15" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8974,7 +8829,7 @@
       <c r="C55" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D55" s="27">
+      <c r="D55" s="25">
         <v>1454</v>
       </c>
       <c r="E55" s="12">
@@ -8989,7 +8844,7 @@
       <c r="H55" s="3">
         <v>0.61199999999999999</v>
       </c>
-      <c r="I55" s="16" t="s">
+      <c r="I55" s="15" t="s">
         <v>31</v>
       </c>
     </row>
@@ -8997,7 +8852,7 @@
       <c r="C56" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D56" s="27">
+      <c r="D56" s="25">
         <v>1454</v>
       </c>
       <c r="E56" s="12">
@@ -9012,7 +8867,7 @@
       <c r="H56" s="3">
         <v>0</v>
       </c>
-      <c r="I56" s="16" t="s">
+      <c r="I56" s="15" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9020,7 +8875,7 @@
       <c r="C57" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D57" s="27">
+      <c r="D57" s="25">
         <v>1454</v>
       </c>
       <c r="E57" s="12">
@@ -9035,7 +8890,7 @@
       <c r="H57" s="3">
         <v>0</v>
       </c>
-      <c r="I57" s="16" t="s">
+      <c r="I57" s="15" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9043,7 +8898,7 @@
       <c r="C58" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D58" s="27">
+      <c r="D58" s="25">
         <v>1454</v>
       </c>
       <c r="E58" s="12">
@@ -9058,7 +8913,7 @@
       <c r="H58" s="3">
         <v>0.28100000000000003</v>
       </c>
-      <c r="I58" s="16" t="s">
+      <c r="I58" s="15" t="s">
         <v>31</v>
       </c>
     </row>
@@ -9066,7 +8921,7 @@
       <c r="C59" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D59" s="27">
+      <c r="D59" s="25">
         <v>1454</v>
       </c>
       <c r="E59" s="12">
@@ -9081,7 +8936,7 @@
       <c r="H59" s="3">
         <v>0</v>
       </c>
-      <c r="I59" s="16" t="s">
+      <c r="I59" s="15" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9089,7 +8944,7 @@
       <c r="C60" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D60" s="27">
+      <c r="D60" s="25">
         <v>1454</v>
       </c>
       <c r="E60" s="12">
@@ -9104,7 +8959,7 @@
       <c r="H60" s="3">
         <v>0</v>
       </c>
-      <c r="I60" s="16" t="s">
+      <c r="I60" s="15" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9112,7 +8967,7 @@
       <c r="C61" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D61" s="27">
+      <c r="D61" s="25">
         <v>1454</v>
       </c>
       <c r="E61" s="12">
@@ -9127,7 +8982,7 @@
       <c r="H61" s="3">
         <v>0.39900000000000002</v>
       </c>
-      <c r="I61" s="16" t="s">
+      <c r="I61" s="15" t="s">
         <v>31</v>
       </c>
     </row>
@@ -9135,7 +8990,7 @@
       <c r="C62" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D62" s="27">
+      <c r="D62" s="25">
         <v>1454</v>
       </c>
       <c r="E62" s="12">
@@ -9150,7 +9005,7 @@
       <c r="H62" s="3">
         <v>0</v>
       </c>
-      <c r="I62" s="16" t="s">
+      <c r="I62" s="15" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9158,7 +9013,7 @@
       <c r="C63" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D63" s="27">
+      <c r="D63" s="25">
         <v>1454</v>
       </c>
       <c r="E63" s="12">
@@ -9173,7 +9028,7 @@
       <c r="H63" s="3">
         <v>0</v>
       </c>
-      <c r="I63" s="16" t="s">
+      <c r="I63" s="15" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9181,7 +9036,7 @@
       <c r="C64" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D64" s="27">
+      <c r="D64" s="25">
         <v>1454</v>
       </c>
       <c r="E64" s="12">
@@ -9196,7 +9051,7 @@
       <c r="H64" s="3">
         <v>0.495</v>
       </c>
-      <c r="I64" s="16" t="s">
+      <c r="I64" s="15" t="s">
         <v>31</v>
       </c>
     </row>
@@ -9204,7 +9059,7 @@
       <c r="C65" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D65" s="27">
+      <c r="D65" s="25">
         <v>1454</v>
       </c>
       <c r="E65" s="12">
@@ -9219,7 +9074,7 @@
       <c r="H65" s="3">
         <v>0</v>
       </c>
-      <c r="I65" s="16" t="s">
+      <c r="I65" s="15" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9227,7 +9082,7 @@
       <c r="C66" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D66" s="27">
+      <c r="D66" s="25">
         <v>1454</v>
       </c>
       <c r="E66" s="12">
@@ -9242,7 +9097,7 @@
       <c r="H66" s="3">
         <v>0</v>
       </c>
-      <c r="I66" s="16" t="s">
+      <c r="I66" s="15" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9250,7 +9105,7 @@
       <c r="C67" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D67" s="27">
+      <c r="D67" s="25">
         <v>1454</v>
       </c>
       <c r="E67" s="12">
@@ -9265,7 +9120,7 @@
       <c r="H67" s="3">
         <v>0.753</v>
       </c>
-      <c r="I67" s="16" t="s">
+      <c r="I67" s="15" t="s">
         <v>31</v>
       </c>
     </row>
@@ -9329,17 +9184,17 @@
     <col min="3" max="3" width="38.5" style="3" customWidth="1"/>
     <col min="4" max="4" width="8.83203125" style="3" customWidth="1"/>
     <col min="5" max="5" width="10.83203125" style="12"/>
-    <col min="6" max="6" width="32.6640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.1640625" style="13" customWidth="1"/>
+    <col min="6" max="6" width="32.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.1640625" style="3" customWidth="1"/>
     <col min="8" max="8" width="19.6640625" style="12" customWidth="1"/>
-    <col min="9" max="9" width="30.83203125" style="16" customWidth="1"/>
+    <col min="9" max="9" width="30.83203125" style="15" customWidth="1"/>
     <col min="10" max="10" width="30.83203125" style="10" customWidth="1"/>
-    <col min="11" max="11" width="22" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22" style="3" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22.5" style="12" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="28.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="26.33203125" style="12" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="30.83203125" style="10" customWidth="1"/>
-    <col min="16" max="16" width="25.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20.6640625" style="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="27.33203125" style="10" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="24.6640625" style="12" bestFit="1" customWidth="1"/>
@@ -9369,31 +9224,31 @@
       <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>75</v>
       </c>
       <c r="E1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="14" t="s">
         <v>6</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="13" t="s">
         <v>8</v>
       </c>
       <c r="L1" s="11" t="s">
@@ -9408,7 +9263,7 @@
       <c r="O1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="P1" s="13" t="s">
         <v>8</v>
       </c>
       <c r="Q1" s="11" t="s">
@@ -9420,67 +9275,67 @@
       <c r="S1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="T1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="U1" s="14" t="s">
+      <c r="U1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="V1" s="14" t="s">
+      <c r="V1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="W1" s="14" t="s">
+      <c r="W1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="X1" s="14" t="s">
+      <c r="X1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="Y1" s="14" t="s">
+      <c r="Y1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="Z1" s="14" t="s">
+      <c r="Z1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="AA1" s="14" t="s">
+      <c r="AA1" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="AB1" s="14" t="s">
+      <c r="AB1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="AC1" s="14" t="s">
+      <c r="AC1" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="AD1" s="14" t="s">
+      <c r="AD1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="AE1" s="14" t="s">
+      <c r="AE1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="AF1" s="14" t="s">
+      <c r="AF1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="AG1" s="14" t="s">
+      <c r="AG1" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="AH1" s="14" t="s">
+      <c r="AH1" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="AI1" s="14" t="s">
+      <c r="AI1" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="AJ1" s="14" t="s">
+      <c r="AJ1" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="AK1" s="14" t="s">
+      <c r="AK1" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="AL1" s="14" t="s">
+      <c r="AL1" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AM1" s="14" t="s">
+      <c r="AM1" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="AN1" s="14" t="s">
+      <c r="AN1" s="13" t="s">
         <v>86</v>
       </c>
     </row>
@@ -9528,25 +9383,25 @@
       <c r="AN2" s="8"/>
     </row>
     <row r="3" spans="2:40" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="40">
+      <c r="D3" s="34">
         <v>1557</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="20">
         <v>9.3100000000000002E-2</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="19">
         <v>0.379</v>
       </c>
-      <c r="H3" s="20">
+      <c r="H3" s="19">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="I3" s="41" t="s">
+      <c r="I3" s="35" t="s">
         <v>29</v>
       </c>
       <c r="T3" s="3" t="s">
@@ -9608,49 +9463,49 @@
       </c>
     </row>
     <row r="4" spans="2:40" x14ac:dyDescent="0.2">
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="40">
+      <c r="D4" s="34">
         <v>1557</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="20">
         <v>0.13400000000000001</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="23">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="H4" s="26">
+      <c r="H4" s="24">
         <v>0.68899999999999995</v>
       </c>
-      <c r="I4" s="41" t="s">
+      <c r="I4" s="35" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="2:40" x14ac:dyDescent="0.2">
-      <c r="B5" s="36"/>
-      <c r="C5" s="35" t="s">
+      <c r="B5" s="31"/>
+      <c r="C5" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="40">
+      <c r="D5" s="34">
         <v>1557</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="24">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="21">
         <v>0.34599999999999997</v>
       </c>
-      <c r="H5" s="21">
+      <c r="H5" s="20">
         <v>1.4E-2</v>
       </c>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="35" t="s">
         <v>31</v>
       </c>
     </row>
@@ -9696,35 +9551,35 @@
       <c r="AN6" s="8"/>
     </row>
     <row r="7" spans="2:40" x14ac:dyDescent="0.2">
-      <c r="C7" s="35"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="41"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="35"/>
     </row>
     <row r="8" spans="2:40" x14ac:dyDescent="0.2">
-      <c r="C8" s="35"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="41"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="35"/>
     </row>
     <row r="9" spans="2:40" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C9" s="35"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="41"/>
-      <c r="K9" s="13"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="35"/>
+      <c r="K9" s="3"/>
       <c r="L9" s="12"/>
       <c r="N9" s="12"/>
-      <c r="P9" s="13"/>
+      <c r="P9" s="3"/>
       <c r="Q9" s="12"/>
       <c r="S9" s="12"/>
       <c r="T9" s="3"/>
@@ -9791,57 +9646,39 @@
       <c r="AN10" s="8"/>
     </row>
     <row r="11" spans="2:40" x14ac:dyDescent="0.2">
-      <c r="D11" s="40"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="D11" s="34"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="2:40" x14ac:dyDescent="0.2">
-      <c r="D12" s="40"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
+      <c r="D12" s="34"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="2:40" x14ac:dyDescent="0.2">
-      <c r="D13" s="40"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+      <c r="D13" s="34"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" spans="2:40" x14ac:dyDescent="0.2">
-      <c r="D14" s="40"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="D14" s="34"/>
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="2:40" x14ac:dyDescent="0.2">
-      <c r="D15" s="40"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="D15" s="34"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="2:40" x14ac:dyDescent="0.2">
-      <c r="D16" s="40"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+      <c r="D16" s="34"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" spans="2:40" x14ac:dyDescent="0.2">
-      <c r="D17" s="40"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+      <c r="D17" s="34"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" spans="2:40" x14ac:dyDescent="0.2">
-      <c r="D18" s="40"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
+      <c r="D18" s="34"/>
       <c r="H18" s="3"/>
     </row>
     <row r="19" spans="2:40" x14ac:dyDescent="0.2">
-      <c r="D19" s="40"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
+      <c r="D19" s="34"/>
       <c r="H19" s="3"/>
     </row>
     <row r="20" spans="2:40" ht="23" customHeight="1" x14ac:dyDescent="0.2">

--- a/docs/working_documents/regression_building.xlsx
+++ b/docs/working_documents/regression_building.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/janlinzner/Projects/Master-Thesis-Spatial-Proximity-Venture-Capital/docs/working_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE49A37-20FC-E94D-B455-543D4C6311F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A7F99A-4287-9342-8581-8C6B7A2AD8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{181369B0-5107-194E-B3EC-08338497CAFD}"/>
+    <workbookView xWindow="14820" yWindow="740" windowWidth="14580" windowHeight="18380" xr2:uid="{181369B0-5107-194E-B3EC-08338497CAFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Variables" sheetId="5" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Follow-On-Approach" sheetId="3" r:id="rId3"/>
     <sheet name="Follow-On-Approach(2)" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="550">
   <si>
     <t>Model No.</t>
   </si>
@@ -926,9 +926,6 @@
     <t>Number of years to the succesful exit.</t>
   </si>
   <si>
-    <t>GDP grwoth in percentage in the year of funding.</t>
-  </si>
-  <si>
     <t>VC Investment volume in the country during the First Seed Year.</t>
   </si>
   <si>
@@ -1571,9 +1568,6 @@
     <t>Investee is in the Top10 of the portfolio company network in the peer group inside of 30km.</t>
   </si>
   <si>
-    <t>Only One Seed Investor</t>
-  </si>
-  <si>
     <t>True if there is only one investor in the Seed Phase.</t>
   </si>
   <si>
@@ -1632,6 +1626,69 @@
   </si>
   <si>
     <t>Existing Lead Investor</t>
+  </si>
+  <si>
+    <t>There is at least one angel investor.</t>
+  </si>
+  <si>
+    <t>angel_investor_in_seed_binary</t>
+  </si>
+  <si>
+    <t>follow_on_investor_in_seed_binary</t>
+  </si>
+  <si>
+    <t>Company received follow-on investments in the seed rounds</t>
+  </si>
+  <si>
+    <t>Follow on Investor in Seed</t>
+  </si>
+  <si>
+    <t>Seed Investor Same City 10km</t>
+  </si>
+  <si>
+    <t>Seed Lead Investor Same City 10km</t>
+  </si>
+  <si>
+    <t>Seed Investor Same City 5km</t>
+  </si>
+  <si>
+    <t>Seed Lead Investor Same City 5km</t>
+  </si>
+  <si>
+    <t>There is at least one investor in a radius of 5km.</t>
+  </si>
+  <si>
+    <t>There is at least one lead investor in a radius of 5km.</t>
+  </si>
+  <si>
+    <t>seed_investor_same_city_10</t>
+  </si>
+  <si>
+    <t>seed_lead_investor_same_city_10</t>
+  </si>
+  <si>
+    <t>seed_investor_same_city_5</t>
+  </si>
+  <si>
+    <t>seed_lead_investor_same_city_5</t>
+  </si>
+  <si>
+    <t>regional_angel_investor_in_seed</t>
+  </si>
+  <si>
+    <t>There is a regional angel investor in the seed stage.</t>
+  </si>
+  <si>
+    <t>Regional Angel Investor Binary</t>
+  </si>
+  <si>
+    <t>No Syndication</t>
+  </si>
+  <si>
+    <t>Angel Investor Binary</t>
+  </si>
+  <si>
+    <t>GDP grwoth in percentage in the year of founding.</t>
   </si>
 </sst>
 </file>
@@ -2950,8 +3007,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BADFB1E4-A7C4-874C-A19A-5FD297EA24A2}" name="Table1" displayName="Table1" ref="B46:F99" totalsRowShown="0" headerRowDxfId="78" dataDxfId="77" tableBorderDxfId="76">
-  <autoFilter ref="B46:F99" xr:uid="{BADFB1E4-A7C4-874C-A19A-5FD297EA24A2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BADFB1E4-A7C4-874C-A19A-5FD297EA24A2}" name="Table1" displayName="Table1" ref="B47:F106" totalsRowShown="0" headerRowDxfId="78" dataDxfId="77" tableBorderDxfId="76">
+  <autoFilter ref="B47:F106" xr:uid="{BADFB1E4-A7C4-874C-A19A-5FD297EA24A2}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{E03D4D6E-868B-3040-94BC-AAAFE476C7F6}" name="Investor Features" dataDxfId="75"/>
     <tableColumn id="2" xr3:uid="{9ADA0B6F-8B1B-0F4F-B7B1-0F3B920D2A58}" name="Variable Type" dataDxfId="74"/>
@@ -2964,8 +3021,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C84D18D9-9362-E54C-A5AF-6AFDC1063900}" name="Table11" displayName="Table11" ref="B125:F135" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" tableBorderDxfId="5">
-  <autoFilter ref="B125:F135" xr:uid="{C84D18D9-9362-E54C-A5AF-6AFDC1063900}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{C84D18D9-9362-E54C-A5AF-6AFDC1063900}" name="Table11" displayName="Table11" ref="B132:F142" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" tableBorderDxfId="5">
+  <autoFilter ref="B132:F142" xr:uid="{C84D18D9-9362-E54C-A5AF-6AFDC1063900}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{4E02C00A-6BF8-9745-BACF-E11A643B1EEE}" name="Network Features" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{8D1B5241-A8B2-564E-B8C3-2F886210B738}" name="Variable Type" dataDxfId="3"/>
@@ -2978,8 +3035,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{625C1DBF-28AB-ED4A-8087-CF30592A3B8C}" name="Table2" displayName="Table2" ref="B29:F44" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69" tableBorderDxfId="68">
-  <autoFilter ref="B29:F44" xr:uid="{625C1DBF-28AB-ED4A-8087-CF30592A3B8C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{625C1DBF-28AB-ED4A-8087-CF30592A3B8C}" name="Table2" displayName="Table2" ref="B29:F45" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69" tableBorderDxfId="68">
+  <autoFilter ref="B29:F45" xr:uid="{625C1DBF-28AB-ED4A-8087-CF30592A3B8C}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{20474591-85CB-DC49-904A-CF74017E751E}" name="Financing Features" dataDxfId="67"/>
     <tableColumn id="2" xr3:uid="{643A3B57-58F9-FA49-A71E-8AAAF9F357F4}" name="Variable Type" dataDxfId="66"/>
@@ -3006,8 +3063,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C288A2F5-FAF5-CC45-A73C-1CA5284AEB54}" name="Table4" displayName="Table4" ref="B110:F123" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53" tableBorderDxfId="52">
-  <autoFilter ref="B110:F123" xr:uid="{C288A2F5-FAF5-CC45-A73C-1CA5284AEB54}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C288A2F5-FAF5-CC45-A73C-1CA5284AEB54}" name="Table4" displayName="Table4" ref="B117:F130" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53" tableBorderDxfId="52">
+  <autoFilter ref="B117:F130" xr:uid="{C288A2F5-FAF5-CC45-A73C-1CA5284AEB54}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{AE66DA98-FE07-294A-AA12-55D5C6B9D761}" name="Distance Features (in 1000 km)" dataDxfId="51"/>
     <tableColumn id="2" xr3:uid="{6C5E990C-FE6B-604E-8D81-B062F12ADAA9}" name="Variable Type" dataDxfId="50"/>
@@ -3020,8 +3077,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F0E04D94-3B0E-964F-A888-9EDE8C1AD5F6}" name="Table5" displayName="Table5" ref="B101:F108" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45" tableBorderDxfId="44">
-  <autoFilter ref="B101:F108" xr:uid="{F0E04D94-3B0E-964F-A888-9EDE8C1AD5F6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F0E04D94-3B0E-964F-A888-9EDE8C1AD5F6}" name="Table5" displayName="Table5" ref="B108:F115" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45" tableBorderDxfId="44">
+  <autoFilter ref="B108:F115" xr:uid="{F0E04D94-3B0E-964F-A888-9EDE8C1AD5F6}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{4BA769C3-20C7-694B-B63D-500312785390}" name="Ecosystem Features" dataDxfId="43"/>
     <tableColumn id="2" xr3:uid="{C7CBBF4E-E32C-5349-BA5F-ACCF31548549}" name="Variable Type" dataDxfId="42"/>
@@ -3034,8 +3091,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2E3D645F-AC26-DF46-BD5D-EBAB2942DB82}" name="Table6" displayName="Table6" ref="B141:F149" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37" tableBorderDxfId="36">
-  <autoFilter ref="B141:F149" xr:uid="{2E3D645F-AC26-DF46-BD5D-EBAB2942DB82}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2E3D645F-AC26-DF46-BD5D-EBAB2942DB82}" name="Table6" displayName="Table6" ref="B148:F156" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37" tableBorderDxfId="36">
+  <autoFilter ref="B148:F156" xr:uid="{2E3D645F-AC26-DF46-BD5D-EBAB2942DB82}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{B6190453-A34F-B84E-8F2A-A1D958E4DB06}" name="Outcome Features" dataDxfId="35"/>
     <tableColumn id="2" xr3:uid="{634432B5-6BC9-564F-B291-C6D01B8BD2DB}" name="Variable Type" dataDxfId="34"/>
@@ -3048,8 +3105,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{44C40AD8-7805-764B-8B4F-9295490166FE}" name="Table48" displayName="Table48" ref="B137:F139" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29" tableBorderDxfId="28">
-  <autoFilter ref="B137:F139" xr:uid="{44C40AD8-7805-764B-8B4F-9295490166FE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{44C40AD8-7805-764B-8B4F-9295490166FE}" name="Table48" displayName="Table48" ref="B144:F146" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29" tableBorderDxfId="28">
+  <autoFilter ref="B144:F146" xr:uid="{44C40AD8-7805-764B-8B4F-9295490166FE}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9969B5D0-6C94-A14A-9C38-C48420232A9C}" name="Economical Features" dataDxfId="27"/>
     <tableColumn id="2" xr3:uid="{02D99B72-6F40-A04C-9824-719B2293FF60}" name="Variable Type" dataDxfId="26"/>
@@ -3062,8 +3119,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{6DEEB368-0C4F-284A-B8BF-76292D1E564D}" name="Table310" displayName="Table310" ref="B152:F158" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21" tableBorderDxfId="20">
-  <autoFilter ref="B152:F158" xr:uid="{6DEEB368-0C4F-284A-B8BF-76292D1E564D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{6DEEB368-0C4F-284A-B8BF-76292D1E564D}" name="Table310" displayName="Table310" ref="B159:F165" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21" tableBorderDxfId="20">
+  <autoFilter ref="B159:F165" xr:uid="{6DEEB368-0C4F-284A-B8BF-76292D1E564D}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{456BE63F-58FC-C941-82F8-F6ABD1A7C06C}" name="Features" dataDxfId="19"/>
     <tableColumn id="2" xr3:uid="{F8D792A3-C29A-9F4B-843D-23EE6D488A01}" name="Variable Type" dataDxfId="18"/>
@@ -3408,7 +3465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D84EA5FA-74C6-FF45-8301-AF21701891F8}">
-  <dimension ref="B2:K152"/>
+  <dimension ref="B2:K159"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -3427,7 +3484,7 @@
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E2" s="43" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="2:11" ht="22" x14ac:dyDescent="0.3">
@@ -3439,7 +3496,7 @@
       <c r="E4" s="59"/>
       <c r="F4" s="60"/>
       <c r="H4" s="61" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I4" s="62"/>
       <c r="J4" s="62"/>
@@ -3462,16 +3519,16 @@
         <v>248</v>
       </c>
       <c r="H5" s="41" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I5" s="54" t="s">
         <v>113</v>
       </c>
       <c r="J5" s="41" t="s">
+        <v>366</v>
+      </c>
+      <c r="K5" s="41" t="s">
         <v>367</v>
-      </c>
-      <c r="K5" s="41" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.2">
@@ -3485,16 +3542,16 @@
         <v>204</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H6" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.2">
@@ -3508,16 +3565,16 @@
         <v>205</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -3531,16 +3588,16 @@
         <v>206</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -3557,13 +3614,13 @@
         <v>40</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -3577,16 +3634,16 @@
         <v>208</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -3600,16 +3657,16 @@
         <v>209</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
@@ -3623,16 +3680,16 @@
         <v>210</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
@@ -3649,13 +3706,13 @@
         <v>34</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
@@ -3672,13 +3729,13 @@
         <v>42</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -3695,13 +3752,13 @@
         <v>41</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -3718,13 +3775,13 @@
         <v>36</v>
       </c>
       <c r="H16" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.2">
@@ -3741,13 +3798,13 @@
         <v>37</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.2">
@@ -3764,13 +3821,13 @@
         <v>38</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.2">
@@ -3787,13 +3844,13 @@
         <v>51</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.2">
@@ -3810,13 +3867,13 @@
         <v>52</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.2">
@@ -3833,13 +3890,13 @@
         <v>53</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.2">
@@ -3856,13 +3913,13 @@
         <v>54</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.2">
@@ -3879,13 +3936,13 @@
         <v>55</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.2">
@@ -3902,13 +3959,13 @@
         <v>56</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.2">
@@ -3925,13 +3982,13 @@
         <v>57</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.2">
@@ -3948,13 +4005,13 @@
         <v>58</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.2">
@@ -3971,24 +4028,24 @@
         <v>59</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H28" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.2">
@@ -4008,24 +4065,24 @@
         <v>248</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>124</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>39</v>
@@ -4059,1641 +4116,1739 @@
         <v>88</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="1" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="H33" s="2"/>
+        <v>531</v>
+      </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="1" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="H34" s="2"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
-        <v>527</v>
+        <v>547</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>526</v>
+        <v>509</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>525</v>
+        <v>510</v>
       </c>
       <c r="H35" s="2"/>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="1" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="H36" s="2"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
-        <v>115</v>
+        <v>511</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>228</v>
+        <v>512</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>420</v>
-      </c>
+        <v>513</v>
+      </c>
+      <c r="H37" s="2"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
-        <v>530</v>
+        <v>115</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>529</v>
+        <v>228</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>528</v>
+        <v>302</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="1" t="s">
-        <v>138</v>
+        <v>528</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>229</v>
+        <v>527</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>421</v>
+        <v>526</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="1" t="s">
-        <v>519</v>
+        <v>138</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>520</v>
+        <v>229</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>521</v>
+        <v>60</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
-        <v>190</v>
+        <v>517</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>191</v>
+        <v>123</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>230</v>
+        <v>518</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>423</v>
+        <v>519</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>191</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>304</v>
+        <v>189</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>422</v>
+        <v>192</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>435</v>
+        <v>231</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>434</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B45" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="E45" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B47" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="C47" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="D47" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="E47" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="F47" s="47" t="s">
+        <v>248</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B48" s="43" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="C46" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="D46" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="E46" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="F46" s="47" t="s">
-        <v>248</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B47" s="43" t="s">
-        <v>108</v>
-      </c>
-      <c r="C47" s="43" t="s">
-        <v>124</v>
-      </c>
-      <c r="D47" s="43" t="s">
+      <c r="D48" s="43" t="s">
         <v>232</v>
       </c>
-      <c r="E47" s="43" t="s">
+      <c r="E48" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="F47" s="52"/>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>430</v>
-      </c>
+      <c r="F48" s="52"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B49" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>431</v>
+        <v>305</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>432</v>
+        <v>307</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>124</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>433</v>
+        <v>309</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>311</v>
+        <v>62</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>63</v>
+        <v>310</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>312</v>
+        <v>63</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>65</v>
+        <v>311</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>313</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D60" s="53" t="s">
-        <v>253</v>
+      <c r="D60" s="1" t="s">
+        <v>252</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D61" s="53" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B62" s="1" t="s">
-        <v>130</v>
+        <v>548</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D62" s="53" t="s">
-        <v>255</v>
+        <v>529</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>316</v>
+        <v>530</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B63" s="1" t="s">
-        <v>131</v>
+        <v>546</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D63" s="53" t="s">
-        <v>256</v>
+        <v>545</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>317</v>
+        <v>544</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D64" s="53" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B65" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D65" s="53" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B66" s="1" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>259</v>
+        <v>123</v>
+      </c>
+      <c r="D66" s="53" t="s">
+        <v>256</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B67" s="1" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>260</v>
+        <v>123</v>
+      </c>
+      <c r="D67" s="53" t="s">
+        <v>257</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B68" s="1" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>235</v>
+      <c r="D68" s="53" t="s">
+        <v>258</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>32</v>
+        <v>318</v>
       </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B69" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B70" s="1" t="s">
-        <v>237</v>
+        <v>154</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>74</v>
+        <v>320</v>
       </c>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B71" s="1" t="s">
-        <v>456</v>
+        <v>155</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>444</v>
+        <v>32</v>
       </c>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B72" s="1" t="s">
-        <v>462</v>
+        <v>156</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>445</v>
+        <v>321</v>
       </c>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B73" s="1" t="s">
-        <v>457</v>
+        <v>237</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>468</v>
+        <v>238</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>446</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>469</v>
+        <v>233</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B75" s="55" t="s">
-        <v>458</v>
+      <c r="B75" s="1" t="s">
+        <v>461</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>471</v>
+        <v>234</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B76" s="55" t="s">
-        <v>464</v>
+      <c r="B76" s="1" t="s">
+        <v>456</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B77" s="55" t="s">
-        <v>459</v>
+      <c r="B77" s="1" t="s">
+        <v>462</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B78" s="55" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B79" s="55" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B80" s="55" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B81" s="55" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.2">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B82" s="55" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B83" s="1" t="s">
-        <v>157</v>
+        <v>451</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B83" s="55" t="s">
+        <v>465</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>239</v>
+        <v>475</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B84" s="1" t="s">
-        <v>158</v>
+        <v>452</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B84" s="55" t="s">
+        <v>460</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>240</v>
+        <v>476</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B85" s="1" t="s">
-        <v>159</v>
+        <v>453</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B85" s="55" t="s">
+        <v>466</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>241</v>
+        <v>469</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B86" s="1" t="s">
-        <v>160</v>
+        <v>454</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B86" s="55" t="s">
+        <v>534</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B87" s="1" t="s">
-        <v>360</v>
+        <v>540</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B87" s="55" t="s">
+        <v>535</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>361</v>
+        <v>236</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B88" s="1" t="s">
-        <v>179</v>
+        <v>541</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B88" s="55" t="s">
+        <v>536</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>262</v>
+        <v>538</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B89" s="1" t="s">
-        <v>180</v>
+        <v>542</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B89" s="55" t="s">
+        <v>537</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>263</v>
+        <v>539</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B90" s="43" t="s">
-        <v>186</v>
-      </c>
-      <c r="C90" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="D90" s="43" t="s">
-        <v>270</v>
-      </c>
-      <c r="E90" s="43"/>
-      <c r="F90" s="43"/>
-    </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B91" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="C91" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="D91" s="43" t="s">
-        <v>271</v>
-      </c>
-      <c r="E91" s="43"/>
-      <c r="F91" s="43"/>
-    </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.2">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B90" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B91" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B92" s="1" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B93" s="1" t="s">
-        <v>196</v>
+        <v>160</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.2">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B94" s="1" t="s">
-        <v>198</v>
+        <v>359</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>266</v>
+        <v>360</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.2">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B95" s="1" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B96" s="1" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>90</v>
+        <v>325</v>
       </c>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B97" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C97" s="1" t="s">
+      <c r="B97" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="C97" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>91</v>
-      </c>
+      <c r="D97" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="E97" s="43"/>
+      <c r="F97" s="43"/>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B98" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="C98" s="1" t="s">
+      <c r="B98" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="C98" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>331</v>
-      </c>
+      <c r="D98" s="43" t="s">
+        <v>271</v>
+      </c>
+      <c r="E98" s="43"/>
+      <c r="F98" s="43"/>
     </row>
     <row r="99" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B99" s="1" t="s">
-        <v>328</v>
+        <v>194</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>330</v>
+        <v>265</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>332</v>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B100" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="101" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B101" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="C101" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="D101" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="E101" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="F101" s="48" t="s">
-        <v>248</v>
+      <c r="B101" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B102" s="1" t="s">
-        <v>164</v>
+        <v>200</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>333</v>
+        <v>199</v>
       </c>
     </row>
     <row r="103" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B103" s="1" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>334</v>
+        <v>90</v>
       </c>
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B104" s="1" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>335</v>
+        <v>91</v>
       </c>
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B105" s="1" t="s">
-        <v>183</v>
+        <v>326</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>358</v>
+        <v>328</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="106" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B106" s="1" t="s">
-        <v>184</v>
+        <v>327</v>
       </c>
       <c r="C106" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B108" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="C108" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="D108" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="E108" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="F108" s="48" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B109" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B110" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D106" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B107" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B108" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B110" s="39" t="s">
-        <v>359</v>
-      </c>
-      <c r="C110" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="D110" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="E110" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="F110" s="49" t="s">
-        <v>248</v>
+      <c r="D110" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="111" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B111" s="1" t="s">
-        <v>103</v>
+        <v>182</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="112" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B112" s="1" t="s">
-        <v>107</v>
+        <v>183</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>139</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>276</v>
+        <v>357</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>28</v>
+        <v>335</v>
       </c>
     </row>
     <row r="113" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B113" s="1" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>139</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>78</v>
+        <v>336</v>
       </c>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B114" s="1" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>139</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B115" s="1" t="s">
-        <v>169</v>
+        <v>478</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>139</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>281</v>
+        <v>479</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B116" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>343</v>
+        <v>480</v>
       </c>
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B117" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>342</v>
+      <c r="B117" s="39" t="s">
+        <v>358</v>
+      </c>
+      <c r="C117" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D117" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="E117" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="F117" s="49" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B118" s="1" t="s">
-        <v>173</v>
+        <v>103</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>139</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
     </row>
     <row r="119" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B119" s="1" t="s">
-        <v>174</v>
+        <v>107</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>139</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>346</v>
+        <v>28</v>
       </c>
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B120" s="1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>139</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>345</v>
+        <v>78</v>
       </c>
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B121" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>139</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B122" s="1" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>139</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B123" s="1" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>139</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>349</v>
+        <v>342</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B124" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="125" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B125" s="56" t="s">
-        <v>188</v>
-      </c>
-      <c r="C125" s="56" t="s">
-        <v>112</v>
-      </c>
-      <c r="D125" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="E125" s="56" t="s">
-        <v>129</v>
-      </c>
-      <c r="F125" s="57" t="s">
-        <v>248</v>
+      <c r="B125" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="126" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B126" s="1" t="s">
-        <v>485</v>
+        <v>174</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>489</v>
+        <v>285</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>484</v>
+        <v>345</v>
       </c>
     </row>
     <row r="127" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B127" s="1" t="s">
-        <v>486</v>
+        <v>175</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>490</v>
+        <v>286</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>487</v>
+        <v>344</v>
       </c>
     </row>
     <row r="128" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B128" s="1" t="s">
-        <v>492</v>
+        <v>176</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>139</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>491</v>
+        <v>287</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>488</v>
+        <v>346</v>
       </c>
     </row>
     <row r="129" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B129" s="1" t="s">
-        <v>494</v>
+        <v>177</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>493</v>
+        <v>288</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>483</v>
+        <v>347</v>
       </c>
     </row>
     <row r="130" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B130" s="1" t="s">
-        <v>497</v>
+        <v>178</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>498</v>
+        <v>289</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="131" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B131" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>499</v>
+        <v>348</v>
       </c>
     </row>
     <row r="132" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B132" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>500</v>
+      <c r="B132" s="56" t="s">
+        <v>188</v>
+      </c>
+      <c r="C132" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D132" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="E132" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="F132" s="57" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="133" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B133" s="1" t="s">
-        <v>516</v>
+        <v>484</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>503</v>
+        <v>483</v>
       </c>
     </row>
     <row r="134" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B134" s="1" t="s">
-        <v>517</v>
+        <v>485</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>508</v>
+        <v>489</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>506</v>
+        <v>486</v>
       </c>
     </row>
     <row r="135" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B135" s="1" t="s">
-        <v>518</v>
+        <v>491</v>
       </c>
       <c r="C135" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="136" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B136" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C136" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D135" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>507</v>
+      <c r="D136" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="137" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B137" s="42" t="s">
-        <v>165</v>
-      </c>
-      <c r="C137" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="D137" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="E137" s="42" t="s">
-        <v>129</v>
-      </c>
-      <c r="F137" s="51" t="s">
-        <v>248</v>
+      <c r="B137" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="138" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B138" s="1" t="s">
-        <v>166</v>
+        <v>495</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>295</v>
+        <v>500</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>482</v>
+        <v>498</v>
       </c>
     </row>
     <row r="139" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B139" s="1" t="s">
-        <v>203</v>
+        <v>504</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>296</v>
+        <v>501</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>350</v>
+        <v>499</v>
+      </c>
+    </row>
+    <row r="140" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B140" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="141" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B141" s="41" t="s">
-        <v>100</v>
-      </c>
-      <c r="C141" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="D141" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="E141" s="41" t="s">
-        <v>129</v>
-      </c>
-      <c r="F141" s="50" t="s">
-        <v>248</v>
+      <c r="B141" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="142" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B142" s="1" t="s">
-        <v>135</v>
+        <v>516</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>290</v>
+        <v>508</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="143" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B143" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>30</v>
+        <v>506</v>
       </c>
     </row>
     <row r="144" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B144" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>438</v>
+      <c r="B144" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="C144" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="D144" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="E144" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="F144" s="51" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B145" s="1" t="s">
-        <v>439</v>
+        <v>166</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>292</v>
+        <v>549</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>440</v>
+        <v>481</v>
       </c>
     </row>
     <row r="146" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B146" s="1" t="s">
-        <v>442</v>
+        <v>203</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>443</v>
+        <v>295</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B147" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>29</v>
+        <v>349</v>
       </c>
     </row>
     <row r="148" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B148" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>351</v>
+      <c r="B148" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="C148" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="D148" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="E148" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="F148" s="50" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B149" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B150" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B151" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B152" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B153" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="154" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B154" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="155" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B155" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B156" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C149" s="1" t="s">
+      <c r="C156" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D149" s="1" t="s">
+      <c r="D156" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="E149" s="1" t="s">
+      <c r="E156" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="151" spans="2:6" ht="22" x14ac:dyDescent="0.3">
-      <c r="B151" s="58" t="s">
+    <row r="158" spans="2:6" ht="22" x14ac:dyDescent="0.3">
+      <c r="B158" s="58" t="s">
+        <v>353</v>
+      </c>
+      <c r="C158" s="59"/>
+      <c r="D158" s="59"/>
+      <c r="E158" s="59"/>
+      <c r="F158" s="60"/>
+    </row>
+    <row r="159" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B159" s="38" t="s">
         <v>354</v>
       </c>
-      <c r="C151" s="59"/>
-      <c r="D151" s="59"/>
-      <c r="E151" s="59"/>
-      <c r="F151" s="60"/>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B152" s="38" t="s">
+      <c r="C159" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="D159" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="E159" s="38" t="s">
         <v>355</v>
       </c>
-      <c r="C152" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="D152" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="E152" s="38" t="s">
+      <c r="F159" s="45" t="s">
         <v>356</v>
-      </c>
-      <c r="F152" s="45" t="s">
-        <v>357</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B151:F151"/>
+    <mergeCell ref="B158:F158"/>
     <mergeCell ref="H4:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
